--- a/financials/PNJ/PNJ_financials.xlsx
+++ b/financials/PNJ/PNJ_financials.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,27 +431,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -528,16 +540,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2007488137408</v>
+        <v>97918137408</v>
       </c>
       <c r="C6" t="n">
-        <v>1020170000000</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>810100000000</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>200000000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -775,16 +787,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>95202960069</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>133409476039</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>95896377795</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>79874296558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1402,16 +1414,16 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>327522006625</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>197207058618</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>119826334344</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>119894353423</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2237,10 +2249,18 @@
           <t>Cổ phiếu ưu đãi</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2249,16 +2269,16 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1909570000000</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>1020170000000</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>810100000000</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>200000000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -2770,27 +2790,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -3286,27 +3306,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>

--- a/financials/PNJ/PNJ_financials.xlsx
+++ b/financials/PNJ/PNJ_financials.xlsx
@@ -1,120 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.00\x"/>
-    <numFmt numFmtId="167" formatCode="#,##0&quot; ngày&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="169" formatCode="#,##0 &quot;ngày&quot;"/>
-    <numFmt numFmtId="170" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0 &quot;ngày&quot;"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
+      <b val="1"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <i val="1"/>
-      <color rgb="FF808080"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF008000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <i val="1"/>
-      <color rgb="FF808080"/>
+      <name val="Tahoma"/>
       <sz val="10"/>
     </font>
     <font>
@@ -132,6 +60,13 @@
     <font>
       <name val="Tahoma"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
@@ -162,37 +97,16 @@
     </font>
     <font>
       <name val="Tahoma"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
       <color rgb="00008000"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Tahoma"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF003366"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFCCFFFF"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -214,19 +128,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -243,222 +148,148 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="37">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="22" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00C6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9E1F2"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF1F4E78"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -466,3849 +297,3959 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E123"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" style="15" min="1" max="1"/>
-    <col width="15" customWidth="1" style="15" min="2" max="2"/>
-    <col width="15" customWidth="1" style="15" min="3" max="3"/>
-    <col width="15" customWidth="1" style="15" min="4" max="4"/>
-    <col width="15" customWidth="1" style="15" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="15">
-      <c r="A1" s="32" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" s="33" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" s="33" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" s="33" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" s="33" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="15">
-      <c r="A2" s="34" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>TÀI SẢN NGẮN HẠN</t>
         </is>
       </c>
-      <c r="B2" s="35" t="n">
+      <c r="B2" s="4" t="n">
         <v>18614031193890</v>
       </c>
-      <c r="C2" s="35" t="n">
+      <c r="C2" s="4" t="n">
         <v>15692597267632</v>
       </c>
-      <c r="D2" s="35" t="n">
+      <c r="D2" s="4" t="n">
         <v>12958118192260</v>
       </c>
-      <c r="E2" s="35" t="n">
+      <c r="E2" s="4" t="n">
         <v>11966357761798</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="15">
-      <c r="A3" s="34" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Tiền và tương đương tiền</t>
         </is>
       </c>
-      <c r="B3" s="35" t="n">
+      <c r="B3" s="4" t="n">
         <v>522025257031</v>
       </c>
-      <c r="C3" s="35" t="n">
+      <c r="C3" s="4" t="n">
         <v>1122712392130</v>
       </c>
-      <c r="D3" s="35" t="n">
+      <c r="D3" s="4" t="n">
         <v>896147917336</v>
       </c>
-      <c r="E3" s="35" t="n">
+      <c r="E3" s="4" t="n">
         <v>879548130711</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="15">
-      <c r="A4" s="34" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Tiền</t>
         </is>
       </c>
-      <c r="B4" s="35" t="n">
+      <c r="B4" s="4" t="n">
         <v>438425257031</v>
       </c>
-      <c r="C4" s="35" t="n">
+      <c r="C4" s="4" t="n">
         <v>1022712392130</v>
       </c>
-      <c r="D4" s="35" t="n">
+      <c r="D4" s="4" t="n">
         <v>896147917336</v>
       </c>
-      <c r="E4" s="35" t="n">
+      <c r="E4" s="4" t="n">
         <v>879548130711</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="15">
-      <c r="A5" s="34" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Các khoản tương đương tiền</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="4" t="n">
         <v>83600000000</v>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="4" t="n">
         <v>100000000000</v>
       </c>
-      <c r="D5" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="15">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Đầu tư ngắn hạn</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
-        <v>2007488137408</v>
-      </c>
-      <c r="C6" s="35" t="n">
-        <v>1020170000000</v>
-      </c>
-      <c r="D6" s="35" t="n">
-        <v>810100000000</v>
-      </c>
-      <c r="E6" s="35" t="n">
-        <v>200000000000</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="15">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="B6" s="4" t="n">
+        <v>97918137408</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Đầu tư ngắn hạn</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="4" t="n">
         <v>97918137408</v>
       </c>
-      <c r="C7" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="15">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="C7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Dự phòng giảm giá</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="15">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="B8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Các khoản phải thu</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="4" t="n">
         <v>153980309545</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="4" t="n">
         <v>401134922152</v>
       </c>
-      <c r="D9" s="35" t="n">
+      <c r="D9" s="4" t="n">
         <v>215035937840</v>
       </c>
-      <c r="E9" s="35" t="n">
+      <c r="E9" s="4" t="n">
         <v>300880402245</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="15">
-      <c r="A10" s="34" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Phải thu khách hàng</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="4" t="n">
         <v>48760415990</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="4" t="n">
         <v>70851635761</v>
       </c>
-      <c r="D10" s="35" t="n">
+      <c r="D10" s="4" t="n">
         <v>69277567110</v>
       </c>
-      <c r="E10" s="35" t="n">
+      <c r="E10" s="4" t="n">
         <v>56532707659</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="15">
-      <c r="A11" s="34" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Trả trước người bán</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="4" t="n">
         <v>38085152243</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="4" t="n">
         <v>253102611434</v>
       </c>
-      <c r="D11" s="35" t="n">
+      <c r="D11" s="4" t="n">
         <v>27775617785</v>
       </c>
-      <c r="E11" s="35" t="n">
+      <c r="E11" s="4" t="n">
         <v>68902837213</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="15">
-      <c r="A12" s="34" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Phải thu nội bộ</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="15">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="B12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Phải thu hợp đồng xây dựng đang thực hiện</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="15">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="B13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Phải thu khác</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
+      <c r="B14" s="4" t="n">
         <v>90681158676</v>
       </c>
-      <c r="C14" s="35" t="n">
+      <c r="C14" s="4" t="n">
         <v>64867442121</v>
       </c>
-      <c r="D14" s="35" t="n">
+      <c r="D14" s="4" t="n">
         <v>32980198226</v>
       </c>
-      <c r="E14" s="35" t="n">
+      <c r="E14" s="4" t="n">
         <v>37641170145</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="15">
-      <c r="A15" s="34" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Dự phòng nợ khó đòi</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
+      <c r="B15" s="4" t="n">
         <v>-31918617346</v>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="4" t="n">
         <v>-28518444279</v>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="4" t="n">
         <v>-5049680837</v>
       </c>
-      <c r="E15" s="35" t="n">
+      <c r="E15" s="4" t="n">
         <v>-2862909308</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="15">
-      <c r="A16" s="34" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Hàng tồn kho, ròng</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
+      <c r="B16" s="4" t="n">
         <v>15835334529837</v>
       </c>
-      <c r="C16" s="35" t="n">
+      <c r="C16" s="4" t="n">
         <v>13015170477311</v>
       </c>
-      <c r="D16" s="35" t="n">
+      <c r="D16" s="4" t="n">
         <v>10940937959289</v>
       </c>
-      <c r="E16" s="35" t="n">
+      <c r="E16" s="4" t="n">
         <v>10506054932284</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="15">
-      <c r="A17" s="34" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Hàng tồn kho</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
+      <c r="B17" s="4" t="n">
         <v>15881309718303</v>
       </c>
-      <c r="C17" s="35" t="n">
+      <c r="C17" s="4" t="n">
         <v>13074586927914</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="4" t="n">
         <v>10944749006797</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="4" t="n">
         <v>10508065026916</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="15">
-      <c r="A18" s="34" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Dự phòng giảm giá hàng tồn kho</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
+      <c r="B18" s="4" t="n">
         <v>-45975188466</v>
       </c>
-      <c r="C18" s="35" t="n">
+      <c r="C18" s="4" t="n">
         <v>-59416450603</v>
       </c>
-      <c r="D18" s="35" t="n">
+      <c r="D18" s="4" t="n">
         <v>-3811047508</v>
       </c>
-      <c r="E18" s="35" t="n">
+      <c r="E18" s="4" t="n">
         <v>-2010094632</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="15">
-      <c r="A19" s="34" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Tài sản lưu động khác</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
-        <v>95202960069</v>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>133409476039</v>
-      </c>
-      <c r="D19" s="35" t="n">
-        <v>95896377795</v>
-      </c>
-      <c r="E19" s="35" t="n">
-        <v>79874296558</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="15">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="B19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Chi phí trả trước ngắn hạn</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
+      <c r="B20" s="4" t="n">
         <v>94862372660</v>
       </c>
-      <c r="C20" s="35" t="n">
+      <c r="C20" s="4" t="n">
         <v>132726608716</v>
       </c>
-      <c r="D20" s="35" t="n">
+      <c r="D20" s="4" t="n">
         <v>94051248427</v>
       </c>
-      <c r="E20" s="35" t="n">
+      <c r="E20" s="4" t="n">
         <v>74007356286</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="15">
-      <c r="A21" s="34" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Thuế GTGT được khấu trừ</t>
         </is>
       </c>
-      <c r="B21" s="35" t="n">
+      <c r="B21" s="4" t="n">
         <v>234579085</v>
       </c>
-      <c r="C21" s="35" t="n">
+      <c r="C21" s="4" t="n">
         <v>682867323</v>
       </c>
-      <c r="D21" s="35" t="n">
+      <c r="D21" s="4" t="n">
         <v>1845129368</v>
       </c>
-      <c r="E21" s="35" t="n">
+      <c r="E21" s="4" t="n">
         <v>5866940272</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="15">
-      <c r="A22" s="34" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Phải thu thuế khác</t>
         </is>
       </c>
-      <c r="B22" s="35" t="n">
+      <c r="B22" s="4" t="n">
         <v>106008324</v>
       </c>
-      <c r="C22" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="15">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="C22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Tài sản lưu động khác</t>
         </is>
       </c>
-      <c r="B23" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="15">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="B23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>TÀI SẢN DÀI HẠN</t>
         </is>
       </c>
-      <c r="B24" s="35" t="n">
+      <c r="B24" s="4" t="n">
         <v>1549599053151</v>
       </c>
-      <c r="C24" s="35" t="n">
+      <c r="C24" s="4" t="n">
         <v>1515133510053</v>
       </c>
-      <c r="D24" s="35" t="n">
+      <c r="D24" s="4" t="n">
         <v>1469439823096</v>
       </c>
-      <c r="E24" s="35" t="n">
+      <c r="E24" s="4" t="n">
         <v>1370766887448</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="15">
-      <c r="A25" s="34" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Phải thu dài hạn</t>
         </is>
       </c>
-      <c r="B25" s="35" t="n">
+      <c r="B25" s="4" t="n">
         <v>121168536356</v>
       </c>
-      <c r="C25" s="35" t="n">
+      <c r="C25" s="4" t="n">
         <v>115599492454</v>
       </c>
-      <c r="D25" s="35" t="n">
+      <c r="D25" s="4" t="n">
         <v>104636239106</v>
       </c>
-      <c r="E25" s="35" t="n">
+      <c r="E25" s="4" t="n">
         <v>93956493011</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="15">
-      <c r="A26" s="34" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Phải thu khách hàng dài hạn</t>
         </is>
       </c>
-      <c r="B26" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="15">
-      <c r="A27" s="34" t="inlineStr">
+      <c r="B26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Phải thu nội bộ dài hạn</t>
         </is>
       </c>
-      <c r="B27" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="15">
-      <c r="A28" s="34" t="inlineStr">
+      <c r="B27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Phải thu dài hạn khác</t>
         </is>
       </c>
-      <c r="B28" s="35" t="n">
+      <c r="B28" s="4" t="n">
         <v>121168536356</v>
       </c>
-      <c r="C28" s="35" t="n">
+      <c r="C28" s="4" t="n">
         <v>115599492454</v>
       </c>
-      <c r="D28" s="35" t="n">
+      <c r="D28" s="4" t="n">
         <v>104636239106</v>
       </c>
-      <c r="E28" s="35" t="n">
+      <c r="E28" s="4" t="n">
         <v>93956493011</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="15">
-      <c r="A29" s="34" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Dự phòng phải thu dài hạn</t>
         </is>
       </c>
-      <c r="B29" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="15">
-      <c r="A30" s="34" t="inlineStr">
+      <c r="B29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Tài sản cố định</t>
         </is>
       </c>
-      <c r="B30" s="35" t="n">
+      <c r="B30" s="4" t="n">
         <v>855770473476</v>
       </c>
-      <c r="C30" s="35" t="n">
+      <c r="C30" s="4" t="n">
         <v>857118818527</v>
       </c>
-      <c r="D30" s="35" t="n">
+      <c r="D30" s="4" t="n">
         <v>882715109732</v>
       </c>
-      <c r="E30" s="35" t="n">
+      <c r="E30" s="4" t="n">
         <v>882432821075</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="15">
-      <c r="A31" s="34" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>GTCL TSCĐ hữu hình</t>
         </is>
       </c>
-      <c r="B31" s="35" t="n">
+      <c r="B31" s="4" t="n">
         <v>236245161003</v>
       </c>
-      <c r="C31" s="35" t="n">
+      <c r="C31" s="4" t="n">
         <v>248430247930</v>
       </c>
-      <c r="D31" s="35" t="n">
+      <c r="D31" s="4" t="n">
         <v>256373758673</v>
       </c>
-      <c r="E31" s="35" t="n">
+      <c r="E31" s="4" t="n">
         <v>239734551747</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="15">
-      <c r="A32" s="34" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Nguyên giá TSCĐ hữu hình</t>
         </is>
       </c>
-      <c r="B32" s="35" t="n">
+      <c r="B32" s="4" t="n">
         <v>845032678156</v>
       </c>
-      <c r="C32" s="35" t="n">
+      <c r="C32" s="4" t="n">
         <v>796271142120</v>
       </c>
-      <c r="D32" s="35" t="n">
+      <c r="D32" s="4" t="n">
         <v>747570855214</v>
       </c>
-      <c r="E32" s="35" t="n">
+      <c r="E32" s="4" t="n">
         <v>672781337441</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="15">
-      <c r="A33" s="34" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Khấu hao lũy kế TSCĐ hữu hình</t>
         </is>
       </c>
-      <c r="B33" s="35" t="n">
+      <c r="B33" s="4" t="n">
         <v>-608787517153</v>
       </c>
-      <c r="C33" s="35" t="n">
+      <c r="C33" s="4" t="n">
         <v>-547840894190</v>
       </c>
-      <c r="D33" s="35" t="n">
+      <c r="D33" s="4" t="n">
         <v>-491197096541</v>
       </c>
-      <c r="E33" s="35" t="n">
+      <c r="E33" s="4" t="n">
         <v>-433046785694</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="15">
-      <c r="A34" s="34" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>GTCL tài sản thuê tài chính</t>
         </is>
       </c>
-      <c r="B34" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="15">
-      <c r="A35" s="34" t="inlineStr">
+      <c r="B34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Nguyên giá tài sản thuê tài chính</t>
         </is>
       </c>
-      <c r="B35" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="15">
-      <c r="A36" s="34" t="inlineStr">
+      <c r="B35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Khấu hao lũy kế tài sản thuê tài chính</t>
         </is>
       </c>
-      <c r="B36" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="15">
-      <c r="A37" s="34" t="inlineStr">
+      <c r="B36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>GTCL tài sản cố định vô hình</t>
         </is>
       </c>
-      <c r="B37" s="35" t="n">
+      <c r="B37" s="4" t="n">
         <v>619525312473</v>
       </c>
-      <c r="C37" s="35" t="n">
+      <c r="C37" s="4" t="n">
         <v>608688570597</v>
       </c>
-      <c r="D37" s="35" t="n">
+      <c r="D37" s="4" t="n">
         <v>626341351059</v>
       </c>
-      <c r="E37" s="35" t="n">
+      <c r="E37" s="4" t="n">
         <v>642698269328</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="15">
-      <c r="A38" s="34" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Nguyên giá TSCĐ vô hình</t>
         </is>
       </c>
-      <c r="B38" s="35" t="n">
+      <c r="B38" s="4" t="n">
         <v>734945157553</v>
       </c>
-      <c r="C38" s="35" t="n">
+      <c r="C38" s="4" t="n">
         <v>708142194553</v>
       </c>
-      <c r="D38" s="35" t="n">
+      <c r="D38" s="4" t="n">
         <v>708071904553</v>
       </c>
-      <c r="E38" s="35" t="n">
+      <c r="E38" s="4" t="n">
         <v>707010800099</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="15">
-      <c r="A39" s="34" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Khấu hao lũy kế TSCĐ vô hình</t>
         </is>
       </c>
-      <c r="B39" s="35" t="n">
+      <c r="B39" s="4" t="n">
         <v>-115419845080</v>
       </c>
-      <c r="C39" s="35" t="n">
+      <c r="C39" s="4" t="n">
         <v>-99453623956</v>
       </c>
-      <c r="D39" s="35" t="n">
+      <c r="D39" s="4" t="n">
         <v>-81730553494</v>
       </c>
-      <c r="E39" s="35" t="n">
+      <c r="E39" s="4" t="n">
         <v>-64312530771</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="15">
-      <c r="A40" s="34" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Xây dựng cơ bản đang dang dở (trước 2015)</t>
         </is>
       </c>
-      <c r="B40" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="15">
-      <c r="A41" s="34" t="inlineStr">
+      <c r="B40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Giá trị ròng tài sản đầu tư</t>
         </is>
       </c>
-      <c r="B41" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="15">
-      <c r="A42" s="34" t="inlineStr">
+      <c r="B41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>Nguyên giá tài sản đầu tư</t>
         </is>
       </c>
-      <c r="B42" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="15">
-      <c r="A43" s="34" t="inlineStr">
+      <c r="B42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Khấu hao lũy kế tài sản đầu tư</t>
         </is>
       </c>
-      <c r="B43" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="15">
-      <c r="A44" s="34" t="inlineStr">
+      <c r="B43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Đầu tư dài hạn</t>
         </is>
       </c>
-      <c r="B44" s="35" t="n">
+      <c r="B44" s="4" t="n">
         <v>5930000000</v>
       </c>
-      <c r="C44" s="35" t="n">
+      <c r="C44" s="4" t="n">
         <v>3980000000</v>
       </c>
-      <c r="D44" s="35" t="n">
+      <c r="D44" s="4" t="n">
         <v>3980000000</v>
       </c>
-      <c r="E44" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="15">
-      <c r="A45" s="34" t="inlineStr">
+      <c r="E44" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Đầu tư vào các công ty con</t>
         </is>
       </c>
-      <c r="B45" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="15">
-      <c r="A46" s="34" t="inlineStr">
+      <c r="B45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Đầu tư vào các công ty liên kết</t>
         </is>
       </c>
-      <c r="B46" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="15">
-      <c r="A47" s="34" t="inlineStr">
+      <c r="B46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>Đầu tư dài hạn khác</t>
         </is>
       </c>
-      <c r="B47" s="35" t="n">
+      <c r="B47" s="4" t="n">
         <v>401201613400</v>
       </c>
-      <c r="C47" s="35" t="n">
+      <c r="C47" s="4" t="n">
         <v>399251613400</v>
       </c>
-      <c r="D47" s="35" t="n">
+      <c r="D47" s="4" t="n">
         <v>399251613400</v>
       </c>
-      <c r="E47" s="35" t="n">
+      <c r="E47" s="4" t="n">
         <v>395271613400</v>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="15">
-      <c r="A48" s="34" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Dự phòng giảm giá đầu tư dài hạn</t>
         </is>
       </c>
-      <c r="B48" s="35" t="n">
+      <c r="B48" s="4" t="n">
         <v>-395271613400</v>
       </c>
-      <c r="C48" s="35" t="n">
+      <c r="C48" s="4" t="n">
         <v>-395271613400</v>
       </c>
-      <c r="D48" s="35" t="n">
+      <c r="D48" s="4" t="n">
         <v>-395271613400</v>
       </c>
-      <c r="E48" s="35" t="n">
+      <c r="E48" s="4" t="n">
         <v>-395271613400</v>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="15">
-      <c r="A49" s="34" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Lợi thế thương mại (trước 2015)</t>
         </is>
       </c>
-      <c r="B49" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="15">
-      <c r="A50" s="34" t="inlineStr">
+      <c r="B49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Tài sản dài hạn khác</t>
         </is>
       </c>
-      <c r="B50" s="35" t="n">
+      <c r="B50" s="4" t="n">
         <v>472022383285</v>
       </c>
-      <c r="C50" s="35" t="n">
+      <c r="C50" s="4" t="n">
         <v>473732557913</v>
       </c>
-      <c r="D50" s="35" t="n">
+      <c r="D50" s="4" t="n">
         <v>449008425848</v>
       </c>
-      <c r="E50" s="35" t="n">
+      <c r="E50" s="4" t="n">
         <v>363550944173</v>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" s="15">
-      <c r="A51" s="34" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Trả trước dài hạn</t>
         </is>
       </c>
-      <c r="B51" s="35" t="n">
+      <c r="B51" s="4" t="n">
         <v>144500376660</v>
       </c>
-      <c r="C51" s="35" t="n">
+      <c r="C51" s="4" t="n">
         <v>276525499295</v>
       </c>
-      <c r="D51" s="35" t="n">
+      <c r="D51" s="4" t="n">
         <v>329182091504</v>
       </c>
-      <c r="E51" s="35" t="n">
+      <c r="E51" s="4" t="n">
         <v>243656590750</v>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" s="15">
-      <c r="A52" s="34" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Thuế thu nhập hoãn lại</t>
         </is>
       </c>
-      <c r="B52" s="35" t="n">
-        <v>327522006625</v>
-      </c>
-      <c r="C52" s="35" t="n">
-        <v>197207058618</v>
-      </c>
-      <c r="D52" s="35" t="n">
-        <v>119826334344</v>
-      </c>
-      <c r="E52" s="35" t="n">
-        <v>119894353423</v>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="15">
-      <c r="A53" s="34" t="inlineStr">
+      <c r="B52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Các tài sản dài hạn khác</t>
         </is>
       </c>
-      <c r="B53" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="15">
-      <c r="A54" s="34" t="inlineStr">
+      <c r="B53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>TỔNG CỘNG TÀI SẢN</t>
         </is>
       </c>
-      <c r="B54" s="35" t="n">
+      <c r="B54" s="4" t="n">
         <v>20163630247041</v>
       </c>
-      <c r="C54" s="35" t="n">
+      <c r="C54" s="4" t="n">
         <v>17207730777685</v>
       </c>
-      <c r="D54" s="35" t="n">
+      <c r="D54" s="4" t="n">
         <v>14427558015356</v>
       </c>
-      <c r="E54" s="35" t="n">
+      <c r="E54" s="4" t="n">
         <v>13337124649246</v>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1" s="15">
-      <c r="A55" s="34" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>NỢ PHẢI TRẢ</t>
         </is>
       </c>
-      <c r="B55" s="35" t="n">
+      <c r="B55" s="4" t="n">
         <v>6888716787629</v>
       </c>
-      <c r="C55" s="35" t="n">
+      <c r="C55" s="4" t="n">
         <v>5952424147163</v>
       </c>
-      <c r="D55" s="35" t="n">
+      <c r="D55" s="4" t="n">
         <v>4621377351380</v>
       </c>
-      <c r="E55" s="35" t="n">
+      <c r="E55" s="4" t="n">
         <v>4893029994396</v>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="15">
-      <c r="A56" s="34" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B56" s="35" t="n">
+      <c r="B56" s="4" t="n">
         <v>6874318773629</v>
       </c>
-      <c r="C56" s="35" t="n">
+      <c r="C56" s="4" t="n">
         <v>5941881733413</v>
       </c>
-      <c r="D56" s="35" t="n">
+      <c r="D56" s="4" t="n">
         <v>4611956609380</v>
       </c>
-      <c r="E56" s="35" t="n">
+      <c r="E56" s="4" t="n">
         <v>4883064421396</v>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" s="15">
-      <c r="A57" s="34" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Vay ngắn hạn</t>
         </is>
       </c>
-      <c r="B57" s="35" t="n">
+      <c r="B57" s="4" t="n">
         <v>4223385635653</v>
       </c>
-      <c r="C57" s="35" t="n">
+      <c r="C57" s="4" t="n">
         <v>3341542016760</v>
       </c>
-      <c r="D57" s="35" t="n">
+      <c r="D57" s="4" t="n">
         <v>2384288254693</v>
       </c>
-      <c r="E57" s="35" t="n">
+      <c r="E57" s="4" t="n">
         <v>2683045875772</v>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="15">
-      <c r="A58" s="34" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Phải trả người bán</t>
         </is>
       </c>
-      <c r="B58" s="35" t="n">
+      <c r="B58" s="4" t="n">
         <v>333861329514</v>
       </c>
-      <c r="C58" s="35" t="n">
+      <c r="C58" s="4" t="n">
         <v>624291098148</v>
       </c>
-      <c r="D58" s="35" t="n">
+      <c r="D58" s="4" t="n">
         <v>257304950807</v>
       </c>
-      <c r="E58" s="35" t="n">
+      <c r="E58" s="4" t="n">
         <v>277212839495</v>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" s="15">
-      <c r="A59" s="34" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>Người mua trả tiền trước</t>
         </is>
       </c>
-      <c r="B59" s="35" t="n">
+      <c r="B59" s="4" t="n">
         <v>182492529057</v>
       </c>
-      <c r="C59" s="35" t="n">
+      <c r="C59" s="4" t="n">
         <v>188182044409</v>
       </c>
-      <c r="D59" s="35" t="n">
+      <c r="D59" s="4" t="n">
         <v>215299493413</v>
       </c>
-      <c r="E59" s="35" t="n">
+      <c r="E59" s="4" t="n">
         <v>222164283405</v>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" s="15">
-      <c r="A60" s="34" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>Thuế và các khoản phải trả Nhà nước</t>
         </is>
       </c>
-      <c r="B60" s="35" t="n">
+      <c r="B60" s="4" t="n">
         <v>777717691575</v>
       </c>
-      <c r="C60" s="35" t="n">
+      <c r="C60" s="4" t="n">
         <v>448697283312</v>
       </c>
-      <c r="D60" s="35" t="n">
+      <c r="D60" s="4" t="n">
         <v>344258054659</v>
       </c>
-      <c r="E60" s="35" t="n">
+      <c r="E60" s="4" t="n">
         <v>292985361927</v>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1" s="15">
-      <c r="A61" s="34" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>Phải trả người lao động</t>
         </is>
       </c>
-      <c r="B61" s="35" t="n">
+      <c r="B61" s="4" t="n">
         <v>569308694234</v>
       </c>
-      <c r="C61" s="35" t="n">
+      <c r="C61" s="4" t="n">
         <v>596322426230</v>
       </c>
-      <c r="D61" s="35" t="n">
+      <c r="D61" s="4" t="n">
         <v>673116492808</v>
       </c>
-      <c r="E61" s="35" t="n">
+      <c r="E61" s="4" t="n">
         <v>534807250396</v>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1" s="15">
-      <c r="A62" s="34" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Chi phí phải trả</t>
         </is>
       </c>
-      <c r="B62" s="35" t="n">
+      <c r="B62" s="4" t="n">
         <v>321827090456</v>
       </c>
-      <c r="C62" s="35" t="n">
+      <c r="C62" s="4" t="n">
         <v>360040211420</v>
       </c>
-      <c r="D62" s="35" t="n">
+      <c r="D62" s="4" t="n">
         <v>307718428978</v>
       </c>
-      <c r="E62" s="35" t="n">
+      <c r="E62" s="4" t="n">
         <v>453432735944</v>
       </c>
     </row>
-    <row r="63" ht="15" customHeight="1" s="15">
-      <c r="A63" s="34" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Phải trả nội bộ</t>
         </is>
       </c>
-      <c r="B63" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="15">
-      <c r="A64" s="34" t="inlineStr">
+      <c r="B63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>Phải trả về xây dựng cơ bản</t>
         </is>
       </c>
-      <c r="B64" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="15">
-      <c r="A65" s="34" t="inlineStr">
+      <c r="B64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>Phải trả khác</t>
         </is>
       </c>
-      <c r="B65" s="35" t="n">
+      <c r="B65" s="4" t="n">
         <v>103175435252</v>
       </c>
-      <c r="C65" s="35" t="n">
+      <c r="C65" s="4" t="n">
         <v>106241642105</v>
       </c>
-      <c r="D65" s="35" t="n">
+      <c r="D65" s="4" t="n">
         <v>228798913738</v>
       </c>
-      <c r="E65" s="35" t="n">
+      <c r="E65" s="4" t="n">
         <v>227169093119</v>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1" s="15">
-      <c r="A66" s="34" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>Dự phòng các khoản phải trả ngắn hạn</t>
         </is>
       </c>
-      <c r="B66" s="35" t="n">
+      <c r="B66" s="4" t="n">
         <v>26574672229</v>
       </c>
-      <c r="C66" s="35" t="n">
+      <c r="C66" s="4" t="n">
         <v>26547708303</v>
       </c>
-      <c r="D66" s="35" t="n">
+      <c r="D66" s="4" t="n">
         <v>29061192534</v>
       </c>
-      <c r="E66" s="35" t="n">
+      <c r="E66" s="4" t="n">
         <v>30129306488</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" s="15">
-      <c r="A67" s="34" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Quỹ khen thưởng, phúc lợi</t>
         </is>
       </c>
-      <c r="B67" s="35" t="n">
+      <c r="B67" s="4" t="n">
         <v>335975695659</v>
       </c>
-      <c r="C67" s="35" t="n">
+      <c r="C67" s="4" t="n">
         <v>250017302726</v>
       </c>
-      <c r="D67" s="35" t="n">
+      <c r="D67" s="4" t="n">
         <v>172110827750</v>
       </c>
-      <c r="E67" s="35" t="n">
+      <c r="E67" s="4" t="n">
         <v>162117674850</v>
       </c>
     </row>
-    <row r="68" ht="15" customHeight="1" s="15">
-      <c r="A68" s="34" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>Nợ dài hạn</t>
         </is>
       </c>
-      <c r="B68" s="35" t="n">
+      <c r="B68" s="4" t="n">
         <v>14398014000</v>
       </c>
-      <c r="C68" s="35" t="n">
+      <c r="C68" s="4" t="n">
         <v>10542413750</v>
       </c>
-      <c r="D68" s="35" t="n">
+      <c r="D68" s="4" t="n">
         <v>9420742000</v>
       </c>
-      <c r="E68" s="35" t="n">
+      <c r="E68" s="4" t="n">
         <v>9965573000</v>
       </c>
     </row>
-    <row r="69" ht="15" customHeight="1" s="15">
-      <c r="A69" s="34" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Phải trả nhà cung cấp dài hạn</t>
         </is>
       </c>
-      <c r="B69" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1" s="15">
-      <c r="A70" s="34" t="inlineStr">
+      <c r="B69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>Phải trả nội bộ dài hạn</t>
         </is>
       </c>
-      <c r="B70" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C70" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" ht="15" customHeight="1" s="15">
-      <c r="A71" s="34" t="inlineStr">
+      <c r="B70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>Phải trả dài hạn khác</t>
         </is>
       </c>
-      <c r="B71" s="35" t="n">
+      <c r="B71" s="4" t="n">
         <v>1715384000</v>
       </c>
-      <c r="C71" s="35" t="n">
+      <c r="C71" s="4" t="n">
         <v>178668000</v>
       </c>
-      <c r="D71" s="35" t="n">
+      <c r="D71" s="4" t="n">
         <v>218668000</v>
       </c>
-      <c r="E71" s="35" t="n">
+      <c r="E71" s="4" t="n">
         <v>218668000</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" s="15">
-      <c r="A72" s="34" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>Vay dài hạn</t>
         </is>
       </c>
-      <c r="B72" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1" s="15">
-      <c r="A73" s="34" t="inlineStr">
+      <c r="B72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>Thuế thu nhập hoãn lại</t>
         </is>
       </c>
-      <c r="B73" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C73" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1" s="15">
-      <c r="A74" s="34" t="inlineStr">
+      <c r="B73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>Dự phòng trợ cấp thôi việc</t>
         </is>
       </c>
-      <c r="B74" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C74" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1" s="15">
-      <c r="A75" s="34" t="inlineStr">
+      <c r="B74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>Dự phòng các khoản nợ dài hạn</t>
         </is>
       </c>
-      <c r="B75" s="35" t="n">
+      <c r="B75" s="4" t="n">
         <v>12682630000</v>
       </c>
-      <c r="C75" s="35" t="n">
+      <c r="C75" s="4" t="n">
         <v>10363745750</v>
       </c>
-      <c r="D75" s="35" t="n">
+      <c r="D75" s="4" t="n">
         <v>9202074000</v>
       </c>
-      <c r="E75" s="35" t="n">
+      <c r="E75" s="4" t="n">
         <v>9746905000</v>
       </c>
     </row>
-    <row r="76" ht="15" customHeight="1" s="15">
-      <c r="A76" s="34" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>Doanh thu chưa thực hiện</t>
         </is>
       </c>
-      <c r="B76" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1" s="15">
-      <c r="A77" s="34" t="inlineStr">
+      <c r="B76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>Quỹ phát triển khoa học công nghệ</t>
         </is>
       </c>
-      <c r="B77" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1" s="15">
-      <c r="A78" s="34" t="inlineStr">
+      <c r="B77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B78" s="35" t="n">
+      <c r="B78" s="4" t="n">
         <v>13274913459412</v>
       </c>
-      <c r="C78" s="35" t="n">
+      <c r="C78" s="4" t="n">
         <v>11255306630522</v>
       </c>
-      <c r="D78" s="35" t="n">
+      <c r="D78" s="4" t="n">
         <v>9806180663976</v>
       </c>
-      <c r="E78" s="35" t="n">
+      <c r="E78" s="4" t="n">
         <v>8444094654850</v>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1" s="15">
-      <c r="A79" s="34" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>Vốn và các quỹ</t>
         </is>
       </c>
-      <c r="B79" s="35" t="n">
+      <c r="B79" s="4" t="n">
         <v>13274913459412</v>
       </c>
-      <c r="C79" s="35" t="n">
+      <c r="C79" s="4" t="n">
         <v>11255306630522</v>
       </c>
-      <c r="D79" s="35" t="n">
+      <c r="D79" s="4" t="n">
         <v>9806180663976</v>
       </c>
-      <c r="E79" s="35" t="n">
+      <c r="E79" s="4" t="n">
         <v>8444094654850</v>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1" s="15">
-      <c r="A80" s="34" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>Vốn góp</t>
         </is>
       </c>
-      <c r="B80" s="35" t="n">
+      <c r="B80" s="4" t="n">
         <v>3413186660000</v>
       </c>
-      <c r="C80" s="35" t="n">
+      <c r="C80" s="4" t="n">
         <v>3380747760000</v>
       </c>
-      <c r="D80" s="35" t="n">
+      <c r="D80" s="4" t="n">
         <v>3281691880000</v>
       </c>
-      <c r="E80" s="35" t="n">
+      <c r="E80" s="4" t="n">
         <v>2461716200000</v>
       </c>
     </row>
-    <row r="81" ht="15" customHeight="1" s="15">
-      <c r="A81" s="34" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Thặng dư vốn cổ phần</t>
         </is>
       </c>
-      <c r="B81" s="35" t="n">
+      <c r="B81" s="4" t="n">
         <v>1982694812458</v>
       </c>
-      <c r="C81" s="35" t="n">
+      <c r="C81" s="4" t="n">
         <v>1950309912458</v>
       </c>
-      <c r="D81" s="35" t="n">
+      <c r="D81" s="4" t="n">
         <v>1851376032458</v>
       </c>
-      <c r="E81" s="35" t="n">
+      <c r="E81" s="4" t="n">
         <v>2251376032458</v>
       </c>
     </row>
-    <row r="82" ht="15" customHeight="1" s="15">
-      <c r="A82" s="34" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>Vốn khác</t>
         </is>
       </c>
-      <c r="B82" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C82" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" ht="15" customHeight="1" s="15">
-      <c r="A83" s="34" t="inlineStr">
+      <c r="B82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>Cổ phiếu quỹ</t>
         </is>
       </c>
-      <c r="B83" s="35" t="n">
+      <c r="B83" s="4" t="n">
         <v>-3384090000</v>
       </c>
-      <c r="C83" s="35" t="n">
+      <c r="C83" s="4" t="n">
         <v>-3384090000</v>
       </c>
-      <c r="D83" s="35" t="n">
+      <c r="D83" s="4" t="n">
         <v>-3384090000</v>
       </c>
-      <c r="E83" s="35" t="n">
+      <c r="E83" s="4" t="n">
         <v>-3384090000</v>
       </c>
     </row>
-    <row r="84" ht="15" customHeight="1" s="15">
-      <c r="A84" s="34" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>Chênh lệch đánh giá lại tài sản</t>
         </is>
       </c>
-      <c r="B84" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C84" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" ht="15" customHeight="1" s="15">
-      <c r="A85" s="34" t="inlineStr">
+      <c r="B84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>Chênh lệch tỷ giá</t>
         </is>
       </c>
-      <c r="B85" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" ht="15" customHeight="1" s="15">
-      <c r="A86" s="34" t="inlineStr">
+      <c r="B85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>Quỹ đầu tư và phát triển</t>
         </is>
       </c>
-      <c r="B86" s="35" t="n">
+      <c r="B86" s="4" t="n">
         <v>3471447556918</v>
       </c>
-      <c r="C86" s="35" t="n">
+      <c r="C86" s="4" t="n">
         <v>2626281556918</v>
       </c>
-      <c r="D86" s="35" t="n">
+      <c r="D86" s="4" t="n">
         <v>1936397556918</v>
       </c>
-      <c r="E86" s="35" t="n">
+      <c r="E86" s="4" t="n">
         <v>1212120556918</v>
       </c>
     </row>
-    <row r="87" ht="15" customHeight="1" s="15">
-      <c r="A87" s="34" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>Quỹ dự phòng tài chính</t>
         </is>
       </c>
-      <c r="B87" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" ht="15" customHeight="1" s="15">
-      <c r="A88" s="34" t="inlineStr">
+      <c r="B87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>Quỹ khác</t>
         </is>
       </c>
-      <c r="B88" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C88" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" ht="15" customHeight="1" s="15">
-      <c r="A89" s="34" t="inlineStr">
+      <c r="B88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>Lãi chưa phân phối</t>
         </is>
       </c>
-      <c r="B89" s="35" t="n">
+      <c r="B89" s="4" t="n">
         <v>4410968520036</v>
       </c>
-      <c r="C89" s="35" t="n">
+      <c r="C89" s="4" t="n">
         <v>3301351491146</v>
       </c>
-      <c r="D89" s="35" t="n">
+      <c r="D89" s="4" t="n">
         <v>2740099284600</v>
       </c>
-      <c r="E89" s="35" t="n">
+      <c r="E89" s="4" t="n">
         <v>2522265955474</v>
       </c>
     </row>
-    <row r="90" ht="15" customHeight="1" s="15">
-      <c r="A90" s="34" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>Quỹ hỗ trợ sắp xếp doanh nghiệp</t>
         </is>
       </c>
-      <c r="B90" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C90" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" ht="15" customHeight="1" s="15">
-      <c r="A91" s="34" t="inlineStr">
+      <c r="B90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>Vốn Ngân sách nhà nước và quỹ khác</t>
         </is>
       </c>
-      <c r="B91" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" ht="15" customHeight="1" s="15">
-      <c r="A92" s="34" t="inlineStr">
+      <c r="B91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>Quỹ khen thưởng, phúc lợi (trước 2010)</t>
         </is>
       </c>
-      <c r="B92" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" ht="15" customHeight="1" s="15">
-      <c r="A93" s="34" t="inlineStr">
+      <c r="B92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>Vốn ngân sách nhà nước và quỹ khác</t>
         </is>
       </c>
-      <c r="B93" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C93" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" ht="15" customHeight="1" s="15">
-      <c r="A94" s="34" t="inlineStr">
+      <c r="B93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>Lợi ích của cổ đông thiểu số</t>
         </is>
       </c>
-      <c r="B94" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C94" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" ht="15" customHeight="1" s="15">
-      <c r="A95" s="34" t="inlineStr">
+      <c r="B94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>Tổng cộng nguồn vốn</t>
         </is>
       </c>
-      <c r="B95" s="35" t="n">
+      <c r="B95" s="4" t="n">
         <v>20163630247041</v>
       </c>
-      <c r="C95" s="35" t="n">
+      <c r="C95" s="4" t="n">
         <v>17207730777685</v>
       </c>
-      <c r="D95" s="35" t="n">
+      <c r="D95" s="4" t="n">
         <v>14427558015356</v>
       </c>
-      <c r="E95" s="35" t="n">
+      <c r="E95" s="4" t="n">
         <v>13337124649246</v>
       </c>
     </row>
-    <row r="96" ht="15" customHeight="1" s="15">
-      <c r="A96" s="34" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>Cổ phiếu ưu đãi</t>
         </is>
       </c>
-      <c r="B96" s="36" t="n"/>
-      <c r="C96" s="36" t="n"/>
-      <c r="D96" s="36" t="n"/>
-      <c r="E96" s="36" t="n"/>
-    </row>
-    <row r="97" ht="15" customHeight="1" s="15">
-      <c r="A97" s="34" t="inlineStr">
+      <c r="B96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>Đầu tư nắm giữ đến ngày đáo hạn</t>
         </is>
       </c>
-      <c r="B97" s="35" t="n">
-        <v>1909570000000</v>
-      </c>
-      <c r="C97" s="35" t="n">
-        <v>1020170000000</v>
-      </c>
-      <c r="D97" s="35" t="n">
-        <v>810100000000</v>
-      </c>
-      <c r="E97" s="35" t="n">
-        <v>200000000000</v>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1" s="15">
-      <c r="A98" s="34" t="inlineStr">
+      <c r="B97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>Vốn kinh doanh ở các đơn vị trực thuộc</t>
         </is>
       </c>
-      <c r="B98" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C98" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" ht="15" customHeight="1" s="15">
-      <c r="A99" s="34" t="inlineStr">
+      <c r="B98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>Tài sản thiếu cần xử lý</t>
         </is>
       </c>
-      <c r="B99" s="35" t="n">
+      <c r="B99" s="4" t="n">
         <v>372199982</v>
       </c>
-      <c r="C99" s="35" t="n">
+      <c r="C99" s="4" t="n">
         <v>831677115</v>
       </c>
-      <c r="D99" s="35" t="n">
+      <c r="D99" s="4" t="n">
         <v>52235556</v>
       </c>
-      <c r="E99" s="35" t="n">
+      <c r="E99" s="4" t="n">
         <v>666596536</v>
       </c>
     </row>
-    <row r="100" ht="15" customHeight="1" s="15">
-      <c r="A100" s="34" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>Phải thu cho vay ngắn hạn</t>
         </is>
       </c>
-      <c r="B100" s="35" t="n">
+      <c r="B100" s="4" t="n">
         <v>8000000000</v>
       </c>
-      <c r="C100" s="35" t="n">
+      <c r="C100" s="4" t="n">
         <v>40000000000</v>
       </c>
-      <c r="D100" s="35" t="n">
+      <c r="D100" s="4" t="n">
         <v>90000000000</v>
       </c>
-      <c r="E100" s="35" t="n">
+      <c r="E100" s="4" t="n">
         <v>140000000000</v>
       </c>
     </row>
-    <row r="101" ht="15" customHeight="1" s="15">
-      <c r="A101" s="34" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>Giao dịch mua bán lại trái phiếu Chính phủ</t>
         </is>
       </c>
-      <c r="B101" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C101" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" ht="15" customHeight="1" s="15">
-      <c r="A102" s="34" t="inlineStr">
+      <c r="B101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>Trả trước người bán dài hạn</t>
         </is>
       </c>
-      <c r="B102" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C102" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" ht="15" customHeight="1" s="15">
-      <c r="A103" s="34" t="inlineStr">
+      <c r="B102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>Phải thu cho vay dài hạn</t>
         </is>
       </c>
-      <c r="B103" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C103" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" ht="15" customHeight="1" s="15">
-      <c r="A104" s="34" t="inlineStr">
+      <c r="B103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>Tài sản dở dang dài hạn</t>
         </is>
       </c>
-      <c r="B104" s="35" t="n">
+      <c r="B104" s="4" t="n">
         <v>94707660034</v>
       </c>
-      <c r="C104" s="35" t="n">
+      <c r="C104" s="4" t="n">
         <v>64702641159</v>
       </c>
-      <c r="D104" s="35" t="n">
+      <c r="D104" s="4" t="n">
         <v>29100048410</v>
       </c>
-      <c r="E104" s="35" t="n">
+      <c r="E104" s="4" t="n">
         <v>30826629189</v>
       </c>
     </row>
-    <row r="105" ht="15" customHeight="1" s="15">
-      <c r="A105" s="34" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>Chi phí sản xuất, kinh doanh dở dang dài hạn</t>
         </is>
       </c>
-      <c r="B105" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C105" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" ht="15" customHeight="1" s="15">
-      <c r="A106" s="34" t="inlineStr">
+      <c r="B105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>Đầu tư nắm giữ đến ngày đáo hạn</t>
         </is>
       </c>
-      <c r="B106" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C106" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" ht="15" customHeight="1" s="15">
-      <c r="A107" s="34" t="inlineStr">
+      <c r="B106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>Thiết bị, vật tư, phụ tùng thay thế dài hạn</t>
         </is>
       </c>
-      <c r="B107" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C107" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" ht="15" customHeight="1" s="15">
-      <c r="A108" s="34" t="inlineStr">
+      <c r="B107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>Doanh thu chưa thực hiện ngắn hạn</t>
         </is>
       </c>
-      <c r="B108" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C108" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" ht="15" customHeight="1" s="15">
-      <c r="A109" s="34" t="inlineStr">
+      <c r="B108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>Quỹ bình ổn giá</t>
         </is>
       </c>
-      <c r="B109" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C109" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D109" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" ht="15" customHeight="1" s="15">
-      <c r="A110" s="34" t="inlineStr">
+      <c r="B109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>Giao dịch mua bán lại trái phiếu chính phủ</t>
         </is>
       </c>
-      <c r="B110" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C110" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" ht="15" customHeight="1" s="15">
-      <c r="A111" s="34" t="inlineStr">
+      <c r="B110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>Người mua trả tiền trước dài hạn</t>
         </is>
       </c>
-      <c r="B111" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C111" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" ht="15" customHeight="1" s="15">
-      <c r="A112" s="34" t="inlineStr">
+      <c r="B111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t>Chi phí phải trả dài hạn</t>
         </is>
       </c>
-      <c r="B112" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C112" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D112" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E112" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" ht="15" customHeight="1" s="15">
-      <c r="A113" s="34" t="inlineStr">
+      <c r="B112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>Phải trả nội bộ về vốn kinh doanh</t>
         </is>
       </c>
-      <c r="B113" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C113" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" ht="15" customHeight="1" s="15">
-      <c r="A114" s="34" t="inlineStr">
+      <c r="B113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t>Trái phiếu chuyển đổi</t>
         </is>
       </c>
-      <c r="B114" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C114" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" ht="15" customHeight="1" s="15">
-      <c r="A115" s="34" t="inlineStr">
+      <c r="B114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
         <is>
           <t>Cổ phiếu ưu đãi</t>
         </is>
       </c>
-      <c r="B115" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C115" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" ht="15" customHeight="1" s="15">
-      <c r="A116" s="34" t="inlineStr">
+      <c r="B115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>Cổ phiếu phổ thông</t>
         </is>
       </c>
-      <c r="B116" s="35" t="n">
+      <c r="B116" s="4" t="n">
         <v>3413186660000</v>
       </c>
-      <c r="C116" s="35" t="n">
+      <c r="C116" s="4" t="n">
         <v>3380747760000</v>
       </c>
-      <c r="D116" s="35" t="n">
+      <c r="D116" s="4" t="n">
         <v>3281691880000</v>
       </c>
-      <c r="E116" s="35" t="n">
+      <c r="E116" s="4" t="n">
         <v>2461716200000</v>
       </c>
     </row>
-    <row r="117" ht="15" customHeight="1" s="15">
-      <c r="A117" s="34" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t>Quyền chọn chuyển đổi trái phiếu</t>
         </is>
       </c>
-      <c r="B117" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C117" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E117" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" ht="15" customHeight="1" s="15">
-      <c r="A118" s="34" t="inlineStr">
+      <c r="B117" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>LNST chưa phân phối lũy kế đến cuối kỳ trước</t>
         </is>
       </c>
-      <c r="B118" s="35" t="n">
+      <c r="B118" s="4" t="n">
         <v>1582471057146</v>
       </c>
-      <c r="C118" s="35" t="n">
+      <c r="C118" s="4" t="n">
         <v>1188435208200</v>
       </c>
-      <c r="D118" s="35" t="n">
+      <c r="D118" s="4" t="n">
         <v>769000107465</v>
       </c>
-      <c r="E118" s="35" t="n">
+      <c r="E118" s="4" t="n">
         <v>859175348677</v>
       </c>
     </row>
-    <row r="119" ht="15" customHeight="1" s="15">
-      <c r="A119" s="34" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t>LNST chưa phân phối kỳ này</t>
         </is>
       </c>
-      <c r="B119" s="35" t="n">
+      <c r="B119" s="4" t="n">
         <v>2828497462890</v>
       </c>
-      <c r="C119" s="35" t="n">
+      <c r="C119" s="4" t="n">
         <v>2112916282946</v>
       </c>
-      <c r="D119" s="35" t="n">
+      <c r="D119" s="4" t="n">
         <v>1971099177135</v>
       </c>
-      <c r="E119" s="35" t="n">
+      <c r="E119" s="4" t="n">
         <v>1663090606797</v>
       </c>
     </row>
-    <row r="120" ht="15" customHeight="1" s="15">
-      <c r="A120" s="34" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
         <is>
           <t>Xây dựng cơ bản đang dở dang</t>
         </is>
       </c>
-      <c r="B120" s="35" t="n">
+      <c r="B120" s="4" t="n">
         <v>94707660034</v>
       </c>
-      <c r="C120" s="35" t="n">
+      <c r="C120" s="4" t="n">
         <v>64702641159</v>
       </c>
-      <c r="D120" s="35" t="n">
+      <c r="D120" s="4" t="n">
         <v>29100048410</v>
       </c>
-      <c r="E120" s="35" t="n">
+      <c r="E120" s="4" t="n">
         <v>30826629189</v>
       </c>
     </row>
-    <row r="121" ht="15" customHeight="1" s="15">
-      <c r="A121" s="34" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>Lợi thế thương mại</t>
         </is>
       </c>
-      <c r="B121" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C121" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" ht="15" customHeight="1" s="15">
-      <c r="A122" s="34" t="inlineStr">
+      <c r="B121" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t>Lợi ích cổ đông không kiểm soát</t>
         </is>
       </c>
-      <c r="B122" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C122" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" ht="15" customHeight="1" s="15">
-      <c r="A123" s="34" t="inlineStr">
+      <c r="B122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
         <is>
           <t>Nguồn kinh phí đã hình thành TSCĐ</t>
         </is>
       </c>
-      <c r="B123" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C123" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" s="35" t="n">
+      <c r="B123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E26"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" style="15" min="1" max="1"/>
-    <col width="15" customWidth="1" style="15" min="2" max="2"/>
-    <col width="15" customWidth="1" style="15" min="3" max="3"/>
-    <col width="15" customWidth="1" style="15" min="4" max="4"/>
-    <col width="15" customWidth="1" style="15" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="15">
-      <c r="A1" s="32" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" s="33" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" s="33" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" s="33" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" s="33" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="15">
-      <c r="A2" s="34" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Doanh thu bán hàng và cung cấp dịch vụ</t>
         </is>
       </c>
-      <c r="B2" s="35" t="n">
+      <c r="B2" s="4" t="n">
         <v>35410589612616</v>
       </c>
-      <c r="C2" s="35" t="n">
+      <c r="C2" s="4" t="n">
         <v>38232401184050</v>
       </c>
-      <c r="D2" s="35" t="n">
+      <c r="D2" s="4" t="n">
         <v>33481608954953</v>
       </c>
-      <c r="E2" s="35" t="n">
+      <c r="E2" s="4" t="n">
         <v>34211128942240</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="15">
-      <c r="A3" s="34" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Các khoản giảm trừ doanh thu</t>
         </is>
       </c>
-      <c r="B3" s="35" t="n">
+      <c r="B3" s="4" t="n">
         <v>-434546683224</v>
       </c>
-      <c r="C3" s="35" t="n">
+      <c r="C3" s="4" t="n">
         <v>-409564012665</v>
       </c>
-      <c r="D3" s="35" t="n">
+      <c r="D3" s="4" t="n">
         <v>-344679758524</v>
       </c>
-      <c r="E3" s="35" t="n">
+      <c r="E3" s="4" t="n">
         <v>-334674383087</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="15">
-      <c r="A4" s="34" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Doanh thu thuần</t>
         </is>
       </c>
-      <c r="B4" s="35" t="n">
+      <c r="B4" s="4" t="n">
         <v>34976042929392</v>
       </c>
-      <c r="C4" s="35" t="n">
+      <c r="C4" s="4" t="n">
         <v>37822837171385</v>
       </c>
-      <c r="D4" s="35" t="n">
+      <c r="D4" s="4" t="n">
         <v>33136929196429</v>
       </c>
-      <c r="E4" s="35" t="n">
+      <c r="E4" s="4" t="n">
         <v>33876454559153</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="15">
-      <c r="A5" s="34" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Giá vốn hàng bán</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="4" t="n">
         <v>-27292194621378</v>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="4" t="n">
         <v>-31149334531193</v>
       </c>
-      <c r="D5" s="35" t="n">
+      <c r="D5" s="4" t="n">
         <v>-27078338249235</v>
       </c>
-      <c r="E5" s="35" t="n">
+      <c r="E5" s="4" t="n">
         <v>-27949348024381</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="15">
-      <c r="A6" s="34" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="4" t="n">
         <v>7683848308014</v>
       </c>
-      <c r="C6" s="35" t="n">
+      <c r="C6" s="4" t="n">
         <v>6673502640192</v>
       </c>
-      <c r="D6" s="35" t="n">
+      <c r="D6" s="4" t="n">
         <v>6058590947194</v>
       </c>
-      <c r="E6" s="35" t="n">
+      <c r="E6" s="4" t="n">
         <v>5927106534772</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="15">
-      <c r="A7" s="34" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Doanh thu hoạt động tài chính</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="4" t="n">
         <v>136303226388</v>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="4" t="n">
         <v>75567438524</v>
       </c>
-      <c r="D7" s="35" t="n">
+      <c r="D7" s="4" t="n">
         <v>97825547538</v>
       </c>
-      <c r="E7" s="35" t="n">
+      <c r="E7" s="4" t="n">
         <v>54036974170</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="15">
-      <c r="A8" s="34" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Chi phí tài chính</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="4" t="n">
         <v>-153168770819</v>
       </c>
-      <c r="C8" s="35" t="n">
+      <c r="C8" s="4" t="n">
         <v>-93616780951</v>
       </c>
-      <c r="D8" s="35" t="n">
+      <c r="D8" s="4" t="n">
         <v>-142580680640</v>
       </c>
-      <c r="E8" s="35" t="n">
+      <c r="E8" s="4" t="n">
         <v>-141471203463</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="15">
-      <c r="A9" s="34" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="4" t="n">
         <v>-119082599327</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="4" t="n">
         <v>-46775305829</v>
       </c>
-      <c r="D9" s="35" t="n">
+      <c r="D9" s="4" t="n">
         <v>-118568804103</v>
       </c>
-      <c r="E9" s="35" t="n">
+      <c r="E9" s="4" t="n">
         <v>-94143431408</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="15">
-      <c r="A10" s="34" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Chi phí bán hàng</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="4" t="n">
         <v>-3322701974507</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="4" t="n">
         <v>-3207574691174</v>
       </c>
-      <c r="D10" s="35" t="n">
+      <c r="D10" s="4" t="n">
         <v>-2835769469802</v>
       </c>
-      <c r="E10" s="35" t="n">
+      <c r="E10" s="4" t="n">
         <v>-2828208644376</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="15">
-      <c r="A11" s="34" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Chi phí quản lý doanh nghiệp</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="4" t="n">
         <v>-824395851865</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="4" t="n">
         <v>-795749355922</v>
       </c>
-      <c r="D11" s="35" t="n">
+      <c r="D11" s="4" t="n">
         <v>-693934934718</v>
       </c>
-      <c r="E11" s="35" t="n">
+      <c r="E11" s="4" t="n">
         <v>-673996996684</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="15">
-      <c r="A12" s="34" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n">
+      <c r="B12" s="4" t="n">
         <v>3519884937211</v>
       </c>
-      <c r="C12" s="35" t="n">
+      <c r="C12" s="4" t="n">
         <v>2652129250669</v>
       </c>
-      <c r="D12" s="35" t="n">
+      <c r="D12" s="4" t="n">
         <v>2484131409572</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="4" t="n">
         <v>2337466664419</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="15">
-      <c r="A13" s="34" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Thu nhập khác</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
+      <c r="B13" s="4" t="n">
         <v>41188910080</v>
       </c>
-      <c r="C13" s="35" t="n">
+      <c r="C13" s="4" t="n">
         <v>10013781125</v>
       </c>
-      <c r="D13" s="35" t="n">
+      <c r="D13" s="4" t="n">
         <v>11846230257</v>
       </c>
-      <c r="E13" s="35" t="n">
+      <c r="E13" s="4" t="n">
         <v>8582642521</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="15">
-      <c r="A14" s="34" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Chi phí khác</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
+      <c r="B14" s="4" t="n">
         <v>-13234356500</v>
       </c>
-      <c r="C14" s="35" t="n">
+      <c r="C14" s="4" t="n">
         <v>-11130582486</v>
       </c>
-      <c r="D14" s="35" t="n">
+      <c r="D14" s="4" t="n">
         <v>-7217637455</v>
       </c>
-      <c r="E14" s="35" t="n">
+      <c r="E14" s="4" t="n">
         <v>-33721752227</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="15">
-      <c r="A15" s="34" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Thu nhập khác, ròng</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
+      <c r="B15" s="4" t="n">
         <v>27954553580</v>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="4" t="n">
         <v>-1116801361</v>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="4" t="n">
         <v>4628592802</v>
       </c>
-      <c r="E15" s="35" t="n">
+      <c r="E15" s="4" t="n">
         <v>-25139109706</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="15">
-      <c r="A16" s="34" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) từ công ty liên doanh</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="15">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="B16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) trước thuế</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
+      <c r="B17" s="4" t="n">
         <v>3547839490791</v>
       </c>
-      <c r="C17" s="35" t="n">
+      <c r="C17" s="4" t="n">
         <v>2651012449308</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="4" t="n">
         <v>2488760002374</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="4" t="n">
         <v>2312327554713</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="15">
-      <c r="A18" s="34" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Thuế thu nhập doanh nghiệp - hiện thời</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
+      <c r="B18" s="4" t="n">
         <v>-849656975908</v>
       </c>
-      <c r="C18" s="35" t="n">
+      <c r="C18" s="4" t="n">
         <v>-615476890636</v>
       </c>
-      <c r="D18" s="35" t="n">
+      <c r="D18" s="4" t="n">
         <v>-517592806160</v>
       </c>
-      <c r="E18" s="35" t="n">
+      <c r="E18" s="4" t="n">
         <v>-521061271124</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="15">
-      <c r="A19" s="34" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Thuế thu nhập doanh nghiệp - hoãn lại</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
+      <c r="B19" s="4" t="n">
         <v>130314948007</v>
       </c>
-      <c r="C19" s="35" t="n">
+      <c r="C19" s="4" t="n">
         <v>77380724274</v>
       </c>
-      <c r="D19" s="35" t="n">
+      <c r="D19" s="4" t="n">
         <v>-68019079</v>
       </c>
-      <c r="E19" s="35" t="n">
+      <c r="E19" s="4" t="n">
         <v>19425559808</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="15">
-      <c r="A20" s="34" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Chi phí thuế thu nhập doanh nghiệp</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
+      <c r="B20" s="4" t="n">
         <v>-719342027901</v>
       </c>
-      <c r="C20" s="35" t="n">
+      <c r="C20" s="4" t="n">
         <v>-538096166362</v>
       </c>
-      <c r="D20" s="35" t="n">
+      <c r="D20" s="4" t="n">
         <v>-517660825239</v>
       </c>
-      <c r="E20" s="35" t="n">
+      <c r="E20" s="4" t="n">
         <v>-501635711316</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="15">
-      <c r="A21" s="34" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) thuần sau thuế</t>
         </is>
       </c>
-      <c r="B21" s="35" t="n">
+      <c r="B21" s="4" t="n">
         <v>2828497462890</v>
       </c>
-      <c r="C21" s="35" t="n">
+      <c r="C21" s="4" t="n">
         <v>2112916282946</v>
       </c>
-      <c r="D21" s="35" t="n">
+      <c r="D21" s="4" t="n">
         <v>1971099177135</v>
       </c>
-      <c r="E21" s="35" t="n">
+      <c r="E21" s="4" t="n">
         <v>1810691843397</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="15">
-      <c r="A22" s="34" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Lợi ích của cổ đông thiểu số</t>
         </is>
       </c>
-      <c r="B22" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="15">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="B22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận của Cổ đông của Công ty mẹ</t>
         </is>
       </c>
-      <c r="B23" s="35" t="n">
+      <c r="B23" s="4" t="n">
         <v>2828497462890</v>
       </c>
-      <c r="C23" s="35" t="n">
+      <c r="C23" s="4" t="n">
         <v>2112916282946</v>
       </c>
-      <c r="D23" s="35" t="n">
+      <c r="D23" s="4" t="n">
         <v>1971099177135</v>
       </c>
-      <c r="E23" s="35" t="n">
+      <c r="E23" s="4" t="n">
         <v>1810691843397</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="15">
-      <c r="A24" s="34" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Lãi cơ bản trên cổ phiếu (VND)</t>
         </is>
       </c>
-      <c r="B24" s="35" t="n">
+      <c r="B24" s="4" t="n">
         <v>7652</v>
       </c>
-      <c r="C24" s="35" t="n">
+      <c r="C24" s="4" t="n">
         <v>5713</v>
       </c>
-      <c r="D24" s="35" t="n">
+      <c r="D24" s="4" t="n">
         <v>5436</v>
       </c>
-      <c r="E24" s="35" t="n">
+      <c r="E24" s="4" t="n">
         <v>5350</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="15">
-      <c r="A25" s="34" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Lãi trên cổ phiếu pha loãng (VND)</t>
         </is>
       </c>
-      <c r="B25" s="35" t="n">
+      <c r="B25" s="4" t="n">
         <v>7652</v>
       </c>
-      <c r="C25" s="35" t="n">
+      <c r="C25" s="4" t="n">
         <v>5713</v>
       </c>
-      <c r="D25" s="35" t="n">
+      <c r="D25" s="4" t="n">
         <v>5436</v>
       </c>
-      <c r="E25" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="15">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="E25" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) từ công ty liên doanh (từ năm 2015)</t>
         </is>
       </c>
-      <c r="B26" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="35" t="n">
+      <c r="B26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E42"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" style="15" min="1" max="1"/>
-    <col width="15" customWidth="1" style="15" min="2" max="2"/>
-    <col width="15" customWidth="1" style="15" min="3" max="3"/>
-    <col width="15" customWidth="1" style="15" min="4" max="4"/>
-    <col width="15" customWidth="1" style="15" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="15">
-      <c r="A1" s="32" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" s="33" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" s="33" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" s="33" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" s="33" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="15">
-      <c r="A2" s="34" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận/(lỗ) trước thuế</t>
         </is>
       </c>
-      <c r="B2" s="35" t="n">
+      <c r="B2" s="4" t="n">
         <v>3547839490791</v>
       </c>
-      <c r="C2" s="35" t="n">
+      <c r="C2" s="4" t="n">
         <v>2651012449308</v>
       </c>
-      <c r="D2" s="35" t="n">
+      <c r="D2" s="4" t="n">
         <v>2488760002374</v>
       </c>
-      <c r="E2" s="35" t="n">
+      <c r="E2" s="4" t="n">
         <v>2312327554713</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="15">
-      <c r="A3" s="34" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Khấu hao TSCĐ và BĐSĐT</t>
         </is>
       </c>
-      <c r="B3" s="35" t="n">
+      <c r="B3" s="4" t="n">
         <v>85291458403</v>
       </c>
-      <c r="C3" s="35" t="n">
+      <c r="C3" s="4" t="n">
         <v>80821846271</v>
       </c>
-      <c r="D3" s="35" t="n">
+      <c r="D3" s="4" t="n">
         <v>81257091304</v>
       </c>
-      <c r="E3" s="35" t="n">
+      <c r="E3" s="4" t="n">
         <v>79516376971</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="15">
-      <c r="A4" s="34" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Chi phí dự phòng</t>
         </is>
       </c>
-      <c r="B4" s="35" t="n">
+      <c r="B4" s="4" t="n">
         <v>-7695240894</v>
       </c>
-      <c r="C4" s="35" t="n">
+      <c r="C4" s="4" t="n">
         <v>77722354056</v>
       </c>
-      <c r="D4" s="35" t="n">
+      <c r="D4" s="4" t="n">
         <v>2374779451</v>
       </c>
-      <c r="E4" s="35" t="n">
+      <c r="E4" s="4" t="n">
         <v>2868205863</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="15">
-      <c r="A5" s="34" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Lãi/lỗ chênh lệch tỷ giá hối đoái do đánh giá lại các khoản mục tiền tệ có gốc ngoại tệ</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="4" t="n">
         <v>-2434348570</v>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="4" t="n">
         <v>140360327</v>
       </c>
-      <c r="D5" s="35" t="n">
+      <c r="D5" s="4" t="n">
         <v>-1611805757</v>
       </c>
-      <c r="E5" s="35" t="n">
+      <c r="E5" s="4" t="n">
         <v>-8239903282</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="15">
-      <c r="A6" s="34" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) từ thanh lý tài sản cố định</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="15">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="B6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>(Lãi)/lỗ từ hoạt động đầu tư</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="4" t="n">
         <v>-110244947701</v>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="4" t="n">
         <v>-47046699012</v>
       </c>
-      <c r="D7" s="35" t="n">
+      <c r="D7" s="4" t="n">
         <v>-79561268312</v>
       </c>
-      <c r="E7" s="35" t="n">
+      <c r="E7" s="4" t="n">
         <v>-21327686776</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="15">
-      <c r="A8" s="34" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="4" t="n">
         <v>119082599327</v>
       </c>
-      <c r="C8" s="35" t="n">
+      <c r="C8" s="4" t="n">
         <v>46775305829</v>
       </c>
-      <c r="D8" s="35" t="n">
+      <c r="D8" s="4" t="n">
         <v>118568804103</v>
       </c>
-      <c r="E8" s="35" t="n">
+      <c r="E8" s="4" t="n">
         <v>94421152974</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="15">
-      <c r="A9" s="34" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Thu lãi và cổ tức</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="15">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="B9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận/(lỗ) từ hoạt động kinh doanh trước những thay đổi vốn lưu động</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="4" t="n">
         <v>3631839011356</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="4" t="n">
         <v>2809425616779</v>
       </c>
-      <c r="D10" s="35" t="n">
+      <c r="D10" s="4" t="n">
         <v>2609787603163</v>
       </c>
-      <c r="E10" s="35" t="n">
+      <c r="E10" s="4" t="n">
         <v>2459565700463</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="15">
-      <c r="A11" s="34" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>(Tăng)/giảm các khoản phải thu</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="4" t="n">
         <v>235691148778</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="4" t="n">
         <v>-261742771385</v>
       </c>
-      <c r="D11" s="35" t="n">
+      <c r="D11" s="4" t="n">
         <v>39100711762</v>
       </c>
-      <c r="E11" s="35" t="n">
+      <c r="E11" s="4" t="n">
         <v>-52151674870</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="15">
-      <c r="A12" s="34" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>(Tăng)/giảm hàng tồn kho</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n">
+      <c r="B12" s="4" t="n">
         <v>-2806722790389</v>
       </c>
-      <c r="C12" s="35" t="n">
+      <c r="C12" s="4" t="n">
         <v>-2129837921117</v>
       </c>
-      <c r="D12" s="35" t="n">
+      <c r="D12" s="4" t="n">
         <v>-436683979881</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="4" t="n">
         <v>-1753323314557</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="15">
-      <c r="A13" s="34" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Tăng/(giảm) các khoản phải trả</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
+      <c r="B13" s="4" t="n">
         <v>-369026498161</v>
       </c>
-      <c r="C13" s="35" t="n">
+      <c r="C13" s="4" t="n">
         <v>273559805376</v>
       </c>
-      <c r="D13" s="35" t="n">
+      <c r="D13" s="4" t="n">
         <v>92449328770</v>
       </c>
-      <c r="E13" s="35" t="n">
+      <c r="E13" s="4" t="n">
         <v>76506711125</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="15">
-      <c r="A14" s="34" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>(Tăng)/giảm chi phí trả trước</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
+      <c r="B14" s="4" t="n">
         <v>169889358691</v>
       </c>
-      <c r="C14" s="35" t="n">
+      <c r="C14" s="4" t="n">
         <v>13981231920</v>
       </c>
-      <c r="D14" s="35" t="n">
+      <c r="D14" s="4" t="n">
         <v>-103556391934</v>
       </c>
-      <c r="E14" s="35" t="n">
+      <c r="E14" s="4" t="n">
         <v>-59503878567</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="15">
-      <c r="A15" s="34" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Tiền lãi vay đã trả</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
+      <c r="B15" s="4" t="n">
         <v>-117889071318</v>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="4" t="n">
         <v>-46067825009</v>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="4" t="n">
         <v>-122841644646</v>
       </c>
-      <c r="E15" s="35" t="n">
+      <c r="E15" s="4" t="n">
         <v>-90657750651</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="15">
-      <c r="A16" s="34" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Thuế thu nhập doanh nghiệp đã nộp</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
+      <c r="B16" s="4" t="n">
         <v>-607285010641</v>
       </c>
-      <c r="C16" s="35" t="n">
+      <c r="C16" s="4" t="n">
         <v>-555484436785</v>
       </c>
-      <c r="D16" s="35" t="n">
+      <c r="D16" s="4" t="n">
         <v>-466349274224</v>
       </c>
-      <c r="E16" s="35" t="n">
+      <c r="E16" s="4" t="n">
         <v>-464338080937</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="15">
-      <c r="A17" s="34" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Tiền thu khác từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="15">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="B17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Tiền chi khác cho hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
+      <c r="B18" s="4" t="n">
         <v>-19687607067</v>
       </c>
-      <c r="C18" s="35" t="n">
+      <c r="C18" s="4" t="n">
         <v>-20648525024</v>
       </c>
-      <c r="D18" s="35" t="n">
+      <c r="D18" s="4" t="n">
         <v>-104164881917</v>
       </c>
-      <c r="E18" s="35" t="n">
+      <c r="E18" s="4" t="n">
         <v>-15516505310</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="15">
-      <c r="A19" s="34" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
+      <c r="B19" s="4" t="n">
         <v>18890403841</v>
       </c>
-      <c r="C19" s="35" t="n">
+      <c r="C19" s="4" t="n">
         <v>83185174755</v>
       </c>
-      <c r="D19" s="35" t="n">
+      <c r="D19" s="4" t="n">
         <v>1507741471093</v>
       </c>
-      <c r="E19" s="35" t="n">
+      <c r="E19" s="4" t="n">
         <v>100581206696</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="15">
-      <c r="A20" s="34" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
+      <c r="B20" s="4" t="n">
         <v>-115542827250</v>
       </c>
-      <c r="C20" s="35" t="n">
+      <c r="C20" s="4" t="n">
         <v>-90406299690</v>
       </c>
-      <c r="D20" s="35" t="n">
+      <c r="D20" s="4" t="n">
         <v>-83115434103</v>
       </c>
-      <c r="E20" s="35" t="n">
+      <c r="E20" s="4" t="n">
         <v>-52384601566</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="15">
-      <c r="A21" s="34" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Tiền thu từ thanh lý, nhượng bán TSCĐ và các tài sản dài hạn khác</t>
         </is>
       </c>
-      <c r="B21" s="35" t="n">
+      <c r="B21" s="4" t="n">
         <v>3636364</v>
       </c>
-      <c r="C21" s="35" t="n">
+      <c r="C21" s="4" t="n">
         <v>3181818</v>
       </c>
-      <c r="D21" s="35" t="n">
+      <c r="D21" s="4" t="n">
         <v>2289295529</v>
       </c>
-      <c r="E21" s="35" t="n">
+      <c r="E21" s="4" t="n">
         <v>1498185785</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="15">
-      <c r="A22" s="34" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Tiền chi cho vay, mua các công cụ nợ của đơn vị khác</t>
         </is>
       </c>
-      <c r="B22" s="35" t="n">
+      <c r="B22" s="4" t="n">
         <v>-4067400000000</v>
       </c>
-      <c r="C22" s="35" t="n">
+      <c r="C22" s="4" t="n">
         <v>-1120070000000</v>
       </c>
-      <c r="D22" s="35" t="n">
+      <c r="D22" s="4" t="n">
         <v>-2240100000000</v>
       </c>
-      <c r="E22" s="35" t="n">
+      <c r="E22" s="4" t="n">
         <v>-540000000000</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="15">
-      <c r="A23" s="34" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Tiền thu hồi cho vay, bán lại các công cụ nợ của đơn vị khác</t>
         </is>
       </c>
-      <c r="B23" s="35" t="n">
+      <c r="B23" s="4" t="n">
         <v>3210000000000</v>
       </c>
-      <c r="C23" s="35" t="n">
+      <c r="C23" s="4" t="n">
         <v>960000000000</v>
       </c>
-      <c r="D23" s="35" t="n">
+      <c r="D23" s="4" t="n">
         <v>1680000000000</v>
       </c>
-      <c r="E23" s="35" t="n">
+      <c r="E23" s="4" t="n">
         <v>200000000000</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="15">
-      <c r="A24" s="34" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Tiền chi đầu tư góp vốn vào đơn vị khác</t>
         </is>
       </c>
-      <c r="B24" s="35" t="n">
+      <c r="B24" s="4" t="n">
         <v>-1950000000</v>
       </c>
-      <c r="C24" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="35" t="n">
+      <c r="C24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4" t="n">
         <v>-3980000000</v>
       </c>
-      <c r="E24" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="15">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="E24" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Tiền thu hồi đầu tư góp vốn vào đơn vị khác</t>
         </is>
       </c>
-      <c r="B25" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="15">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="B25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Tiền thu lãi cho vay, cổ tức và lợi nhuận được chia</t>
         </is>
       </c>
-      <c r="B26" s="35" t="n">
+      <c r="B26" s="4" t="n">
         <v>81101160826</v>
       </c>
-      <c r="C26" s="35" t="n">
+      <c r="C26" s="4" t="n">
         <v>39436141188</v>
       </c>
-      <c r="D26" s="35" t="n">
+      <c r="D26" s="4" t="n">
         <v>66432820820</v>
       </c>
-      <c r="E26" s="35" t="n">
+      <c r="E26" s="4" t="n">
         <v>20219137155</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="15">
-      <c r="A27" s="34" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền thuần từ hoạt động đầu tư</t>
         </is>
       </c>
-      <c r="B27" s="35" t="n">
+      <c r="B27" s="4" t="n">
         <v>-893788030060</v>
       </c>
-      <c r="C27" s="35" t="n">
+      <c r="C27" s="4" t="n">
         <v>-211036976684</v>
       </c>
-      <c r="D27" s="35" t="n">
+      <c r="D27" s="4" t="n">
         <v>-578473317754</v>
       </c>
-      <c r="E27" s="35" t="n">
+      <c r="E27" s="4" t="n">
         <v>-370667278626</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="15">
-      <c r="A28" s="34" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Tiền thu từ phát hành cổ phiếu, nhận vốn góp của chủ sở hữu</t>
         </is>
       </c>
-      <c r="B28" s="35" t="n">
+      <c r="B28" s="4" t="n">
         <v>64823800000</v>
       </c>
-      <c r="C28" s="35" t="n">
+      <c r="C28" s="4" t="n">
         <v>67243920000</v>
       </c>
-      <c r="D28" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="35" t="n">
+      <c r="D28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4" t="n">
         <v>1447231530000</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="15">
-      <c r="A29" s="34" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Tiền chi trả vốn góp cho các chủ sở hữu, mua lại cổ phiếu của doanh nghiệp đã phát hành</t>
         </is>
       </c>
-      <c r="B29" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="15">
-      <c r="A30" s="34" t="inlineStr">
+      <c r="B29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Tiền thu được các khoản đi vay</t>
         </is>
       </c>
-      <c r="B30" s="35" t="n">
+      <c r="B30" s="4" t="n">
         <v>9817871495359</v>
       </c>
-      <c r="C30" s="35" t="n">
+      <c r="C30" s="4" t="n">
         <v>6788859495016</v>
       </c>
-      <c r="D30" s="35" t="n">
+      <c r="D30" s="4" t="n">
         <v>8159472964689</v>
       </c>
-      <c r="E30" s="35" t="n">
+      <c r="E30" s="4" t="n">
         <v>6261254967206</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="15">
-      <c r="A31" s="34" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Tiền trả nợ gốc vay</t>
         </is>
       </c>
-      <c r="B31" s="35" t="n">
+      <c r="B31" s="4" t="n">
         <v>-8936027876466</v>
       </c>
-      <c r="C31" s="35" t="n">
+      <c r="C31" s="4" t="n">
         <v>-5831605732949</v>
       </c>
-      <c r="D31" s="35" t="n">
+      <c r="D31" s="4" t="n">
         <v>-8458230585768</v>
       </c>
-      <c r="E31" s="35" t="n">
+      <c r="E31" s="4" t="n">
         <v>-6300139792578</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="15">
-      <c r="A32" s="34" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Tiền trả nợ gốc thuê tài chính</t>
         </is>
       </c>
-      <c r="B32" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="15">
-      <c r="A33" s="34" t="inlineStr">
+      <c r="B32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Cổ tức, lợi nhuận đã trả cho chủ sở hữu</t>
         </is>
       </c>
-      <c r="B33" s="35" t="n">
+      <c r="B33" s="4" t="n">
         <v>-673692457830</v>
       </c>
-      <c r="C33" s="35" t="n">
+      <c r="C33" s="4" t="n">
         <v>-671681829760</v>
       </c>
-      <c r="D33" s="35" t="n">
+      <c r="D33" s="4" t="n">
         <v>-615443389700</v>
       </c>
-      <c r="E33" s="35" t="n">
+      <c r="E33" s="4" t="n">
         <v>-616671158340</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="15">
-      <c r="A34" s="34" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Tiền lãi đã nhận</t>
         </is>
       </c>
-      <c r="B34" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="15">
-      <c r="A35" s="34" t="inlineStr">
+      <c r="B34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền thuần từ hoạt động tài chính</t>
         </is>
       </c>
-      <c r="B35" s="35" t="n">
+      <c r="B35" s="4" t="n">
         <v>272974961063</v>
       </c>
-      <c r="C35" s="35" t="n">
+      <c r="C35" s="4" t="n">
         <v>352815852307</v>
       </c>
-      <c r="D35" s="35" t="n">
+      <c r="D35" s="4" t="n">
         <v>-914201010779</v>
       </c>
-      <c r="E35" s="35" t="n">
+      <c r="E35" s="4" t="n">
         <v>791675546288</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="15">
-      <c r="A36" s="34" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền thuần trong kỳ</t>
         </is>
       </c>
-      <c r="B36" s="35" t="n">
+      <c r="B36" s="4" t="n">
         <v>-601922665156</v>
       </c>
-      <c r="C36" s="35" t="n">
+      <c r="C36" s="4" t="n">
         <v>224964050378</v>
       </c>
-      <c r="D36" s="35" t="n">
+      <c r="D36" s="4" t="n">
         <v>15067142560</v>
       </c>
-      <c r="E36" s="35" t="n">
+      <c r="E36" s="4" t="n">
         <v>521589474358</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="15">
-      <c r="A37" s="34" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Tiền và tương đương tiền đầu kỳ</t>
         </is>
       </c>
-      <c r="B37" s="35" t="n">
+      <c r="B37" s="4" t="n">
         <v>1122712392130</v>
       </c>
-      <c r="C37" s="35" t="n">
+      <c r="C37" s="4" t="n">
         <v>896147917336</v>
       </c>
-      <c r="D37" s="35" t="n">
+      <c r="D37" s="4" t="n">
         <v>879548130711</v>
       </c>
-      <c r="E37" s="35" t="n">
+      <c r="E37" s="4" t="n">
         <v>355454838957</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="15">
-      <c r="A38" s="34" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Ảnh hưởng của thay đổi tỷ giá hối đoái quy đổi ngoại tệ</t>
         </is>
       </c>
-      <c r="B38" s="35" t="n">
+      <c r="B38" s="4" t="n">
         <v>1235530057</v>
       </c>
-      <c r="C38" s="35" t="n">
+      <c r="C38" s="4" t="n">
         <v>1600424416</v>
       </c>
-      <c r="D38" s="35" t="n">
+      <c r="D38" s="4" t="n">
         <v>1532644065</v>
       </c>
-      <c r="E38" s="35" t="n">
+      <c r="E38" s="4" t="n">
         <v>2503817396</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="15">
-      <c r="A39" s="34" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Tiền và tương đương tiền cuối kỳ</t>
         </is>
       </c>
-      <c r="B39" s="35" t="n">
+      <c r="B39" s="4" t="n">
         <v>522025257031</v>
       </c>
-      <c r="C39" s="35" t="n">
+      <c r="C39" s="4" t="n">
         <v>1122712392130</v>
       </c>
-      <c r="D39" s="35" t="n">
+      <c r="D39" s="4" t="n">
         <v>896147917336</v>
       </c>
-      <c r="E39" s="35" t="n">
+      <c r="E39" s="4" t="n">
         <v>879548130711</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="15">
-      <c r="A40" s="34" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Phân bổ lợi thế thương mại</t>
         </is>
       </c>
-      <c r="B40" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="15">
-      <c r="A41" s="34" t="inlineStr">
+      <c r="B40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Các khoản điều chỉnh khác</t>
         </is>
       </c>
-      <c r="B41" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="15">
-      <c r="A42" s="34" t="inlineStr">
+      <c r="B41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>(Tăng)/giảm chứng khoán kinh doanh</t>
         </is>
       </c>
-      <c r="B42" s="35" t="n">
+      <c r="B42" s="4" t="n">
         <v>-97918137408</v>
       </c>
-      <c r="C42" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="35" t="n">
+      <c r="C42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -4321,1038 +4262,1045 @@
   <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" style="15" min="1" max="1"/>
-    <col width="14" customWidth="1" style="15" min="2" max="2"/>
-    <col width="14" customWidth="1" style="15" min="3" max="3"/>
-    <col width="14" customWidth="1" style="15" min="4" max="4"/>
-    <col width="14" customWidth="1" style="15" min="5" max="5"/>
-    <col width="3" customWidth="1" style="15" min="6" max="6"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" s="15">
-      <c r="A1" s="17" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>CHỈ SỐ TÀI CHÍNH — PNJ</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1" s="15">
-      <c r="A2" s="19" t="inlineStr">
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Khối "CHỈ SỐ TÀI CHÍNH" tính bằng công thức từ khối "DỮ LIỆU TRÍCH XUẤT" bên dưới, không phải số nhập tay. Khối "DỮ LIỆU TRÍCH XUẤT" được dò tự động theo TÊN khoản mục (đúng theo tên gốc trong báo cáo) và theo NĂM từ 3 sheet balance_sheet / income_statement — không tham chiếu ô cố định. Có thể sửa nhãn khoản mục ở cột A khối này nếu công ty đổi tên dòng; công thức sẽ tự dò lại. Các năm được xếp tăng dần từ trái sang phải.</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>I. CHỈ SỐ TÀI CHÍNH</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n"/>
-      <c r="C4" s="21" t="n"/>
-      <c r="D4" s="21" t="n"/>
-      <c r="E4" s="21" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Chỉ tiêu</t>
         </is>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="10">
         <f>'balance_sheet'!E1</f>
         <v/>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="10">
         <f>'balance_sheet'!D1</f>
         <v/>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="10">
         <f>'balance_sheet'!C1</f>
         <v/>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="10">
         <f>'balance_sheet'!B1</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>1. Khả năng sinh lời</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="14">
         <f>IFERROR(C$54/((C$39+B$39)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="14">
         <f>IFERROR(D$54/((D$39+C$39)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="14">
         <f>IFERROR(E$54/((E$39+D$39)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>ROA (LNST / Tổng tài sản bình quân)</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="14">
         <f>IFERROR(C$53/((C$40+B$40)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="14">
         <f>IFERROR(D$53/((D$40+C$40)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="14">
         <f>IFERROR(E$53/((E$40+D$40)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="14">
         <f>IFERROR((C$54-B$54)/ABS(B$54),"n/a")</f>
         <v/>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="14">
         <f>IFERROR((D$54-C$54)/ABS(C$54),"n/a")</f>
         <v/>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="14">
         <f>IFERROR((E$54-D$54)/ABS(D$54),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Tăng trưởng Doanh thu thuần</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="14">
         <f>IFERROR((C$46-B$46)/ABS(B$46),"n/a")</f>
         <v/>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="14">
         <f>IFERROR((D$46-C$46)/ABS(C$46),"n/a")</f>
         <v/>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="14">
         <f>IFERROR((E$46-D$46)/ABS(D$46),"n/a")</f>
         <v/>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>2. Biên lợi nhuận</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Biên lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="14">
         <f>IFERROR(B$48/B$46,"n/a")</f>
         <v/>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="14">
         <f>IFERROR(C$48/C$46,"n/a")</f>
         <v/>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="14">
         <f>IFERROR(D$48/D$46,"n/a")</f>
         <v/>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="14">
         <f>IFERROR(E$48/E$46,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Biên lợi nhuận ròng</t>
         </is>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="14">
         <f>IFERROR(B$53/B$46,"n/a")</f>
         <v/>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="14">
         <f>IFERROR(C$53/C$46,"n/a")</f>
         <v/>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="14">
         <f>IFERROR(D$53/D$46,"n/a")</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="14">
         <f>IFERROR(E$53/E$46,"n/a")</f>
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>3. Đòn bẩy tài chính</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
         </is>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="15">
         <f>IFERROR((B$44+B$45)/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="15">
         <f>IFERROR((C$44+C$45)/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="15">
         <f>IFERROR((D$44+D$45)/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="15">
         <f>IFERROR((E$44+E$45)/E$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="15">
         <f>IFERROR(B$45/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="15">
         <f>IFERROR(C$45/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="15">
         <f>IFERROR(D$45/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="15">
         <f>IFERROR(E$45/E$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="15">
         <f>IFERROR(B$44/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="15">
         <f>IFERROR(C$44/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="15">
         <f>IFERROR(D$44/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="15">
         <f>IFERROR(E$44/E$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Nợ phải trả/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="15">
         <f>IFERROR(B$41/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="15">
         <f>IFERROR(C$41/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="15">
         <f>IFERROR(D$41/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="15">
         <f>IFERROR(E$41/E$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="15">
         <f>IFERROR(B$43/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="15">
         <f>IFERROR(C$43/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="15">
         <f>IFERROR(D$43/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="15">
         <f>IFERROR(E$43/E$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="15">
         <f>IFERROR(B$42/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="15">
         <f>IFERROR(C$42/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="15">
         <f>IFERROR(D$42/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="15">
         <f>IFERROR(E$42/E$39,"n/a")</f>
         <v/>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>4. Chi phí &amp; khả năng trả lãi</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Chi phí bán hàng, quản lý/LN gộp</t>
         </is>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="14">
         <f>IFERROR((ABS(B$49)+ABS(B$50))/B$48,"n/a")</f>
         <v/>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="14">
         <f>IFERROR((ABS(C$49)+ABS(C$50))/C$48,"n/a")</f>
         <v/>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="14">
         <f>IFERROR((ABS(D$49)+ABS(D$50))/D$48,"n/a")</f>
         <v/>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="14">
         <f>IFERROR((ABS(E$49)+ABS(E$50))/E$48,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="14">
         <f>IFERROR(ABS(B$52)/B$51,"n/a")</f>
         <v/>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="14">
         <f>IFERROR(ABS(C$52)/C$51,"n/a")</f>
         <v/>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="14">
         <f>IFERROR(ABS(D$52)/D$51,"n/a")</f>
         <v/>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="14">
         <f>IFERROR(ABS(E$52)/E$51,"n/a")</f>
         <v/>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>5. Chu kỳ hoạt động vốn lưu động</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Số ngày phải trả (DPO)</t>
         </is>
       </c>
-      <c r="B29" s="26" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="16">
         <f>IFERROR(((C$56+B$56)/2)/ABS(C$47)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="16">
         <f>IFERROR(((D$56+C$56)/2)/ABS(D$47)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="16">
         <f>IFERROR(((E$56+D$56)/2)/ABS(E$47)*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>Số ngày phải thu (DSO)</t>
         </is>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C30" s="30">
+      <c r="C30" s="16">
         <f>IFERROR(((C$55+B$55)/2)/C$46*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D30" s="30">
+      <c r="D30" s="16">
         <f>IFERROR(((D$55+C$55)/2)/D$46*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E30" s="30">
+      <c r="E30" s="16">
         <f>IFERROR(((E$55+D$55)/2)/E$46*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Số ngày tồn kho (DIO)</t>
         </is>
       </c>
-      <c r="B31" s="26" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="16">
         <f>IFERROR(((C$57+B$57)/2)/ABS(C$47)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="16">
         <f>IFERROR(((D$57+C$57)/2)/ABS(D$47)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E31" s="30">
+      <c r="E31" s="16">
         <f>IFERROR(((E$57+D$57)/2)/ABS(E$47)*365,"n/a")</f>
         <v/>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
-      <c r="A33" s="24" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>6. Cơ cấu tài sản</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>Tiền và tương đương tiền/Tài sản</t>
         </is>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="14">
         <f>IFERROR(B$58/B$40,"n/a")</f>
         <v/>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="14">
         <f>IFERROR(C$58/C$40,"n/a")</f>
         <v/>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="14">
         <f>IFERROR(D$58/D$40,"n/a")</f>
         <v/>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="14">
         <f>IFERROR(E$58/E$40,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="25" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>Hàng tồn kho/Tài sản</t>
         </is>
       </c>
-      <c r="B35" s="27">
+      <c r="B35" s="14">
         <f>IFERROR(B$57/B$40,"n/a")</f>
         <v/>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="14">
         <f>IFERROR(C$57/C$40,"n/a")</f>
         <v/>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="14">
         <f>IFERROR(D$57/D$40,"n/a")</f>
         <v/>
       </c>
-      <c r="E35" s="27">
+      <c r="E35" s="14">
         <f>IFERROR(E$57/E$40,"n/a")</f>
         <v/>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
         </is>
       </c>
-      <c r="B37" s="21" t="n"/>
-      <c r="C37" s="21" t="n"/>
-      <c r="D37" s="21" t="n"/>
-      <c r="E37" s="21" t="n"/>
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Khoản mục</t>
         </is>
       </c>
-      <c r="B38" s="23">
+      <c r="B38" s="10">
         <f>'balance_sheet'!E1</f>
         <v/>
       </c>
-      <c r="C38" s="23">
+      <c r="C38" s="10">
         <f>'balance_sheet'!D1</f>
         <v/>
       </c>
-      <c r="D38" s="23">
+      <c r="D38" s="10">
         <f>'balance_sheet'!C1</f>
         <v/>
       </c>
-      <c r="E38" s="23">
+      <c r="E38" s="10">
         <f>'balance_sheet'!B1</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="29" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B39" s="31">
+      <c r="B39" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D39" s="31">
+      <c r="D39" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E39" s="31">
+      <c r="E39" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="29" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>TỔNG CỘNG TÀI SẢN</t>
         </is>
       </c>
-      <c r="B40" s="31">
+      <c r="B40" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C40" s="31">
+      <c r="C40" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D40" s="31">
+      <c r="D40" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E40" s="31">
+      <c r="E40" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>NỢ PHẢI TRẢ</t>
         </is>
       </c>
-      <c r="B41" s="31">
+      <c r="B41" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="29" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B42" s="31">
+      <c r="B42" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Nợ dài hạn</t>
         </is>
       </c>
-      <c r="B43" s="31">
+      <c r="B43" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D43" s="31">
+      <c r="D43" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E43" s="31">
+      <c r="E43" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Vay ngắn hạn</t>
         </is>
       </c>
-      <c r="B44" s="31">
+      <c r="B44" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Vay dài hạn</t>
         </is>
       </c>
-      <c r="B45" s="31">
+      <c r="B45" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D45" s="31">
+      <c r="D45" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Doanh thu thuần</t>
         </is>
       </c>
-      <c r="B46" s="31">
+      <c r="B46" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C46" s="31">
+      <c r="C46" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D46" s="31">
+      <c r="D46" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E46" s="31">
+      <c r="E46" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>Giá vốn hàng bán</t>
         </is>
       </c>
-      <c r="B47" s="31">
+      <c r="B47" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D47" s="31">
+      <c r="D47" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E47" s="31">
+      <c r="E47" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B48" s="31">
+      <c r="B48" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D48" s="31">
+      <c r="D48" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E48" s="31">
+      <c r="E48" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Chi phí bán hàng</t>
         </is>
       </c>
-      <c r="B49" s="31">
+      <c r="B49" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C49" s="31">
+      <c r="C49" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D49" s="31">
+      <c r="D49" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E49" s="31">
+      <c r="E49" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="29" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Chi phí quản lý doanh nghiệp</t>
         </is>
       </c>
-      <c r="B50" s="31">
+      <c r="B50" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D50" s="31">
+      <c r="D50" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E50" s="31">
+      <c r="E50" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B51" s="31">
+      <c r="B51" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D51" s="31">
+      <c r="D51" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E51" s="31">
+      <c r="E51" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B52" s="31">
+      <c r="B52" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C52" s="31">
+      <c r="C52" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D52" s="31">
+      <c r="D52" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E52" s="31">
+      <c r="E52" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) thuần sau thuế</t>
         </is>
       </c>
-      <c r="B53" s="31">
+      <c r="B53" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D53" s="31">
+      <c r="D53" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E53" s="31">
+      <c r="E53" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="29" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận của Cổ đông của Công ty mẹ</t>
         </is>
       </c>
-      <c r="B54" s="31">
+      <c r="B54" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C54" s="31">
+      <c r="C54" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D54" s="31">
+      <c r="D54" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E54" s="31">
+      <c r="E54" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Phải thu khách hàng</t>
         </is>
       </c>
-      <c r="B55" s="31">
+      <c r="B55" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C55" s="31">
+      <c r="C55" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D55" s="31">
+      <c r="D55" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E55" s="31">
+      <c r="E55" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="29" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Phải trả người bán</t>
         </is>
       </c>
-      <c r="B56" s="31">
+      <c r="B56" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D56" s="31">
+      <c r="D56" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E56" s="31">
+      <c r="E56" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="29" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Hàng tồn kho, ròng</t>
         </is>
       </c>
-      <c r="B57" s="31">
+      <c r="B57" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D57" s="31">
+      <c r="D57" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E57" s="31">
+      <c r="E57" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="29" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Tiền và tương đương tiền</t>
         </is>
       </c>
-      <c r="B58" s="31">
+      <c r="B58" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C58" s="31">
+      <c r="C58" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D58" s="31">
+      <c r="D58" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E58" s="31">
+      <c r="E58" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
@@ -5362,78 +5310,6 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B7:E7">
-    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8:E8">
-    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9:E9">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10:E10">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13:E13">
-    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14:E14">
-    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B17:E17">
-    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="1">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="0">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B20:E20">
-    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="1">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="0">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26:E26">
-    <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="1">
-      <formula>0.5</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="0">
-      <formula>0.15</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/financials/PNJ/PNJ_financials.xlsx
+++ b/financials/PNJ/PNJ_financials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,11 +546,11 @@
   <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -561,22 +561,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>11966357761798</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>12958118192260</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>15692597267632</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>18614031193890</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>15692597267632</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>12958118192260</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>11966357761798</v>
       </c>
     </row>
     <row r="3">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>879548130711</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>896147917336</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>1122712392130</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>522025257031</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1122712392130</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>896147917336</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>879548130711</v>
       </c>
     </row>
     <row r="4">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>879548130711</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>896147917336</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>1022712392130</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>438425257031</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1022712392130</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>896147917336</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>879548130711</v>
       </c>
     </row>
     <row r="5">
@@ -644,16 +644,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>100000000000</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>83600000000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>100000000000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -663,16 +663,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>97918137408</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -682,16 +682,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>97918137408</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>300880402245</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>215035937840</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>401134922152</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>153980309545</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>401134922152</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>215035937840</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>300880402245</v>
       </c>
     </row>
     <row r="10">
@@ -739,16 +739,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>56532707659</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>69277567110</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>70851635761</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>48760415990</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>70851635761</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>69277567110</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>56532707659</v>
       </c>
     </row>
     <row r="11">
@@ -758,16 +758,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>68902837213</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>27775617785</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>253102611434</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>38085152243</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>253102611434</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>27775617785</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>68902837213</v>
       </c>
     </row>
     <row r="12">
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>37641170145</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>32980198226</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>64867442121</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>90681158676</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>64867442121</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>32980198226</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>37641170145</v>
       </c>
     </row>
     <row r="15">
@@ -834,16 +834,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-2862909308</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-5049680837</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-28518444279</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>-31918617346</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-28518444279</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-5049680837</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-2862909308</v>
       </c>
     </row>
     <row r="16">
@@ -853,16 +853,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>10506054932284</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>10940937959289</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>13015170477311</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>15835334529837</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>13015170477311</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>10940937959289</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>10506054932284</v>
       </c>
     </row>
     <row r="17">
@@ -872,16 +872,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>10508065026916</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>10944749006797</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>13074586927914</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>15881309718303</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>13074586927914</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>10944749006797</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>10508065026916</v>
       </c>
     </row>
     <row r="18">
@@ -891,16 +891,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>-2010094632</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-3811047508</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-59416450603</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>-45975188466</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-59416450603</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-3811047508</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-2010094632</v>
       </c>
     </row>
     <row r="19">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>74007356286</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>94051248427</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>132726608716</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>94862372660</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>132726608716</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>94051248427</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>74007356286</v>
       </c>
     </row>
     <row r="21">
@@ -948,16 +948,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>5866940272</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1845129368</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>682867323</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>234579085</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>682867323</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>1845129368</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>5866940272</v>
       </c>
     </row>
     <row r="22">
@@ -967,16 +967,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>106008324</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1005,16 +1005,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>1370766887448</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>1469439823096</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>1515133510053</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>1549599053151</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>1515133510053</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>1469439823096</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>1370766887448</v>
       </c>
     </row>
     <row r="25">
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>93956493011</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>104636239106</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>115599492454</v>
+      </c>
+      <c r="E25" s="4" t="n">
         <v>121168536356</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>115599492454</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>104636239106</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>93956493011</v>
       </c>
     </row>
     <row r="26">
@@ -1081,16 +1081,16 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
+        <v>93956493011</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>104636239106</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>115599492454</v>
+      </c>
+      <c r="E28" s="4" t="n">
         <v>121168536356</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>115599492454</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>104636239106</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>93956493011</v>
       </c>
     </row>
     <row r="29">
@@ -1119,16 +1119,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>882432821075</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>882715109732</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>857118818527</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>855770473476</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>857118818527</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>882715109732</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>882432821075</v>
       </c>
     </row>
     <row r="31">
@@ -1138,16 +1138,16 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>239734551747</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>256373758673</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>248430247930</v>
+      </c>
+      <c r="E31" s="4" t="n">
         <v>236245161003</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>248430247930</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>256373758673</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>239734551747</v>
       </c>
     </row>
     <row r="32">
@@ -1157,16 +1157,16 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
+        <v>672781337441</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>747570855214</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>796271142120</v>
+      </c>
+      <c r="E32" s="4" t="n">
         <v>845032678156</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>796271142120</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>747570855214</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>672781337441</v>
       </c>
     </row>
     <row r="33">
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>-433046785694</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>-491197096541</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>-547840894190</v>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>-608787517153</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>-547840894190</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>-491197096541</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>-433046785694</v>
       </c>
     </row>
     <row r="34">
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>642698269328</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>626341351059</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>608688570597</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>619525312473</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>608688570597</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>626341351059</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>642698269328</v>
       </c>
     </row>
     <row r="38">
@@ -1271,16 +1271,16 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
+        <v>707010800099</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>708071904553</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>708142194553</v>
+      </c>
+      <c r="E38" s="4" t="n">
         <v>734945157553</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>708142194553</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>708071904553</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>707010800099</v>
       </c>
     </row>
     <row r="39">
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>-64312530771</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>-81730553494</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>-99453623956</v>
+      </c>
+      <c r="E39" s="4" t="n">
         <v>-115419845080</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>-99453623956</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>-81730553494</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>-64312530771</v>
       </c>
     </row>
     <row r="40">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>5930000000</v>
+        <v>0</v>
       </c>
       <c r="C44" s="4" t="n">
         <v>3980000000</v>
@@ -1394,7 +1394,7 @@
         <v>3980000000</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0</v>
+        <v>5930000000</v>
       </c>
     </row>
     <row r="45">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>401201613400</v>
+        <v>395271613400</v>
       </c>
       <c r="C47" s="4" t="n">
         <v>399251613400</v>
@@ -1451,7 +1451,7 @@
         <v>399251613400</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>395271613400</v>
+        <v>401201613400</v>
       </c>
     </row>
     <row r="48">
@@ -1499,16 +1499,16 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
+        <v>363550944173</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>449008425848</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>473732557913</v>
+      </c>
+      <c r="E50" s="4" t="n">
         <v>472022383285</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>473732557913</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>449008425848</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>363550944173</v>
       </c>
     </row>
     <row r="51">
@@ -1518,16 +1518,16 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
+        <v>243656590750</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>329182091504</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>276525499295</v>
+      </c>
+      <c r="E51" s="4" t="n">
         <v>144500376660</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>276525499295</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>329182091504</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>243656590750</v>
       </c>
     </row>
     <row r="52">
@@ -1575,16 +1575,16 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
+        <v>13337124649246</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>14427558015356</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>17207730777685</v>
+      </c>
+      <c r="E54" s="4" t="n">
         <v>20163630247041</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>17207730777685</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>14427558015356</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>13337124649246</v>
       </c>
     </row>
     <row r="55">
@@ -1594,16 +1594,16 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
+        <v>4893029994396</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>4621377351380</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>5952424147163</v>
+      </c>
+      <c r="E55" s="4" t="n">
         <v>6888716787629</v>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>5952424147163</v>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>4621377351380</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>4893029994396</v>
       </c>
     </row>
     <row r="56">
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
+        <v>4883064421396</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>4611956609380</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>5941881733413</v>
+      </c>
+      <c r="E56" s="4" t="n">
         <v>6874318773629</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>5941881733413</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>4611956609380</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>4883064421396</v>
       </c>
     </row>
     <row r="57">
@@ -1632,16 +1632,16 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
+        <v>2683045875772</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>2384288254693</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>3341542016760</v>
+      </c>
+      <c r="E57" s="4" t="n">
         <v>4223385635653</v>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>3341542016760</v>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>2384288254693</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>2683045875772</v>
       </c>
     </row>
     <row r="58">
@@ -1651,16 +1651,16 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
+        <v>277212839495</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>257304950807</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>624291098148</v>
+      </c>
+      <c r="E58" s="4" t="n">
         <v>333861329514</v>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>624291098148</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>257304950807</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>277212839495</v>
       </c>
     </row>
     <row r="59">
@@ -1670,16 +1670,16 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
+        <v>222164283405</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>215299493413</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>188182044409</v>
+      </c>
+      <c r="E59" s="4" t="n">
         <v>182492529057</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>188182044409</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>215299493413</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>222164283405</v>
       </c>
     </row>
     <row r="60">
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
+        <v>292985361927</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>344258054659</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>448697283312</v>
+      </c>
+      <c r="E60" s="4" t="n">
         <v>777717691575</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>448697283312</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>344258054659</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>292985361927</v>
       </c>
     </row>
     <row r="61">
@@ -1708,16 +1708,16 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
+        <v>534807250396</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>673116492808</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>596322426230</v>
+      </c>
+      <c r="E61" s="4" t="n">
         <v>569308694234</v>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>596322426230</v>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>673116492808</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>534807250396</v>
       </c>
     </row>
     <row r="62">
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="B62" s="4" t="n">
+        <v>453432735944</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>307718428978</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>360040211420</v>
+      </c>
+      <c r="E62" s="4" t="n">
         <v>321827090456</v>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>360040211420</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>307718428978</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>453432735944</v>
       </c>
     </row>
     <row r="63">
@@ -1784,16 +1784,16 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
+        <v>227169093119</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>228798913738</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>106241642105</v>
+      </c>
+      <c r="E65" s="4" t="n">
         <v>103175435252</v>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>106241642105</v>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>228798913738</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>227169093119</v>
       </c>
     </row>
     <row r="66">
@@ -1803,16 +1803,16 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
+        <v>30129306488</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>29061192534</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>26547708303</v>
+      </c>
+      <c r="E66" s="4" t="n">
         <v>26574672229</v>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>26547708303</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>29061192534</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>30129306488</v>
       </c>
     </row>
     <row r="67">
@@ -1822,16 +1822,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
+        <v>162117674850</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>172110827750</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>250017302726</v>
+      </c>
+      <c r="E67" s="4" t="n">
         <v>335975695659</v>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>250017302726</v>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>172110827750</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>162117674850</v>
       </c>
     </row>
     <row r="68">
@@ -1841,16 +1841,16 @@
         </is>
       </c>
       <c r="B68" s="4" t="n">
+        <v>9965573000</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>9420742000</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>10542413750</v>
+      </c>
+      <c r="E68" s="4" t="n">
         <v>14398014000</v>
-      </c>
-      <c r="C68" s="4" t="n">
-        <v>10542413750</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>9420742000</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>9965573000</v>
       </c>
     </row>
     <row r="69">
@@ -1898,16 +1898,16 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
+        <v>218668000</v>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>218668000</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>178668000</v>
+      </c>
+      <c r="E71" s="4" t="n">
         <v>1715384000</v>
-      </c>
-      <c r="C71" s="4" t="n">
-        <v>178668000</v>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>218668000</v>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>218668000</v>
       </c>
     </row>
     <row r="72">
@@ -1974,16 +1974,16 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
+        <v>9746905000</v>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>9202074000</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>10363745750</v>
+      </c>
+      <c r="E75" s="4" t="n">
         <v>12682630000</v>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>10363745750</v>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>9202074000</v>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>9746905000</v>
       </c>
     </row>
     <row r="76">
@@ -2031,16 +2031,16 @@
         </is>
       </c>
       <c r="B78" s="4" t="n">
+        <v>8444094654850</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>9806180663976</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>11255306630522</v>
+      </c>
+      <c r="E78" s="4" t="n">
         <v>13274913459412</v>
-      </c>
-      <c r="C78" s="4" t="n">
-        <v>11255306630522</v>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>9806180663976</v>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>8444094654850</v>
       </c>
     </row>
     <row r="79">
@@ -2050,16 +2050,16 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
+        <v>8444094654850</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>9806180663976</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>11255306630522</v>
+      </c>
+      <c r="E79" s="4" t="n">
         <v>13274913459412</v>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>11255306630522</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>9806180663976</v>
-      </c>
-      <c r="E79" s="4" t="n">
-        <v>8444094654850</v>
       </c>
     </row>
     <row r="80">
@@ -2069,16 +2069,16 @@
         </is>
       </c>
       <c r="B80" s="4" t="n">
+        <v>2461716200000</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>3281691880000</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>3380747760000</v>
+      </c>
+      <c r="E80" s="4" t="n">
         <v>3413186660000</v>
-      </c>
-      <c r="C80" s="4" t="n">
-        <v>3380747760000</v>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>3281691880000</v>
-      </c>
-      <c r="E80" s="4" t="n">
-        <v>2461716200000</v>
       </c>
     </row>
     <row r="81">
@@ -2088,16 +2088,16 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
+        <v>2251376032458</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>1851376032458</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>1950309912458</v>
+      </c>
+      <c r="E81" s="4" t="n">
         <v>1982694812458</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>1950309912458</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>1851376032458</v>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>2251376032458</v>
       </c>
     </row>
     <row r="82">
@@ -2183,16 +2183,16 @@
         </is>
       </c>
       <c r="B86" s="4" t="n">
+        <v>1212120556918</v>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>1936397556918</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>2626281556918</v>
+      </c>
+      <c r="E86" s="4" t="n">
         <v>3471447556918</v>
-      </c>
-      <c r="C86" s="4" t="n">
-        <v>2626281556918</v>
-      </c>
-      <c r="D86" s="4" t="n">
-        <v>1936397556918</v>
-      </c>
-      <c r="E86" s="4" t="n">
-        <v>1212120556918</v>
       </c>
     </row>
     <row r="87">
@@ -2240,16 +2240,16 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
+        <v>2522265955474</v>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>2740099284600</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>3301351491146</v>
+      </c>
+      <c r="E89" s="4" t="n">
         <v>4410968520036</v>
-      </c>
-      <c r="C89" s="4" t="n">
-        <v>3301351491146</v>
-      </c>
-      <c r="D89" s="4" t="n">
-        <v>2740099284600</v>
-      </c>
-      <c r="E89" s="4" t="n">
-        <v>2522265955474</v>
       </c>
     </row>
     <row r="90">
@@ -2354,16 +2354,16 @@
         </is>
       </c>
       <c r="B95" s="4" t="n">
+        <v>13337124649246</v>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>14427558015356</v>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>17207730777685</v>
+      </c>
+      <c r="E95" s="4" t="n">
         <v>20163630247041</v>
-      </c>
-      <c r="C95" s="4" t="n">
-        <v>17207730777685</v>
-      </c>
-      <c r="D95" s="4" t="n">
-        <v>14427558015356</v>
-      </c>
-      <c r="E95" s="4" t="n">
-        <v>13337124649246</v>
       </c>
     </row>
     <row r="96">
@@ -2430,16 +2430,16 @@
         </is>
       </c>
       <c r="B99" s="4" t="n">
+        <v>666596536</v>
+      </c>
+      <c r="C99" s="4" t="n">
+        <v>52235556</v>
+      </c>
+      <c r="D99" s="4" t="n">
+        <v>831677115</v>
+      </c>
+      <c r="E99" s="4" t="n">
         <v>372199982</v>
-      </c>
-      <c r="C99" s="4" t="n">
-        <v>831677115</v>
-      </c>
-      <c r="D99" s="4" t="n">
-        <v>52235556</v>
-      </c>
-      <c r="E99" s="4" t="n">
-        <v>666596536</v>
       </c>
     </row>
     <row r="100">
@@ -2449,16 +2449,16 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
+        <v>140000000000</v>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>90000000000</v>
+      </c>
+      <c r="D100" s="4" t="n">
+        <v>40000000000</v>
+      </c>
+      <c r="E100" s="4" t="n">
         <v>8000000000</v>
-      </c>
-      <c r="C100" s="4" t="n">
-        <v>40000000000</v>
-      </c>
-      <c r="D100" s="4" t="n">
-        <v>90000000000</v>
-      </c>
-      <c r="E100" s="4" t="n">
-        <v>140000000000</v>
       </c>
     </row>
     <row r="101">
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
+        <v>30826629189</v>
+      </c>
+      <c r="C104" s="4" t="n">
+        <v>29100048410</v>
+      </c>
+      <c r="D104" s="4" t="n">
+        <v>64702641159</v>
+      </c>
+      <c r="E104" s="4" t="n">
         <v>94707660034</v>
-      </c>
-      <c r="C104" s="4" t="n">
-        <v>64702641159</v>
-      </c>
-      <c r="D104" s="4" t="n">
-        <v>29100048410</v>
-      </c>
-      <c r="E104" s="4" t="n">
-        <v>30826629189</v>
       </c>
     </row>
     <row r="105">
@@ -2753,16 +2753,16 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
+        <v>2461716200000</v>
+      </c>
+      <c r="C116" s="4" t="n">
+        <v>3281691880000</v>
+      </c>
+      <c r="D116" s="4" t="n">
+        <v>3380747760000</v>
+      </c>
+      <c r="E116" s="4" t="n">
         <v>3413186660000</v>
-      </c>
-      <c r="C116" s="4" t="n">
-        <v>3380747760000</v>
-      </c>
-      <c r="D116" s="4" t="n">
-        <v>3281691880000</v>
-      </c>
-      <c r="E116" s="4" t="n">
-        <v>2461716200000</v>
       </c>
     </row>
     <row r="117">
@@ -2791,16 +2791,16 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
+        <v>859175348677</v>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>769000107465</v>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>1188435208200</v>
+      </c>
+      <c r="E118" s="4" t="n">
         <v>1582471057146</v>
-      </c>
-      <c r="C118" s="4" t="n">
-        <v>1188435208200</v>
-      </c>
-      <c r="D118" s="4" t="n">
-        <v>769000107465</v>
-      </c>
-      <c r="E118" s="4" t="n">
-        <v>859175348677</v>
       </c>
     </row>
     <row r="119">
@@ -2810,16 +2810,16 @@
         </is>
       </c>
       <c r="B119" s="4" t="n">
+        <v>1663090606797</v>
+      </c>
+      <c r="C119" s="4" t="n">
+        <v>1971099177135</v>
+      </c>
+      <c r="D119" s="4" t="n">
+        <v>2112916282946</v>
+      </c>
+      <c r="E119" s="4" t="n">
         <v>2828497462890</v>
-      </c>
-      <c r="C119" s="4" t="n">
-        <v>2112916282946</v>
-      </c>
-      <c r="D119" s="4" t="n">
-        <v>1971099177135</v>
-      </c>
-      <c r="E119" s="4" t="n">
-        <v>1663090606797</v>
       </c>
     </row>
     <row r="120">
@@ -2829,16 +2829,16 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
+        <v>30826629189</v>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>29100048410</v>
+      </c>
+      <c r="D120" s="4" t="n">
+        <v>64702641159</v>
+      </c>
+      <c r="E120" s="4" t="n">
         <v>94707660034</v>
-      </c>
-      <c r="C120" s="4" t="n">
-        <v>64702641159</v>
-      </c>
-      <c r="D120" s="4" t="n">
-        <v>29100048410</v>
-      </c>
-      <c r="E120" s="4" t="n">
-        <v>30826629189</v>
       </c>
     </row>
     <row r="121">
@@ -2912,11 +2912,11 @@
   <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2927,22 +2927,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -2953,16 +2953,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>34211128942240</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>33481608954953</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>38232401184050</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>35410589612616</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>38232401184050</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>33481608954953</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>34211128942240</v>
       </c>
     </row>
     <row r="3">
@@ -2972,16 +2972,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>-334674383087</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>-344679758524</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>-409564012665</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>-434546683224</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>-409564012665</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>-344679758524</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>-334674383087</v>
       </c>
     </row>
     <row r="4">
@@ -2991,16 +2991,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>33876454559153</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>33136929196429</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>37822837171385</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>34976042929392</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>37822837171385</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>33136929196429</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>33876454559153</v>
       </c>
     </row>
     <row r="5">
@@ -3010,16 +3010,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-27949348024381</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-27078338249235</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-31149334531193</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>-27292194621378</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-31149334531193</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-27078338249235</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-27949348024381</v>
       </c>
     </row>
     <row r="6">
@@ -3029,16 +3029,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>5927106534772</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>6058590947194</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>6673502640192</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>7683848308014</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>6673502640192</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>6058590947194</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>5927106534772</v>
       </c>
     </row>
     <row r="7">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>54036974170</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>97825547538</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>75567438524</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>136303226388</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>75567438524</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>97825547538</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>54036974170</v>
       </c>
     </row>
     <row r="8">
@@ -3067,16 +3067,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>-141471203463</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>-142580680640</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>-93616780951</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>-153168770819</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>-93616780951</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>-142580680640</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>-141471203463</v>
       </c>
     </row>
     <row r="9">
@@ -3086,16 +3086,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>-94143431408</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>-118568804103</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>-46775305829</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>-119082599327</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>-46775305829</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>-118568804103</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>-94143431408</v>
       </c>
     </row>
     <row r="10">
@@ -3105,16 +3105,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>-2828208644376</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>-2835769469802</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>-3207574691174</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>-3322701974507</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>-3207574691174</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>-2835769469802</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>-2828208644376</v>
       </c>
     </row>
     <row r="11">
@@ -3124,16 +3124,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>-673996996684</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>-693934934718</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>-795749355922</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>-824395851865</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>-795749355922</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>-693934934718</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>-673996996684</v>
       </c>
     </row>
     <row r="12">
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>2337466664419</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>2484131409572</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>2652129250669</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>3519884937211</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>2652129250669</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>2484131409572</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>2337466664419</v>
       </c>
     </row>
     <row r="13">
@@ -3162,16 +3162,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>8582642521</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>11846230257</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>10013781125</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>41188910080</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>10013781125</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>11846230257</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>8582642521</v>
       </c>
     </row>
     <row r="14">
@@ -3181,16 +3181,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>-33721752227</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-7217637455</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>-11130582486</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>-13234356500</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>-11130582486</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>-7217637455</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>-33721752227</v>
       </c>
     </row>
     <row r="15">
@@ -3200,16 +3200,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-25139109706</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>4628592802</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-1116801361</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>27954553580</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-1116801361</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>4628592802</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-25139109706</v>
       </c>
     </row>
     <row r="16">
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>2312327554713</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>2488760002374</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>2651012449308</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>3547839490791</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>2651012449308</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>2488760002374</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>2312327554713</v>
       </c>
     </row>
     <row r="18">
@@ -3257,16 +3257,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>-521061271124</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-517592806160</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-615476890636</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>-849656975908</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-615476890636</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-517592806160</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-521061271124</v>
       </c>
     </row>
     <row r="19">
@@ -3276,16 +3276,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>19425559808</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>-68019079</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>77380724274</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>130314948007</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>77380724274</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>-68019079</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>19425559808</v>
       </c>
     </row>
     <row r="20">
@@ -3295,16 +3295,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>-501635711316</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-517660825239</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-538096166362</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>-719342027901</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-538096166362</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-517660825239</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-501635711316</v>
       </c>
     </row>
     <row r="21">
@@ -3314,16 +3314,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>1810691843397</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1971099177135</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>2112916282946</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>2828497462890</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>2112916282946</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>1971099177135</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>1810691843397</v>
       </c>
     </row>
     <row r="22">
@@ -3352,16 +3352,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>1810691843397</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>1971099177135</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>2112916282946</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>2828497462890</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>2112916282946</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>1971099177135</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>1810691843397</v>
       </c>
     </row>
     <row r="24">
@@ -3371,16 +3371,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>5350</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>5436</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>5713</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>7652</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>5713</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>5436</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>5350</v>
       </c>
     </row>
     <row r="25">
@@ -3390,16 +3390,16 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>5436</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>5713</v>
+      </c>
+      <c r="E25" s="4" t="n">
         <v>7652</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>5713</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>5436</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3435,11 +3435,11 @@
   <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="89" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3450,22 +3450,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>2312327554713</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>2488760002374</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>2651012449308</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>3547839490791</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>2651012449308</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>2488760002374</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>2312327554713</v>
       </c>
     </row>
     <row r="3">
@@ -3495,16 +3495,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>79516376971</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>81257091304</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>80821846271</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>85291458403</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>80821846271</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>81257091304</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>79516376971</v>
       </c>
     </row>
     <row r="4">
@@ -3514,16 +3514,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>2868205863</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>2374779451</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>77722354056</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>-7695240894</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>77722354056</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>2374779451</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>2868205863</v>
       </c>
     </row>
     <row r="5">
@@ -3533,16 +3533,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-8239903282</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-1611805757</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>140360327</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>-2434348570</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>140360327</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-1611805757</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-8239903282</v>
       </c>
     </row>
     <row r="6">
@@ -3571,16 +3571,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>-21327686776</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>-79561268312</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-47046699012</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>-110244947701</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-47046699012</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-79561268312</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-21327686776</v>
       </c>
     </row>
     <row r="8">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>94421152974</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>118568804103</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>46775305829</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>119082599327</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>46775305829</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>118568804103</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>94421152974</v>
       </c>
     </row>
     <row r="9">
@@ -3628,16 +3628,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>2459565700463</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2609787603163</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>2809425616779</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>3631839011356</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>2809425616779</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>2609787603163</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>2459565700463</v>
       </c>
     </row>
     <row r="11">
@@ -3647,16 +3647,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>-52151674870</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>39100711762</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>-261742771385</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>235691148778</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>-261742771385</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>39100711762</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>-52151674870</v>
       </c>
     </row>
     <row r="12">
@@ -3666,16 +3666,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>-1753323314557</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-436683979881</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>-2129837921117</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>-2806722790389</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>-2129837921117</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-436683979881</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>-1753323314557</v>
       </c>
     </row>
     <row r="13">
@@ -3685,16 +3685,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>76506711125</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>92449328770</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>273559805376</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>-369026498161</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>273559805376</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>92449328770</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>76506711125</v>
       </c>
     </row>
     <row r="14">
@@ -3704,16 +3704,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>-59503878567</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-103556391934</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>13981231920</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>169889358691</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>13981231920</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>-103556391934</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>-59503878567</v>
       </c>
     </row>
     <row r="15">
@@ -3723,16 +3723,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-90657750651</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-122841644646</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-46067825009</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>-117889071318</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-46067825009</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-122841644646</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-90657750651</v>
       </c>
     </row>
     <row r="16">
@@ -3742,16 +3742,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>-464338080937</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>-466349274224</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>-555484436785</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>-607285010641</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>-555484436785</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>-466349274224</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>-464338080937</v>
       </c>
     </row>
     <row r="17">
@@ -3780,16 +3780,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>-15516505310</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-104164881917</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-20648525024</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>-19687607067</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-20648525024</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-104164881917</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-15516505310</v>
       </c>
     </row>
     <row r="19">
@@ -3799,16 +3799,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>100581206696</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>1507741471093</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>83185174755</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>18890403841</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>83185174755</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>1507741471093</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>100581206696</v>
       </c>
     </row>
     <row r="20">
@@ -3818,16 +3818,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>-52384601566</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-83115434103</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-90406299690</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>-115542827250</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-90406299690</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-83115434103</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-52384601566</v>
       </c>
     </row>
     <row r="21">
@@ -3837,16 +3837,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>1498185785</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>2289295529</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>3181818</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>3636364</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>3181818</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>2289295529</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>1498185785</v>
       </c>
     </row>
     <row r="22">
@@ -3856,16 +3856,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>-540000000000</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>-2240100000000</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>-1120070000000</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>-4067400000000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>-1120070000000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>-2240100000000</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>-540000000000</v>
       </c>
     </row>
     <row r="23">
@@ -3875,16 +3875,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>200000000000</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>1680000000000</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>960000000000</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>3210000000000</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>960000000000</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>1680000000000</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>200000000000</v>
       </c>
     </row>
     <row r="24">
@@ -3894,16 +3894,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>-3980000000</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>-1950000000</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>-3980000000</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3932,16 +3932,16 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
+        <v>20219137155</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>66432820820</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>39436141188</v>
+      </c>
+      <c r="E26" s="4" t="n">
         <v>81101160826</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>39436141188</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>66432820820</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>20219137155</v>
       </c>
     </row>
     <row r="27">
@@ -3951,16 +3951,16 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
+        <v>-370667278626</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>-578473317754</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>-211036976684</v>
+      </c>
+      <c r="E27" s="4" t="n">
         <v>-893788030060</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>-211036976684</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>-578473317754</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>-370667278626</v>
       </c>
     </row>
     <row r="28">
@@ -3970,16 +3970,16 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
+        <v>1447231530000</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>67243920000</v>
+      </c>
+      <c r="E28" s="4" t="n">
         <v>64823800000</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>67243920000</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>1447231530000</v>
       </c>
     </row>
     <row r="29">
@@ -4008,16 +4008,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>6261254967206</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>8159472964689</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>6788859495016</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>9817871495359</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>6788859495016</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>8159472964689</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>6261254967206</v>
       </c>
     </row>
     <row r="31">
@@ -4027,16 +4027,16 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>-6300139792578</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>-8458230585768</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>-5831605732949</v>
+      </c>
+      <c r="E31" s="4" t="n">
         <v>-8936027876466</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>-5831605732949</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>-8458230585768</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>-6300139792578</v>
       </c>
     </row>
     <row r="32">
@@ -4065,16 +4065,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>-616671158340</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>-615443389700</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>-671681829760</v>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>-673692457830</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>-671681829760</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>-615443389700</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>-616671158340</v>
       </c>
     </row>
     <row r="34">
@@ -4103,16 +4103,16 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
+        <v>791675546288</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>-914201010779</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>352815852307</v>
+      </c>
+      <c r="E35" s="4" t="n">
         <v>272974961063</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>352815852307</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>-914201010779</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>791675546288</v>
       </c>
     </row>
     <row r="36">
@@ -4122,16 +4122,16 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
+        <v>521589474358</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>15067142560</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>224964050378</v>
+      </c>
+      <c r="E36" s="4" t="n">
         <v>-601922665156</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>224964050378</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>15067142560</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>521589474358</v>
       </c>
     </row>
     <row r="37">
@@ -4141,16 +4141,16 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>355454838957</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>879548130711</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>896147917336</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>1122712392130</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>896147917336</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>879548130711</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>355454838957</v>
       </c>
     </row>
     <row r="38">
@@ -4160,16 +4160,16 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
+        <v>2503817396</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>1532644065</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>1600424416</v>
+      </c>
+      <c r="E38" s="4" t="n">
         <v>1235530057</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>1600424416</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>1532644065</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>2503817396</v>
       </c>
     </row>
     <row r="39">
@@ -4179,16 +4179,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>879548130711</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>896147917336</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>1122712392130</v>
+      </c>
+      <c r="E39" s="4" t="n">
         <v>522025257031</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>1122712392130</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>896147917336</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>879548130711</v>
       </c>
     </row>
     <row r="40">
@@ -4236,16 +4236,16 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="n">
         <v>-97918137408</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4262,11 +4262,11 @@
   <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4277,12 +4277,8 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Khối "CHỈ SỐ TÀI CHÍNH" tính bằng công thức từ khối "DỮ LIỆU TRÍCH XUẤT" bên dưới, không phải số nhập tay. Khối "DỮ LIỆU TRÍCH XUẤT" được dò tự động theo TÊN khoản mục (đúng theo tên gốc trong báo cáo) và theo NĂM từ 3 sheet balance_sheet / income_statement — không tham chiếu ô cố định. Có thể sửa nhãn khoản mục ở cột A khối này nếu công ty đổi tên dòng; công thức sẽ tự dò lại. Các năm được xếp tăng dần từ trái sang phải.</t>
-        </is>
-      </c>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="6" t="n"/>
     </row>
     <row r="3"/>
     <row r="4">
@@ -4303,19 +4299,19 @@
         </is>
       </c>
       <c r="B5" s="10">
+        <f>'balance_sheet'!B1</f>
+        <v/>
+      </c>
+      <c r="C5" s="10">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="D5" s="10">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="E5" s="10">
         <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="C5" s="10">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="D5" s="10">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="E5" s="10">
-        <f>'balance_sheet'!B1</f>
         <v/>
       </c>
     </row>
@@ -4829,19 +4825,19 @@
         </is>
       </c>
       <c r="B38" s="10">
+        <f>'balance_sheet'!B1</f>
+        <v/>
+      </c>
+      <c r="C38" s="10">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="D38" s="10">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="E38" s="10">
         <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="C38" s="10">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="D38" s="10">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="E38" s="10">
-        <f>'balance_sheet'!B1</f>
         <v/>
       </c>
     </row>

--- a/financials/PNJ/PNJ_financials.xlsx
+++ b/financials/PNJ/PNJ_financials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,11 +546,11 @@
   <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -561,22 +561,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2022</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
         </is>
       </c>
     </row>
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>18614031193890</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>15692597267632</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>12958118192260</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>11966357761798</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>12958118192260</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>15692597267632</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>18614031193890</v>
       </c>
     </row>
     <row r="3">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>522025257031</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1122712392130</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>896147917336</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>879548130711</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>896147917336</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>1122712392130</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>522025257031</v>
       </c>
     </row>
     <row r="4">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>438425257031</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1022712392130</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>896147917336</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>879548130711</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>896147917336</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>1022712392130</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>438425257031</v>
       </c>
     </row>
     <row r="5">
@@ -644,16 +644,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0</v>
+        <v>83600000000</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
+        <v>100000000000</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>100000000000</v>
+        <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>83600000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0</v>
+        <v>97918137408</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>97918137408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>97918137408</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0</v>
@@ -691,7 +691,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>97918137408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>153980309545</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>401134922152</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>215035937840</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>300880402245</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>215035937840</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>401134922152</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>153980309545</v>
       </c>
     </row>
     <row r="10">
@@ -739,16 +739,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>48760415990</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>70851635761</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>69277567110</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>56532707659</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>69277567110</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>70851635761</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>48760415990</v>
       </c>
     </row>
     <row r="11">
@@ -758,16 +758,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>38085152243</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>253102611434</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>27775617785</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>68902837213</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>27775617785</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>253102611434</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>38085152243</v>
       </c>
     </row>
     <row r="12">
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>90681158676</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>64867442121</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>32980198226</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>37641170145</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>32980198226</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>64867442121</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>90681158676</v>
       </c>
     </row>
     <row r="15">
@@ -834,16 +834,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-31918617346</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-28518444279</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-5049680837</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>-2862909308</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-5049680837</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-28518444279</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-31918617346</v>
       </c>
     </row>
     <row r="16">
@@ -853,16 +853,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>15835334529837</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>13015170477311</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>10940937959289</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>10506054932284</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>10940937959289</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>13015170477311</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>15835334529837</v>
       </c>
     </row>
     <row r="17">
@@ -872,16 +872,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>15881309718303</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>13074586927914</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>10944749006797</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>10508065026916</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>10944749006797</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>13074586927914</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>15881309718303</v>
       </c>
     </row>
     <row r="18">
@@ -891,16 +891,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>-45975188466</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-59416450603</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-3811047508</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>-2010094632</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-3811047508</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-59416450603</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-45975188466</v>
       </c>
     </row>
     <row r="19">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>94862372660</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>132726608716</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>94051248427</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>74007356286</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>94051248427</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>132726608716</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>94862372660</v>
       </c>
     </row>
     <row r="21">
@@ -948,16 +948,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>234579085</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>682867323</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>1845129368</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>5866940272</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>1845129368</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>682867323</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>234579085</v>
       </c>
     </row>
     <row r="22">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>0</v>
+        <v>106008324</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>106008324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1005,16 +1005,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>1549599053151</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>1515133510053</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>1469439823096</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>1370766887448</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>1469439823096</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>1515133510053</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>1549599053151</v>
       </c>
     </row>
     <row r="25">
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>121168536356</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>115599492454</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>104636239106</v>
+      </c>
+      <c r="E25" s="4" t="n">
         <v>93956493011</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>104636239106</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>115599492454</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>121168536356</v>
       </c>
     </row>
     <row r="26">
@@ -1081,16 +1081,16 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
+        <v>121168536356</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>115599492454</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>104636239106</v>
+      </c>
+      <c r="E28" s="4" t="n">
         <v>93956493011</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>104636239106</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>115599492454</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>121168536356</v>
       </c>
     </row>
     <row r="29">
@@ -1119,16 +1119,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>855770473476</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>857118818527</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>882715109732</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>882432821075</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>882715109732</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>857118818527</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>855770473476</v>
       </c>
     </row>
     <row r="31">
@@ -1138,16 +1138,16 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>236245161003</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>248430247930</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>256373758673</v>
+      </c>
+      <c r="E31" s="4" t="n">
         <v>239734551747</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>256373758673</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>248430247930</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>236245161003</v>
       </c>
     </row>
     <row r="32">
@@ -1157,16 +1157,16 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
+        <v>845032678156</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>796271142120</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>747570855214</v>
+      </c>
+      <c r="E32" s="4" t="n">
         <v>672781337441</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>747570855214</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>796271142120</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>845032678156</v>
       </c>
     </row>
     <row r="33">
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>-608787517153</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>-547840894190</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>-491197096541</v>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>-433046785694</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>-491197096541</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>-547840894190</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>-608787517153</v>
       </c>
     </row>
     <row r="34">
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>619525312473</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>608688570597</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>626341351059</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>642698269328</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>626341351059</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>608688570597</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>619525312473</v>
       </c>
     </row>
     <row r="38">
@@ -1271,16 +1271,16 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
+        <v>734945157553</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>708142194553</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>708071904553</v>
+      </c>
+      <c r="E38" s="4" t="n">
         <v>707010800099</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>708071904553</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>708142194553</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>734945157553</v>
       </c>
     </row>
     <row r="39">
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>-115419845080</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>-99453623956</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>-81730553494</v>
+      </c>
+      <c r="E39" s="4" t="n">
         <v>-64312530771</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>-81730553494</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>-99453623956</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>-115419845080</v>
       </c>
     </row>
     <row r="40">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>0</v>
+        <v>5930000000</v>
       </c>
       <c r="C44" s="4" t="n">
         <v>3980000000</v>
@@ -1394,7 +1394,7 @@
         <v>3980000000</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>5930000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>395271613400</v>
+        <v>401201613400</v>
       </c>
       <c r="C47" s="4" t="n">
         <v>399251613400</v>
@@ -1451,7 +1451,7 @@
         <v>399251613400</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>401201613400</v>
+        <v>395271613400</v>
       </c>
     </row>
     <row r="48">
@@ -1499,16 +1499,16 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
+        <v>472022383285</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>473732557913</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>449008425848</v>
+      </c>
+      <c r="E50" s="4" t="n">
         <v>363550944173</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>449008425848</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>473732557913</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>472022383285</v>
       </c>
     </row>
     <row r="51">
@@ -1518,16 +1518,16 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
+        <v>144500376660</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>276525499295</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>329182091504</v>
+      </c>
+      <c r="E51" s="4" t="n">
         <v>243656590750</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>329182091504</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>276525499295</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>144500376660</v>
       </c>
     </row>
     <row r="52">
@@ -1575,16 +1575,16 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
+        <v>20163630247041</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>17207730777685</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>14427558015356</v>
+      </c>
+      <c r="E54" s="4" t="n">
         <v>13337124649246</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>14427558015356</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>17207730777685</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>20163630247041</v>
       </c>
     </row>
     <row r="55">
@@ -1594,16 +1594,16 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
+        <v>6888716787629</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>5952424147163</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>4621377351380</v>
+      </c>
+      <c r="E55" s="4" t="n">
         <v>4893029994396</v>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>4621377351380</v>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>5952424147163</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>6888716787629</v>
       </c>
     </row>
     <row r="56">
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
+        <v>6874318773629</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>5941881733413</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>4611956609380</v>
+      </c>
+      <c r="E56" s="4" t="n">
         <v>4883064421396</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>4611956609380</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>5941881733413</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>6874318773629</v>
       </c>
     </row>
     <row r="57">
@@ -1632,16 +1632,16 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
+        <v>4223385635653</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>3341542016760</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>2384288254693</v>
+      </c>
+      <c r="E57" s="4" t="n">
         <v>2683045875772</v>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>2384288254693</v>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>3341542016760</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>4223385635653</v>
       </c>
     </row>
     <row r="58">
@@ -1651,16 +1651,16 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
+        <v>333861329514</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>624291098148</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>257304950807</v>
+      </c>
+      <c r="E58" s="4" t="n">
         <v>277212839495</v>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>257304950807</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>624291098148</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>333861329514</v>
       </c>
     </row>
     <row r="59">
@@ -1670,16 +1670,16 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
+        <v>182492529057</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>188182044409</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>215299493413</v>
+      </c>
+      <c r="E59" s="4" t="n">
         <v>222164283405</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>215299493413</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>188182044409</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>182492529057</v>
       </c>
     </row>
     <row r="60">
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
+        <v>777717691575</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>448697283312</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>344258054659</v>
+      </c>
+      <c r="E60" s="4" t="n">
         <v>292985361927</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>344258054659</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>448697283312</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>777717691575</v>
       </c>
     </row>
     <row r="61">
@@ -1708,16 +1708,16 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
+        <v>569308694234</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>596322426230</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>673116492808</v>
+      </c>
+      <c r="E61" s="4" t="n">
         <v>534807250396</v>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>673116492808</v>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>596322426230</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>569308694234</v>
       </c>
     </row>
     <row r="62">
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="B62" s="4" t="n">
+        <v>321827090456</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>360040211420</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>307718428978</v>
+      </c>
+      <c r="E62" s="4" t="n">
         <v>453432735944</v>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>307718428978</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>360040211420</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>321827090456</v>
       </c>
     </row>
     <row r="63">
@@ -1784,16 +1784,16 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
+        <v>103175435252</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>106241642105</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>228798913738</v>
+      </c>
+      <c r="E65" s="4" t="n">
         <v>227169093119</v>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>228798913738</v>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>106241642105</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>103175435252</v>
       </c>
     </row>
     <row r="66">
@@ -1803,16 +1803,16 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
+        <v>26574672229</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>26547708303</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>29061192534</v>
+      </c>
+      <c r="E66" s="4" t="n">
         <v>30129306488</v>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>29061192534</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>26547708303</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>26574672229</v>
       </c>
     </row>
     <row r="67">
@@ -1822,16 +1822,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
+        <v>335975695659</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>250017302726</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>172110827750</v>
+      </c>
+      <c r="E67" s="4" t="n">
         <v>162117674850</v>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>172110827750</v>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>250017302726</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>335975695659</v>
       </c>
     </row>
     <row r="68">
@@ -1841,16 +1841,16 @@
         </is>
       </c>
       <c r="B68" s="4" t="n">
+        <v>14398014000</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>10542413750</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>9420742000</v>
+      </c>
+      <c r="E68" s="4" t="n">
         <v>9965573000</v>
-      </c>
-      <c r="C68" s="4" t="n">
-        <v>9420742000</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>10542413750</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>14398014000</v>
       </c>
     </row>
     <row r="69">
@@ -1898,16 +1898,16 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
+        <v>1715384000</v>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>178668000</v>
+      </c>
+      <c r="D71" s="4" t="n">
         <v>218668000</v>
       </c>
-      <c r="C71" s="4" t="n">
+      <c r="E71" s="4" t="n">
         <v>218668000</v>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>178668000</v>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>1715384000</v>
       </c>
     </row>
     <row r="72">
@@ -1974,16 +1974,16 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
+        <v>12682630000</v>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>10363745750</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>9202074000</v>
+      </c>
+      <c r="E75" s="4" t="n">
         <v>9746905000</v>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>9202074000</v>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>10363745750</v>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>12682630000</v>
       </c>
     </row>
     <row r="76">
@@ -2031,16 +2031,16 @@
         </is>
       </c>
       <c r="B78" s="4" t="n">
+        <v>13274913459412</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>11255306630522</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>9806180663976</v>
+      </c>
+      <c r="E78" s="4" t="n">
         <v>8444094654850</v>
-      </c>
-      <c r="C78" s="4" t="n">
-        <v>9806180663976</v>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>11255306630522</v>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>13274913459412</v>
       </c>
     </row>
     <row r="79">
@@ -2050,16 +2050,16 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
+        <v>13274913459412</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>11255306630522</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>9806180663976</v>
+      </c>
+      <c r="E79" s="4" t="n">
         <v>8444094654850</v>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>9806180663976</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>11255306630522</v>
-      </c>
-      <c r="E79" s="4" t="n">
-        <v>13274913459412</v>
       </c>
     </row>
     <row r="80">
@@ -2069,16 +2069,16 @@
         </is>
       </c>
       <c r="B80" s="4" t="n">
+        <v>3413186660000</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>3380747760000</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>3281691880000</v>
+      </c>
+      <c r="E80" s="4" t="n">
         <v>2461716200000</v>
-      </c>
-      <c r="C80" s="4" t="n">
-        <v>3281691880000</v>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>3380747760000</v>
-      </c>
-      <c r="E80" s="4" t="n">
-        <v>3413186660000</v>
       </c>
     </row>
     <row r="81">
@@ -2088,16 +2088,16 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
+        <v>1982694812458</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>1950309912458</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>1851376032458</v>
+      </c>
+      <c r="E81" s="4" t="n">
         <v>2251376032458</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>1851376032458</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>1950309912458</v>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>1982694812458</v>
       </c>
     </row>
     <row r="82">
@@ -2183,16 +2183,16 @@
         </is>
       </c>
       <c r="B86" s="4" t="n">
+        <v>3471447556918</v>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>2626281556918</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>1936397556918</v>
+      </c>
+      <c r="E86" s="4" t="n">
         <v>1212120556918</v>
-      </c>
-      <c r="C86" s="4" t="n">
-        <v>1936397556918</v>
-      </c>
-      <c r="D86" s="4" t="n">
-        <v>2626281556918</v>
-      </c>
-      <c r="E86" s="4" t="n">
-        <v>3471447556918</v>
       </c>
     </row>
     <row r="87">
@@ -2240,16 +2240,16 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
+        <v>4410968520036</v>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>3301351491146</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>2740099284600</v>
+      </c>
+      <c r="E89" s="4" t="n">
         <v>2522265955474</v>
-      </c>
-      <c r="C89" s="4" t="n">
-        <v>2740099284600</v>
-      </c>
-      <c r="D89" s="4" t="n">
-        <v>3301351491146</v>
-      </c>
-      <c r="E89" s="4" t="n">
-        <v>4410968520036</v>
       </c>
     </row>
     <row r="90">
@@ -2354,16 +2354,16 @@
         </is>
       </c>
       <c r="B95" s="4" t="n">
+        <v>20163630247041</v>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>17207730777685</v>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>14427558015356</v>
+      </c>
+      <c r="E95" s="4" t="n">
         <v>13337124649246</v>
-      </c>
-      <c r="C95" s="4" t="n">
-        <v>14427558015356</v>
-      </c>
-      <c r="D95" s="4" t="n">
-        <v>17207730777685</v>
-      </c>
-      <c r="E95" s="4" t="n">
-        <v>20163630247041</v>
       </c>
     </row>
     <row r="96">
@@ -2430,16 +2430,16 @@
         </is>
       </c>
       <c r="B99" s="4" t="n">
+        <v>372199982</v>
+      </c>
+      <c r="C99" s="4" t="n">
+        <v>831677115</v>
+      </c>
+      <c r="D99" s="4" t="n">
+        <v>52235556</v>
+      </c>
+      <c r="E99" s="4" t="n">
         <v>666596536</v>
-      </c>
-      <c r="C99" s="4" t="n">
-        <v>52235556</v>
-      </c>
-      <c r="D99" s="4" t="n">
-        <v>831677115</v>
-      </c>
-      <c r="E99" s="4" t="n">
-        <v>372199982</v>
       </c>
     </row>
     <row r="100">
@@ -2449,16 +2449,16 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
+        <v>8000000000</v>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>40000000000</v>
+      </c>
+      <c r="D100" s="4" t="n">
+        <v>90000000000</v>
+      </c>
+      <c r="E100" s="4" t="n">
         <v>140000000000</v>
-      </c>
-      <c r="C100" s="4" t="n">
-        <v>90000000000</v>
-      </c>
-      <c r="D100" s="4" t="n">
-        <v>40000000000</v>
-      </c>
-      <c r="E100" s="4" t="n">
-        <v>8000000000</v>
       </c>
     </row>
     <row r="101">
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
+        <v>94707660034</v>
+      </c>
+      <c r="C104" s="4" t="n">
+        <v>64702641159</v>
+      </c>
+      <c r="D104" s="4" t="n">
+        <v>29100048410</v>
+      </c>
+      <c r="E104" s="4" t="n">
         <v>30826629189</v>
-      </c>
-      <c r="C104" s="4" t="n">
-        <v>29100048410</v>
-      </c>
-      <c r="D104" s="4" t="n">
-        <v>64702641159</v>
-      </c>
-      <c r="E104" s="4" t="n">
-        <v>94707660034</v>
       </c>
     </row>
     <row r="105">
@@ -2753,16 +2753,16 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
+        <v>3413186660000</v>
+      </c>
+      <c r="C116" s="4" t="n">
+        <v>3380747760000</v>
+      </c>
+      <c r="D116" s="4" t="n">
+        <v>3281691880000</v>
+      </c>
+      <c r="E116" s="4" t="n">
         <v>2461716200000</v>
-      </c>
-      <c r="C116" s="4" t="n">
-        <v>3281691880000</v>
-      </c>
-      <c r="D116" s="4" t="n">
-        <v>3380747760000</v>
-      </c>
-      <c r="E116" s="4" t="n">
-        <v>3413186660000</v>
       </c>
     </row>
     <row r="117">
@@ -2791,16 +2791,16 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
+        <v>1582471057146</v>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>1188435208200</v>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>769000107465</v>
+      </c>
+      <c r="E118" s="4" t="n">
         <v>859175348677</v>
-      </c>
-      <c r="C118" s="4" t="n">
-        <v>769000107465</v>
-      </c>
-      <c r="D118" s="4" t="n">
-        <v>1188435208200</v>
-      </c>
-      <c r="E118" s="4" t="n">
-        <v>1582471057146</v>
       </c>
     </row>
     <row r="119">
@@ -2810,16 +2810,16 @@
         </is>
       </c>
       <c r="B119" s="4" t="n">
+        <v>2828497462890</v>
+      </c>
+      <c r="C119" s="4" t="n">
+        <v>2112916282946</v>
+      </c>
+      <c r="D119" s="4" t="n">
+        <v>1971099177135</v>
+      </c>
+      <c r="E119" s="4" t="n">
         <v>1663090606797</v>
-      </c>
-      <c r="C119" s="4" t="n">
-        <v>1971099177135</v>
-      </c>
-      <c r="D119" s="4" t="n">
-        <v>2112916282946</v>
-      </c>
-      <c r="E119" s="4" t="n">
-        <v>2828497462890</v>
       </c>
     </row>
     <row r="120">
@@ -2829,16 +2829,16 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
+        <v>94707660034</v>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>64702641159</v>
+      </c>
+      <c r="D120" s="4" t="n">
+        <v>29100048410</v>
+      </c>
+      <c r="E120" s="4" t="n">
         <v>30826629189</v>
-      </c>
-      <c r="C120" s="4" t="n">
-        <v>29100048410</v>
-      </c>
-      <c r="D120" s="4" t="n">
-        <v>64702641159</v>
-      </c>
-      <c r="E120" s="4" t="n">
-        <v>94707660034</v>
       </c>
     </row>
     <row r="121">
@@ -2912,11 +2912,11 @@
   <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2927,22 +2927,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2022</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
         </is>
       </c>
     </row>
@@ -2953,16 +2953,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>35410589612616</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>38232401184050</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>33481608954953</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>34211128942240</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>33481608954953</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>38232401184050</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>35410589612616</v>
       </c>
     </row>
     <row r="3">
@@ -2972,16 +2972,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>-434546683224</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>-409564012665</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>-344679758524</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>-334674383087</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>-344679758524</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>-409564012665</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>-434546683224</v>
       </c>
     </row>
     <row r="4">
@@ -2991,16 +2991,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>34976042929392</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>37822837171385</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>33136929196429</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>33876454559153</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>33136929196429</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>37822837171385</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>34976042929392</v>
       </c>
     </row>
     <row r="5">
@@ -3010,16 +3010,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-27292194621378</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-31149334531193</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-27078338249235</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>-27949348024381</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-27078338249235</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-31149334531193</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-27292194621378</v>
       </c>
     </row>
     <row r="6">
@@ -3029,16 +3029,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>7683848308014</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>6673502640192</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>6058590947194</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>5927106534772</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>6058590947194</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>6673502640192</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>7683848308014</v>
       </c>
     </row>
     <row r="7">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>136303226388</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>75567438524</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>97825547538</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>54036974170</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>97825547538</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>75567438524</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>136303226388</v>
       </c>
     </row>
     <row r="8">
@@ -3067,16 +3067,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>-153168770819</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>-93616780951</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>-142580680640</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>-141471203463</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>-142580680640</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>-93616780951</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>-153168770819</v>
       </c>
     </row>
     <row r="9">
@@ -3086,16 +3086,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>-119082599327</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>-46775305829</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>-118568804103</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>-94143431408</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>-118568804103</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>-46775305829</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>-119082599327</v>
       </c>
     </row>
     <row r="10">
@@ -3105,16 +3105,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>-3322701974507</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>-3207574691174</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>-2835769469802</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>-2828208644376</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>-2835769469802</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>-3207574691174</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>-3322701974507</v>
       </c>
     </row>
     <row r="11">
@@ -3124,16 +3124,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>-824395851865</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>-795749355922</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>-693934934718</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>-673996996684</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>-693934934718</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>-795749355922</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>-824395851865</v>
       </c>
     </row>
     <row r="12">
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>3519884937211</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>2652129250669</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>2484131409572</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>2337466664419</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>2484131409572</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>2652129250669</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>3519884937211</v>
       </c>
     </row>
     <row r="13">
@@ -3162,16 +3162,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>41188910080</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>10013781125</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>11846230257</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>8582642521</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>11846230257</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>10013781125</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>41188910080</v>
       </c>
     </row>
     <row r="14">
@@ -3181,16 +3181,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>-13234356500</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-11130582486</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>-7217637455</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>-33721752227</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>-7217637455</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>-11130582486</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>-13234356500</v>
       </c>
     </row>
     <row r="15">
@@ -3200,16 +3200,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>27954553580</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-1116801361</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>4628592802</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>-25139109706</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>4628592802</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-1116801361</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>27954553580</v>
       </c>
     </row>
     <row r="16">
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>3547839490791</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>2651012449308</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>2488760002374</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>2312327554713</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>2488760002374</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>2651012449308</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>3547839490791</v>
       </c>
     </row>
     <row r="18">
@@ -3257,16 +3257,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>-849656975908</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-615476890636</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-517592806160</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>-521061271124</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-517592806160</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-615476890636</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-849656975908</v>
       </c>
     </row>
     <row r="19">
@@ -3276,16 +3276,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>130314948007</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>77380724274</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>-68019079</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>19425559808</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>-68019079</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>77380724274</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>130314948007</v>
       </c>
     </row>
     <row r="20">
@@ -3295,16 +3295,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>-719342027901</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-538096166362</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-517660825239</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>-501635711316</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-517660825239</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-538096166362</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-719342027901</v>
       </c>
     </row>
     <row r="21">
@@ -3314,16 +3314,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>2828497462890</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>2112916282946</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>1971099177135</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>1810691843397</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>1971099177135</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>2112916282946</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>2828497462890</v>
       </c>
     </row>
     <row r="22">
@@ -3352,16 +3352,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>2828497462890</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>2112916282946</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>1971099177135</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>1810691843397</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>1971099177135</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>2112916282946</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>2828497462890</v>
       </c>
     </row>
     <row r="24">
@@ -3371,16 +3371,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>7652</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>5713</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>5436</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>5350</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>5436</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>5713</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>7652</v>
       </c>
     </row>
     <row r="25">
@@ -3390,16 +3390,16 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>0</v>
+        <v>7652</v>
       </c>
       <c r="C25" s="4" t="n">
+        <v>5713</v>
+      </c>
+      <c r="D25" s="4" t="n">
         <v>5436</v>
       </c>
-      <c r="D25" s="4" t="n">
-        <v>5713</v>
-      </c>
       <c r="E25" s="4" t="n">
-        <v>7652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3435,11 +3435,11 @@
   <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="89" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3450,22 +3450,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2022</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
         </is>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>3547839490791</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>2651012449308</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>2488760002374</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>2312327554713</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>2488760002374</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>2651012449308</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>3547839490791</v>
       </c>
     </row>
     <row r="3">
@@ -3495,16 +3495,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>85291458403</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>80821846271</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>81257091304</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>79516376971</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>81257091304</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>80821846271</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>85291458403</v>
       </c>
     </row>
     <row r="4">
@@ -3514,16 +3514,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>-7695240894</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>77722354056</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>2374779451</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>2868205863</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>2374779451</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>77722354056</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>-7695240894</v>
       </c>
     </row>
     <row r="5">
@@ -3533,16 +3533,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-2434348570</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>140360327</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-1611805757</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>-8239903282</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-1611805757</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>140360327</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-2434348570</v>
       </c>
     </row>
     <row r="6">
@@ -3571,16 +3571,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>-110244947701</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>-47046699012</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-79561268312</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>-21327686776</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-79561268312</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-47046699012</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-110244947701</v>
       </c>
     </row>
     <row r="8">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>119082599327</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>46775305829</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>118568804103</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>94421152974</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>118568804103</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>46775305829</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>119082599327</v>
       </c>
     </row>
     <row r="9">
@@ -3628,16 +3628,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>3631839011356</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2809425616779</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>2609787603163</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>2459565700463</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>2609787603163</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>2809425616779</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>3631839011356</v>
       </c>
     </row>
     <row r="11">
@@ -3647,16 +3647,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>235691148778</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>-261742771385</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>39100711762</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>-52151674870</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>39100711762</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>-261742771385</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>235691148778</v>
       </c>
     </row>
     <row r="12">
@@ -3666,16 +3666,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>-2806722790389</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-2129837921117</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>-436683979881</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>-1753323314557</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>-436683979881</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-2129837921117</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>-2806722790389</v>
       </c>
     </row>
     <row r="13">
@@ -3685,16 +3685,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>-369026498161</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>273559805376</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>92449328770</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>76506711125</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>92449328770</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>273559805376</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>-369026498161</v>
       </c>
     </row>
     <row r="14">
@@ -3704,16 +3704,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>169889358691</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>13981231920</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>-103556391934</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>-59503878567</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>-103556391934</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>13981231920</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>169889358691</v>
       </c>
     </row>
     <row r="15">
@@ -3723,16 +3723,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-117889071318</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-46067825009</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-122841644646</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>-90657750651</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-122841644646</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-46067825009</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-117889071318</v>
       </c>
     </row>
     <row r="16">
@@ -3742,16 +3742,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>-607285010641</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>-555484436785</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>-466349274224</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>-464338080937</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>-466349274224</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>-555484436785</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>-607285010641</v>
       </c>
     </row>
     <row r="17">
@@ -3780,16 +3780,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>-19687607067</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-20648525024</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-104164881917</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>-15516505310</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-104164881917</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-20648525024</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-19687607067</v>
       </c>
     </row>
     <row r="19">
@@ -3799,16 +3799,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>18890403841</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>83185174755</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>1507741471093</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>100581206696</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>1507741471093</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>83185174755</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>18890403841</v>
       </c>
     </row>
     <row r="20">
@@ -3818,16 +3818,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>-115542827250</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-90406299690</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-83115434103</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>-52384601566</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-83115434103</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-90406299690</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-115542827250</v>
       </c>
     </row>
     <row r="21">
@@ -3837,16 +3837,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>3636364</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>3181818</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>2289295529</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>1498185785</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>2289295529</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>3181818</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>3636364</v>
       </c>
     </row>
     <row r="22">
@@ -3856,16 +3856,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>-4067400000000</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>-1120070000000</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>-2240100000000</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>-540000000000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>-2240100000000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>-1120070000000</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>-4067400000000</v>
       </c>
     </row>
     <row r="23">
@@ -3875,16 +3875,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>3210000000000</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>960000000000</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>1680000000000</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>200000000000</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>1680000000000</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>960000000000</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>3210000000000</v>
       </c>
     </row>
     <row r="24">
@@ -3894,16 +3894,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>0</v>
+        <v>-1950000000</v>
       </c>
       <c r="C24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4" t="n">
         <v>-3980000000</v>
       </c>
-      <c r="D24" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E24" s="4" t="n">
-        <v>-1950000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3932,16 +3932,16 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
+        <v>81101160826</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>39436141188</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>66432820820</v>
+      </c>
+      <c r="E26" s="4" t="n">
         <v>20219137155</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>66432820820</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>39436141188</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>81101160826</v>
       </c>
     </row>
     <row r="27">
@@ -3951,16 +3951,16 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
+        <v>-893788030060</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>-211036976684</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>-578473317754</v>
+      </c>
+      <c r="E27" s="4" t="n">
         <v>-370667278626</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>-578473317754</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>-211036976684</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>-893788030060</v>
       </c>
     </row>
     <row r="28">
@@ -3970,16 +3970,16 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
+        <v>64823800000</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>67243920000</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4" t="n">
         <v>1447231530000</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>67243920000</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>64823800000</v>
       </c>
     </row>
     <row r="29">
@@ -4008,16 +4008,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>9817871495359</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>6788859495016</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>8159472964689</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>6261254967206</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>8159472964689</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>6788859495016</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>9817871495359</v>
       </c>
     </row>
     <row r="31">
@@ -4027,16 +4027,16 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>-8936027876466</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>-5831605732949</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>-8458230585768</v>
+      </c>
+      <c r="E31" s="4" t="n">
         <v>-6300139792578</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>-8458230585768</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>-5831605732949</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>-8936027876466</v>
       </c>
     </row>
     <row r="32">
@@ -4065,16 +4065,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>-673692457830</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>-671681829760</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>-615443389700</v>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>-616671158340</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>-615443389700</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>-671681829760</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>-673692457830</v>
       </c>
     </row>
     <row r="34">
@@ -4103,16 +4103,16 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
+        <v>272974961063</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>352815852307</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>-914201010779</v>
+      </c>
+      <c r="E35" s="4" t="n">
         <v>791675546288</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>-914201010779</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>352815852307</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>272974961063</v>
       </c>
     </row>
     <row r="36">
@@ -4122,16 +4122,16 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
+        <v>-601922665156</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>224964050378</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>15067142560</v>
+      </c>
+      <c r="E36" s="4" t="n">
         <v>521589474358</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>15067142560</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>224964050378</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>-601922665156</v>
       </c>
     </row>
     <row r="37">
@@ -4141,16 +4141,16 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>1122712392130</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>896147917336</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>879548130711</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>355454838957</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>879548130711</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>896147917336</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>1122712392130</v>
       </c>
     </row>
     <row r="38">
@@ -4160,16 +4160,16 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
+        <v>1235530057</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>1600424416</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>1532644065</v>
+      </c>
+      <c r="E38" s="4" t="n">
         <v>2503817396</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>1532644065</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>1600424416</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>1235530057</v>
       </c>
     </row>
     <row r="39">
@@ -4179,16 +4179,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>522025257031</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>1122712392130</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>896147917336</v>
+      </c>
+      <c r="E39" s="4" t="n">
         <v>879548130711</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>896147917336</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>1122712392130</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>522025257031</v>
       </c>
     </row>
     <row r="40">
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>0</v>
+        <v>-97918137408</v>
       </c>
       <c r="C42" s="4" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>-97918137408</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4262,11 +4262,11 @@
   <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4277,8 +4277,12 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="6" t="n"/>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Khối "CHỈ SỐ TÀI CHÍNH" tính bằng công thức từ khối "DỮ LIỆU TRÍCH XUẤT" bên dưới, không phải số nhập tay. Khối "DỮ LIỆU TRÍCH XUẤT" được dò tự động theo TÊN khoản mục (đúng theo tên gốc trong báo cáo) và theo NĂM từ 3 sheet balance_sheet / income_statement — không tham chiếu ô cố định. Có thể sửa nhãn khoản mục ở cột A khối này nếu công ty đổi tên dòng; công thức sẽ tự dò lại. Các năm được xếp tăng dần từ trái sang phải.</t>
+        </is>
+      </c>
     </row>
     <row r="3"/>
     <row r="4">
@@ -4299,19 +4303,19 @@
         </is>
       </c>
       <c r="B5" s="10">
+        <f>'balance_sheet'!E1</f>
+        <v/>
+      </c>
+      <c r="C5" s="10">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="D5" s="10">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="E5" s="10">
         <f>'balance_sheet'!B1</f>
-        <v/>
-      </c>
-      <c r="C5" s="10">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="D5" s="10">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="E5" s="10">
-        <f>'balance_sheet'!E1</f>
         <v/>
       </c>
     </row>
@@ -4825,19 +4829,19 @@
         </is>
       </c>
       <c r="B38" s="10">
+        <f>'balance_sheet'!E1</f>
+        <v/>
+      </c>
+      <c r="C38" s="10">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="D38" s="10">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="E38" s="10">
         <f>'balance_sheet'!B1</f>
-        <v/>
-      </c>
-      <c r="C38" s="10">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="D38" s="10">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="E38" s="10">
-        <f>'balance_sheet'!E1</f>
         <v/>
       </c>
     </row>

--- a/financials/PNJ/PNJ_financials.xlsx
+++ b/financials/PNJ/PNJ_financials.xlsx
@@ -543,14 +543,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:I123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -561,22 +565,42 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -587,16 +611,28 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>5405256600641</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>7333364485251</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>7143929036497</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>9292192238421</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>11966357761798</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>12958118192260</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>15692597267632</v>
+      </c>
+      <c r="I2" s="4" t="n">
         <v>18614031193890</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>15692597267632</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>12958118192260</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>11966357761798</v>
       </c>
     </row>
     <row r="3">
@@ -606,16 +642,28 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>206721179629</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>95224439008</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>422234781061</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>355454838957</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>879548130711</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>896147917336</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>1122712392130</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>522025257031</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1122712392130</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>896147917336</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>879548130711</v>
       </c>
     </row>
     <row r="4">
@@ -625,16 +673,28 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>206721179629</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>95224439008</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>422234781061</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>355454838957</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>879548130711</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>896147917336</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>1022712392130</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>438425257031</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1022712392130</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>896147917336</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>879548130711</v>
       </c>
     </row>
     <row r="5">
@@ -644,16 +704,28 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>100000000000</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>83600000000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>100000000000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -663,16 +735,28 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="n">
         <v>97918137408</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -681,17 +765,21 @@
           <t>Đầu tư ngắn hạn</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="n">
         <v>97918137408</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -712,6 +800,18 @@
       <c r="E8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -720,16 +820,28 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>155196257825</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>129688313476</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>98997286429</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>111969758488</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>300880402245</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>215035937840</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>401134922152</v>
+      </c>
+      <c r="I9" s="4" t="n">
         <v>153980309545</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>401134922152</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>215035937840</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>300880402245</v>
       </c>
     </row>
     <row r="10">
@@ -739,16 +851,28 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>57664060443</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>48292876716</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>67591685619</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>59930655833</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>56532707659</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>69277567110</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>70851635761</v>
+      </c>
+      <c r="I10" s="4" t="n">
         <v>48760415990</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>70851635761</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>69277567110</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>56532707659</v>
       </c>
     </row>
     <row r="11">
@@ -758,16 +882,28 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>57981679202</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>74867455343</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>20218946599</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>30659175548</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>68902837213</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>27775617785</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>253102611434</v>
+      </c>
+      <c r="I11" s="4" t="n">
         <v>38085152243</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>253102611434</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>27775617785</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>68902837213</v>
       </c>
     </row>
     <row r="12">
@@ -788,6 +924,18 @@
       <c r="E12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -807,6 +955,18 @@
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -815,16 +975,28 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>39159008338</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>5287941028</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>12261206010</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>22831538994</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>37641170145</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>32980198226</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>64867442121</v>
+      </c>
+      <c r="I14" s="4" t="n">
         <v>90681158676</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>64867442121</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>32980198226</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>37641170145</v>
       </c>
     </row>
     <row r="15">
@@ -834,16 +1006,28 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-1202878846</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>-2004798077</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>-2862909308</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>-5049680837</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>-28518444279</v>
+      </c>
+      <c r="I15" s="4" t="n">
         <v>-31918617346</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-28518444279</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-5049680837</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-2862909308</v>
       </c>
     </row>
     <row r="16">
@@ -853,16 +1037,28 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>4968145942990</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>7030420371216</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>6545905987056</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>8754741712359</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>10506054932284</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>10940937959289</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>13015170477311</v>
+      </c>
+      <c r="I16" s="4" t="n">
         <v>15835334529837</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>13015170477311</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>10940937959289</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>10506054932284</v>
       </c>
     </row>
     <row r="17">
@@ -872,16 +1068,28 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>4968145942990</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>7030420371216</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>6545905987056</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>8754741712359</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>10508065026916</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>10944749006797</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>13074586927914</v>
+      </c>
+      <c r="I17" s="4" t="n">
         <v>15881309718303</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>13074586927914</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>10944749006797</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>10508065026916</v>
       </c>
     </row>
     <row r="18">
@@ -891,16 +1099,28 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>-2010094632</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>-3811047508</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>-59416450603</v>
+      </c>
+      <c r="I18" s="4" t="n">
         <v>-45975188466</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-59416450603</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-3811047508</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-2010094632</v>
       </c>
     </row>
     <row r="19">
@@ -921,6 +1141,18 @@
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -929,16 +1161,28 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>66191416708</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>71633378895</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>66112866470</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>56716921380</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>74007356286</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>94051248427</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>132726608716</v>
+      </c>
+      <c r="I20" s="4" t="n">
         <v>94862372660</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>132726608716</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>94051248427</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>74007356286</v>
       </c>
     </row>
     <row r="21">
@@ -948,16 +1192,28 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>625511019</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>6306692920</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>10670276957</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>8705831517</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>5866940272</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>1845129368</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>682867323</v>
+      </c>
+      <c r="I21" s="4" t="n">
         <v>234579085</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>682867323</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>1845129368</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>5866940272</v>
       </c>
     </row>
     <row r="22">
@@ -967,16 +1223,28 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>8376292470</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>91289736</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>7838524</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>4603175720</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4" t="n">
         <v>106008324</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -985,16 +1253,20 @@
           <t>Tài sản lưu động khác</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="4" t="n">
+      <c r="B23" s="4" t="inlineStr"/>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1005,16 +1277,28 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>1032638955963</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>1269599936565</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>1339217061954</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>1326824308701</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>1370766887448</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1469439823096</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>1515133510053</v>
+      </c>
+      <c r="I24" s="4" t="n">
         <v>1549599053151</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>1515133510053</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>1469439823096</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>1370766887448</v>
       </c>
     </row>
     <row r="25">
@@ -1024,16 +1308,28 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>57498444869</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>70721623109</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>77310617360</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>84131506164</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>93956493011</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>104636239106</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>115599492454</v>
+      </c>
+      <c r="I25" s="4" t="n">
         <v>121168536356</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>115599492454</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>104636239106</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>93956493011</v>
       </c>
     </row>
     <row r="26">
@@ -1054,6 +1350,18 @@
       <c r="E26" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1073,6 +1381,18 @@
       <c r="E27" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1081,16 +1401,28 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
+        <v>57498444869</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>70721623109</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>77310617360</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>84131506164</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>93956493011</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>104636239106</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>115599492454</v>
+      </c>
+      <c r="I28" s="4" t="n">
         <v>121168536356</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>115599492454</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>104636239106</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>93956493011</v>
       </c>
     </row>
     <row r="29">
@@ -1111,6 +1443,18 @@
       <c r="E29" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1119,16 +1463,28 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>719287274744</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>923870354474</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>931617117533</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>909985491983</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>882432821075</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>882715109732</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>857118818527</v>
+      </c>
+      <c r="I30" s="4" t="n">
         <v>855770473476</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>857118818527</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>882715109732</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>882432821075</v>
       </c>
     </row>
     <row r="31">
@@ -1138,16 +1494,28 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>225960569846</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>263827234353</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>281244232172</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>259137188160</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>239734551747</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>256373758673</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>248430247930</v>
+      </c>
+      <c r="I31" s="4" t="n">
         <v>236245161003</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>248430247930</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>256373758673</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>239734551747</v>
       </c>
     </row>
     <row r="32">
@@ -1157,16 +1525,28 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
+        <v>454178423940</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>534818699342</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>600464186725</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>633614629426</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>672781337441</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>747570855214</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>796271142120</v>
+      </c>
+      <c r="I32" s="4" t="n">
         <v>845032678156</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>796271142120</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>747570855214</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>672781337441</v>
       </c>
     </row>
     <row r="33">
@@ -1176,16 +1556,28 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>-228217854094</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>-270991464989</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>-319219954553</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>-374477441266</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>-433046785694</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>-491197096541</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>-547840894190</v>
+      </c>
+      <c r="I33" s="4" t="n">
         <v>-608787517153</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>-547840894190</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>-491197096541</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>-433046785694</v>
       </c>
     </row>
     <row r="34">
@@ -1206,6 +1598,18 @@
       <c r="E34" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1225,6 +1629,18 @@
       <c r="E35" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -1244,6 +1660,18 @@
       <c r="E36" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1252,16 +1680,28 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>493326704898</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>660043120121</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>650372885361</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>650848303823</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>642698269328</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>626341351059</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>608688570597</v>
+      </c>
+      <c r="I37" s="4" t="n">
         <v>619525312473</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>608688570597</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>626341351059</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>642698269328</v>
       </c>
     </row>
     <row r="38">
@@ -1271,16 +1711,28 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
+        <v>499937407873</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>679619883005</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>683791142309</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>697774918988</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>707010800099</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>708071904553</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>708142194553</v>
+      </c>
+      <c r="I38" s="4" t="n">
         <v>734945157553</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>708142194553</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>708071904553</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>707010800099</v>
       </c>
     </row>
     <row r="39">
@@ -1290,16 +1742,28 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>-6610702975</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>-19576762884</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>-33418256948</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>-46926615165</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>-64312530771</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>-81730553494</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>-99453623956</v>
+      </c>
+      <c r="I39" s="4" t="n">
         <v>-115419845080</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>-99453623956</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>-81730553494</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>-64312530771</v>
       </c>
     </row>
     <row r="40">
@@ -1320,6 +1784,18 @@
       <c r="E40" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1339,6 +1815,18 @@
       <c r="E41" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -1358,6 +1846,18 @@
       <c r="E42" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -1377,6 +1877,18 @@
       <c r="E43" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1385,16 +1897,28 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>3980000000</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>3980000000</v>
+      </c>
+      <c r="I44" s="4" t="n">
         <v>5930000000</v>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>3980000000</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>3980000000</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1415,6 +1939,18 @@
       <c r="E45" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -1434,6 +1970,18 @@
       <c r="E46" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1442,17 +1990,29 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>401201613400</v>
+        <v>395271613400</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>399251613400</v>
+        <v>395271613400</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>399251613400</v>
+        <v>395271613400</v>
       </c>
       <c r="E47" s="4" t="n">
         <v>395271613400</v>
       </c>
+      <c r="F47" s="4" t="n">
+        <v>395271613400</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>399251613400</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>399251613400</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>401201613400</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -1472,6 +2032,18 @@
       <c r="E48" s="4" t="n">
         <v>-395271613400</v>
       </c>
+      <c r="F48" s="4" t="n">
+        <v>-395271613400</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>-395271613400</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>-395271613400</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>-395271613400</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -1491,6 +2063,18 @@
       <c r="E49" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -1499,16 +2083,28 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
+        <v>185030555196</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>246550560548</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>297285460058</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>301911940704</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>363550944173</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>449008425848</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>473732557913</v>
+      </c>
+      <c r="I50" s="4" t="n">
         <v>472022383285</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>473732557913</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>449008425848</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>363550944173</v>
       </c>
     </row>
     <row r="51">
@@ -1518,16 +2114,28 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
+        <v>99678730358</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>158318980481</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>206301766031</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>201443147089</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>243656590750</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>329182091504</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>276525499295</v>
+      </c>
+      <c r="I51" s="4" t="n">
         <v>144500376660</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>276525499295</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>329182091504</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>243656590750</v>
       </c>
     </row>
     <row r="52">
@@ -1548,6 +2156,18 @@
       <c r="E52" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -1567,6 +2187,18 @@
       <c r="E53" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -1575,16 +2207,28 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
+        <v>6437895556604</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>8602964421816</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>8483146098451</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>10619016547122</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>13337124649246</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>14427558015356</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>17207730777685</v>
+      </c>
+      <c r="I54" s="4" t="n">
         <v>20163630247041</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>17207730777685</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>14427558015356</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>13337124649246</v>
       </c>
     </row>
     <row r="55">
@@ -1594,16 +2238,28 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
+        <v>2692822128700</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>4025698610469</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>3241284233443</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>4606382566869</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>4893029994396</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>4621377351380</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>5952424147163</v>
+      </c>
+      <c r="I55" s="4" t="n">
         <v>6888716787629</v>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>5952424147163</v>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>4621377351380</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>4893029994396</v>
       </c>
     </row>
     <row r="56">
@@ -1613,16 +2269,28 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
+        <v>2677317785700</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>4017860824469</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>3231907356443</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>4563002409508</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>4883064421396</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>4611956609380</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>5941881733413</v>
+      </c>
+      <c r="I56" s="4" t="n">
         <v>6874318773629</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>5941881733413</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>4611956609380</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>4883064421396</v>
       </c>
     </row>
     <row r="57">
@@ -1632,16 +2300,28 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
+        <v>1558482498026</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>2610902622222</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>1839275064065</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>2721930701144</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>2683045875772</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>2384288254693</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>3341542016760</v>
+      </c>
+      <c r="I57" s="4" t="n">
         <v>4223385635653</v>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>3341542016760</v>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>2384288254693</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>2683045875772</v>
       </c>
     </row>
     <row r="58">
@@ -1651,16 +2331,28 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
+        <v>342676925196</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>690808185195</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>481588464720</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>680447298103</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>277212839495</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>257304950807</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>624291098148</v>
+      </c>
+      <c r="I58" s="4" t="n">
         <v>333861329514</v>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>624291098148</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>257304950807</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>277212839495</v>
       </c>
     </row>
     <row r="59">
@@ -1670,16 +2362,28 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
+        <v>82798544221</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>95353052369</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>157182968364</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>156729112135</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>222164283405</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>215299493413</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>188182044409</v>
+      </c>
+      <c r="I59" s="4" t="n">
         <v>182492529057</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>188182044409</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>215299493413</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>222164283405</v>
       </c>
     </row>
     <row r="60">
@@ -1689,16 +2393,28 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
+        <v>153579308096</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>192682671178</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>214710310923</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>309500571902</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>292985361927</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>344258054659</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>448697283312</v>
+      </c>
+      <c r="I60" s="4" t="n">
         <v>777717691575</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>448697283312</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>344258054659</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>292985361927</v>
       </c>
     </row>
     <row r="61">
@@ -1708,16 +2424,28 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
+        <v>228337052181</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>222296091737</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>290765645610</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>385144216152</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>534807250396</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>673116492808</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>596322426230</v>
+      </c>
+      <c r="I61" s="4" t="n">
         <v>569308694234</v>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>596322426230</v>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>673116492808</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>534807250396</v>
       </c>
     </row>
     <row r="62">
@@ -1727,16 +2455,28 @@
         </is>
       </c>
       <c r="B62" s="4" t="n">
+        <v>10833940595</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>45877630688</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>55520256916</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>69534599697</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>453432735944</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>307718428978</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>360040211420</v>
+      </c>
+      <c r="I62" s="4" t="n">
         <v>321827090456</v>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>360040211420</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>307718428978</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>453432735944</v>
       </c>
     </row>
     <row r="63">
@@ -1757,6 +2497,18 @@
       <c r="E63" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -1776,6 +2528,18 @@
       <c r="E64" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -1784,16 +2548,28 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
+        <v>237629562960</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>69257739996</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>76978636900</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>83404423727</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>227169093119</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>228798913738</v>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>106241642105</v>
+      </c>
+      <c r="I65" s="4" t="n">
         <v>103175435252</v>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>106241642105</v>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>228798913738</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>227169093119</v>
       </c>
     </row>
     <row r="66">
@@ -1803,17 +2579,29 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
-        <v>26574672229</v>
+        <v>0</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>26547708303</v>
+        <v>0</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>29061192534</v>
+        <v>0</v>
       </c>
       <c r="E66" s="4" t="n">
         <v>30129306488</v>
       </c>
+      <c r="F66" s="4" t="n">
+        <v>30129306488</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>29061192534</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>26547708303</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>26574672229</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -1822,16 +2610,28 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
+        <v>62979954425</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>90682831084</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>115886008945</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>126182180160</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>162117674850</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>172110827750</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>250017302726</v>
+      </c>
+      <c r="I67" s="4" t="n">
         <v>335975695659</v>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>250017302726</v>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>172110827750</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>162117674850</v>
       </c>
     </row>
     <row r="68">
@@ -1841,16 +2641,28 @@
         </is>
       </c>
       <c r="B68" s="4" t="n">
+        <v>15504343000</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>7837786000</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>9376877000</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>43380157361</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>9965573000</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>9420742000</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>10542413750</v>
+      </c>
+      <c r="I68" s="4" t="n">
         <v>14398014000</v>
-      </c>
-      <c r="C68" s="4" t="n">
-        <v>10542413750</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>9420742000</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>9965573000</v>
       </c>
     </row>
     <row r="69">
@@ -1871,6 +2683,18 @@
       <c r="E69" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -1890,6 +2714,18 @@
       <c r="E70" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -1898,16 +2734,28 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
+        <v>628026000</v>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>476006000</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>526168000</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>518668000</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>218668000</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>218668000</v>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>178668000</v>
+      </c>
+      <c r="I71" s="4" t="n">
         <v>1715384000</v>
-      </c>
-      <c r="C71" s="4" t="n">
-        <v>178668000</v>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>218668000</v>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>218668000</v>
       </c>
     </row>
     <row r="72">
@@ -1917,15 +2765,27 @@
         </is>
       </c>
       <c r="B72" s="4" t="n">
-        <v>0</v>
+        <v>7800000000</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>0</v>
+        <v>3700000000</v>
       </c>
       <c r="D72" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1935,16 +2795,20 @@
           <t>Thuế thu nhập hoãn lại</t>
         </is>
       </c>
-      <c r="B73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="4" t="n">
+      <c r="B73" s="4" t="inlineStr"/>
+      <c r="C73" s="4" t="inlineStr"/>
+      <c r="D73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1966,6 +2830,18 @@
       <c r="E74" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -1974,16 +2850,28 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
+        <v>7076317000</v>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>3661780000</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>8850709000</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>42861489361</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>9746905000</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>9202074000</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>10363745750</v>
+      </c>
+      <c r="I75" s="4" t="n">
         <v>12682630000</v>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>10363745750</v>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>9202074000</v>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>9746905000</v>
       </c>
     </row>
     <row r="76">
@@ -2004,6 +2892,18 @@
       <c r="E76" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -2023,6 +2923,18 @@
       <c r="E77" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -2031,16 +2943,28 @@
         </is>
       </c>
       <c r="B78" s="4" t="n">
+        <v>3745073427904</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>4577265811347</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>5241861865008</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>6012633980253</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>8444094654850</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>9806180663976</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>11255306630522</v>
+      </c>
+      <c r="I78" s="4" t="n">
         <v>13274913459412</v>
-      </c>
-      <c r="C78" s="4" t="n">
-        <v>11255306630522</v>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>9806180663976</v>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>8444094654850</v>
       </c>
     </row>
     <row r="79">
@@ -2050,16 +2974,28 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
+        <v>3745073427904</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>4577265811347</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>5241861865008</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>6012633980253</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>8444094654850</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>9806180663976</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>11255306630522</v>
+      </c>
+      <c r="I79" s="4" t="n">
         <v>13274913459412</v>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>11255306630522</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>9806180663976</v>
-      </c>
-      <c r="E79" s="4" t="n">
-        <v>8444094654850</v>
       </c>
     </row>
     <row r="80">
@@ -2069,16 +3005,28 @@
         </is>
       </c>
       <c r="B80" s="4" t="n">
+        <v>1670029820000</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>2252935850000</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>2276123620000</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>2276123620000</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>2461716200000</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>3281691880000</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>3380747760000</v>
+      </c>
+      <c r="I80" s="4" t="n">
         <v>3413186660000</v>
-      </c>
-      <c r="C80" s="4" t="n">
-        <v>3380747760000</v>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>3281691880000</v>
-      </c>
-      <c r="E80" s="4" t="n">
-        <v>2461716200000</v>
       </c>
     </row>
     <row r="81">
@@ -2088,16 +3036,28 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
+        <v>925397862458</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>968074112458</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>991261882458</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>991261882458</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>2251376032458</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>1851376032458</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>1950309912458</v>
+      </c>
+      <c r="I81" s="4" t="n">
         <v>1982694812458</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>1950309912458</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>1851376032458</v>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>2251376032458</v>
       </c>
     </row>
     <row r="82">
@@ -2118,6 +3078,18 @@
       <c r="E82" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -2126,15 +3098,27 @@
         </is>
       </c>
       <c r="B83" s="4" t="n">
-        <v>-3384090000</v>
+        <v>-7090000</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>-3384090000</v>
+        <v>-2101090000</v>
       </c>
       <c r="D83" s="4" t="n">
         <v>-3384090000</v>
       </c>
       <c r="E83" s="4" t="n">
+        <v>-4908890000</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>-3384090000</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>-3384090000</v>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>-3384090000</v>
+      </c>
+      <c r="I83" s="4" t="n">
         <v>-3384090000</v>
       </c>
     </row>
@@ -2156,6 +3140,18 @@
       <c r="E84" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -2175,6 +3171,18 @@
       <c r="E85" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -2183,16 +3191,28 @@
         </is>
       </c>
       <c r="B86" s="4" t="n">
+        <v>265087556918</v>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>313083556918</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>372779556918</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>800503556918</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>1212120556918</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>1936397556918</v>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>2626281556918</v>
+      </c>
+      <c r="I86" s="4" t="n">
         <v>3471447556918</v>
-      </c>
-      <c r="C86" s="4" t="n">
-        <v>2626281556918</v>
-      </c>
-      <c r="D86" s="4" t="n">
-        <v>1936397556918</v>
-      </c>
-      <c r="E86" s="4" t="n">
-        <v>1212120556918</v>
       </c>
     </row>
     <row r="87">
@@ -2213,6 +3233,18 @@
       <c r="E87" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -2232,6 +3264,18 @@
       <c r="E88" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -2240,16 +3284,28 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
+        <v>884565278528</v>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>1045273381971</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>1605080895632</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>1949653810877</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>2522265955474</v>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>2740099284600</v>
+      </c>
+      <c r="H89" s="4" t="n">
+        <v>3301351491146</v>
+      </c>
+      <c r="I89" s="4" t="n">
         <v>4410968520036</v>
-      </c>
-      <c r="C89" s="4" t="n">
-        <v>3301351491146</v>
-      </c>
-      <c r="D89" s="4" t="n">
-        <v>2740099284600</v>
-      </c>
-      <c r="E89" s="4" t="n">
-        <v>2522265955474</v>
       </c>
     </row>
     <row r="90">
@@ -2270,6 +3326,18 @@
       <c r="E90" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -2289,6 +3357,18 @@
       <c r="E91" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -2308,6 +3388,18 @@
       <c r="E92" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -2327,6 +3419,18 @@
       <c r="E93" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -2346,6 +3450,18 @@
       <c r="E94" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -2354,16 +3470,28 @@
         </is>
       </c>
       <c r="B95" s="4" t="n">
+        <v>6437895556604</v>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>8602964421816</v>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>8483146098451</v>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>10619016547122</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>13337124649246</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>14427558015356</v>
+      </c>
+      <c r="H95" s="4" t="n">
+        <v>17207730777685</v>
+      </c>
+      <c r="I95" s="4" t="n">
         <v>20163630247041</v>
-      </c>
-      <c r="C95" s="4" t="n">
-        <v>17207730777685</v>
-      </c>
-      <c r="D95" s="4" t="n">
-        <v>14427558015356</v>
-      </c>
-      <c r="E95" s="4" t="n">
-        <v>13337124649246</v>
       </c>
     </row>
     <row r="96">
@@ -2384,6 +3512,18 @@
       <c r="E96" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -2403,6 +3543,18 @@
       <c r="E97" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -2422,6 +3574,18 @@
       <c r="E98" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -2430,16 +3594,28 @@
         </is>
       </c>
       <c r="B99" s="4" t="n">
+        <v>391509842</v>
+      </c>
+      <c r="C99" s="4" t="n">
+        <v>1240040389</v>
+      </c>
+      <c r="D99" s="4" t="n">
+        <v>128327047</v>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>553186190</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>666596536</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>52235556</v>
+      </c>
+      <c r="H99" s="4" t="n">
+        <v>831677115</v>
+      </c>
+      <c r="I99" s="4" t="n">
         <v>372199982</v>
-      </c>
-      <c r="C99" s="4" t="n">
-        <v>831677115</v>
-      </c>
-      <c r="D99" s="4" t="n">
-        <v>52235556</v>
-      </c>
-      <c r="E99" s="4" t="n">
-        <v>666596536</v>
       </c>
     </row>
     <row r="100">
@@ -2449,16 +3625,28 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>140000000000</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>90000000000</v>
+      </c>
+      <c r="H100" s="4" t="n">
+        <v>40000000000</v>
+      </c>
+      <c r="I100" s="4" t="n">
         <v>8000000000</v>
-      </c>
-      <c r="C100" s="4" t="n">
-        <v>40000000000</v>
-      </c>
-      <c r="D100" s="4" t="n">
-        <v>90000000000</v>
-      </c>
-      <c r="E100" s="4" t="n">
-        <v>140000000000</v>
       </c>
     </row>
     <row r="101">
@@ -2479,6 +3667,18 @@
       <c r="E101" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -2498,6 +3698,18 @@
       <c r="E102" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -2517,6 +3729,18 @@
       <c r="E103" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -2525,16 +3749,28 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
+        <v>70822681154</v>
+      </c>
+      <c r="C104" s="4" t="n">
+        <v>28457398434</v>
+      </c>
+      <c r="D104" s="4" t="n">
+        <v>33003867003</v>
+      </c>
+      <c r="E104" s="4" t="n">
+        <v>30795369850</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>30826629189</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>29100048410</v>
+      </c>
+      <c r="H104" s="4" t="n">
+        <v>64702641159</v>
+      </c>
+      <c r="I104" s="4" t="n">
         <v>94707660034</v>
-      </c>
-      <c r="C104" s="4" t="n">
-        <v>64702641159</v>
-      </c>
-      <c r="D104" s="4" t="n">
-        <v>29100048410</v>
-      </c>
-      <c r="E104" s="4" t="n">
-        <v>30826629189</v>
       </c>
     </row>
     <row r="105">
@@ -2555,6 +3791,18 @@
       <c r="E105" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
@@ -2562,16 +3810,20 @@
           <t>Đầu tư nắm giữ đến ngày đáo hạn</t>
         </is>
       </c>
-      <c r="B106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" s="4" t="n">
+      <c r="B106" s="4" t="inlineStr"/>
+      <c r="C106" s="4" t="inlineStr"/>
+      <c r="D106" s="4" t="inlineStr"/>
+      <c r="E106" s="4" t="inlineStr"/>
+      <c r="F106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2593,6 +3845,18 @@
       <c r="E107" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -2612,6 +3876,18 @@
       <c r="E108" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -2631,6 +3907,18 @@
       <c r="E109" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -2650,6 +3938,18 @@
       <c r="E110" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -2669,6 +3969,18 @@
       <c r="E111" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
@@ -2688,6 +4000,18 @@
       <c r="E112" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -2707,6 +4031,18 @@
       <c r="E113" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -2726,6 +4062,18 @@
       <c r="E114" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -2733,16 +4081,20 @@
           <t>Cổ phiếu ưu đãi</t>
         </is>
       </c>
-      <c r="B115" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C115" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" s="4" t="n">
+      <c r="B115" s="4" t="inlineStr"/>
+      <c r="C115" s="4" t="inlineStr"/>
+      <c r="D115" s="4" t="inlineStr"/>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2753,16 +4105,28 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
+        <v>1670029820000</v>
+      </c>
+      <c r="C116" s="4" t="n">
+        <v>2252935850000</v>
+      </c>
+      <c r="D116" s="4" t="n">
+        <v>2276123620000</v>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>2276123620000</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>2461716200000</v>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>3281691880000</v>
+      </c>
+      <c r="H116" s="4" t="n">
+        <v>3380747760000</v>
+      </c>
+      <c r="I116" s="4" t="n">
         <v>3413186660000</v>
-      </c>
-      <c r="C116" s="4" t="n">
-        <v>3380747760000</v>
-      </c>
-      <c r="D116" s="4" t="n">
-        <v>3281691880000</v>
-      </c>
-      <c r="E116" s="4" t="n">
-        <v>2461716200000</v>
       </c>
     </row>
     <row r="117">
@@ -2783,6 +4147,18 @@
       <c r="E117" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F117" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -2791,16 +4167,28 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
+        <v>98780546381</v>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>29482225528</v>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>670845205971</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>920611645232</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>859175348677</v>
+      </c>
+      <c r="G118" s="4" t="n">
+        <v>769000107465</v>
+      </c>
+      <c r="H118" s="4" t="n">
+        <v>1188435208200</v>
+      </c>
+      <c r="I118" s="4" t="n">
         <v>1582471057146</v>
-      </c>
-      <c r="C118" s="4" t="n">
-        <v>1188435208200</v>
-      </c>
-      <c r="D118" s="4" t="n">
-        <v>769000107465</v>
-      </c>
-      <c r="E118" s="4" t="n">
-        <v>859175348677</v>
       </c>
     </row>
     <row r="119">
@@ -2810,16 +4198,28 @@
         </is>
       </c>
       <c r="B119" s="4" t="n">
+        <v>785784732147</v>
+      </c>
+      <c r="C119" s="4" t="n">
+        <v>1015791156443</v>
+      </c>
+      <c r="D119" s="4" t="n">
+        <v>934235689661</v>
+      </c>
+      <c r="E119" s="4" t="n">
+        <v>1029042165645</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>1663090606797</v>
+      </c>
+      <c r="G119" s="4" t="n">
+        <v>1971099177135</v>
+      </c>
+      <c r="H119" s="4" t="n">
+        <v>2112916282946</v>
+      </c>
+      <c r="I119" s="4" t="n">
         <v>2828497462890</v>
-      </c>
-      <c r="C119" s="4" t="n">
-        <v>2112916282946</v>
-      </c>
-      <c r="D119" s="4" t="n">
-        <v>1971099177135</v>
-      </c>
-      <c r="E119" s="4" t="n">
-        <v>1663090606797</v>
       </c>
     </row>
     <row r="120">
@@ -2829,16 +4229,28 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
+        <v>70822681154</v>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>28457398434</v>
+      </c>
+      <c r="D120" s="4" t="n">
+        <v>33003867003</v>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>30795369850</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>30826629189</v>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>29100048410</v>
+      </c>
+      <c r="H120" s="4" t="n">
+        <v>64702641159</v>
+      </c>
+      <c r="I120" s="4" t="n">
         <v>94707660034</v>
-      </c>
-      <c r="C120" s="4" t="n">
-        <v>64702641159</v>
-      </c>
-      <c r="D120" s="4" t="n">
-        <v>29100048410</v>
-      </c>
-      <c r="E120" s="4" t="n">
-        <v>30826629189</v>
       </c>
     </row>
     <row r="121">
@@ -2859,6 +4271,18 @@
       <c r="E121" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F121" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -2878,6 +4302,18 @@
       <c r="E122" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -2895,6 +4331,18 @@
         <v>0</v>
       </c>
       <c r="E123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2909,14 +4357,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2927,22 +4379,42 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -2953,16 +4425,28 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>14678799605798</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>17144251446632</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>17681913026177</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>19735646137250</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>34211128942240</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>33481608954953</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>38232401184050</v>
+      </c>
+      <c r="I2" s="4" t="n">
         <v>35410589612616</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>38232401184050</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>33481608954953</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>34211128942240</v>
       </c>
     </row>
     <row r="3">
@@ -2972,16 +4456,28 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>-107663860948</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>-143570366109</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>-171124375178</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>-188587772416</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>-334674383087</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>-344679758524</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>-409564012665</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>-434546683224</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>-409564012665</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>-344679758524</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>-334674383087</v>
       </c>
     </row>
     <row r="4">
@@ -2991,16 +4487,28 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>14571135744850</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>17000681080523</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>17510788650999</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>19547058364834</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>33876454559153</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>33136929196429</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>37822837171385</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>34976042929392</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>37822837171385</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>33136929196429</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>33876454559153</v>
       </c>
     </row>
     <row r="5">
@@ -3010,16 +4518,28 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-11792052183391</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-13539967588262</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-14076055770112</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>-15948760134458</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>-27949348024381</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>-27078338249235</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>-31149334531193</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>-27292194621378</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-31149334531193</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-27078338249235</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-27949348024381</v>
       </c>
     </row>
     <row r="6">
@@ -3029,16 +4549,28 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>2779083561459</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>3460713492261</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>3434732880887</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>3598298230376</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>5927106534772</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>6058590947194</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>6673502640192</v>
+      </c>
+      <c r="I6" s="4" t="n">
         <v>7683848308014</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>6673502640192</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>6058590947194</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>5927106534772</v>
       </c>
     </row>
     <row r="7">
@@ -3048,16 +4580,28 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>6846027091</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>16820020734</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>2368958316</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>16326114795</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>54036974170</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>97825547538</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>75567438524</v>
+      </c>
+      <c r="I7" s="4" t="n">
         <v>136303226388</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>75567438524</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>97825547538</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>54036974170</v>
       </c>
     </row>
     <row r="8">
@@ -3067,16 +4611,28 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>-66345864211</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>-133678118497</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>-161541087492</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>-118252734395</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>-141471203463</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>-142580680640</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>-93616780951</v>
+      </c>
+      <c r="I8" s="4" t="n">
         <v>-153168770819</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>-93616780951</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>-142580680640</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>-141471203463</v>
       </c>
     </row>
     <row r="9">
@@ -3086,16 +4642,28 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>-61109039390</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>-115367610418</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>-154416694276</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>-104380274160</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>-94143431408</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>-118568804103</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>-46775305829</v>
+      </c>
+      <c r="I9" s="4" t="n">
         <v>-119082599327</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>-46775305829</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>-118568804103</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>-94143431408</v>
       </c>
     </row>
     <row r="10">
@@ -3105,16 +4673,28 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>-1170069069426</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>-1361807553507</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>-1420855653447</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>-1687654952494</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>-2828208644376</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>-2835769469802</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>-3207574691174</v>
+      </c>
+      <c r="I10" s="4" t="n">
         <v>-3322701974507</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>-3207574691174</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>-2835769469802</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>-2828208644376</v>
       </c>
     </row>
     <row r="11">
@@ -3124,16 +4704,28 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>-345868153940</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>-475831697930</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>-505572794605</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>-501819303928</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-673996996684</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>-693934934718</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>-795749355922</v>
+      </c>
+      <c r="I11" s="4" t="n">
         <v>-824395851865</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>-795749355922</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>-693934934718</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>-673996996684</v>
       </c>
     </row>
     <row r="12">
@@ -3143,16 +4735,28 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>1203646500973</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1506216143061</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>1349132303659</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>1306897354354</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>2337466664419</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>2484131409572</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>2652129250669</v>
+      </c>
+      <c r="I12" s="4" t="n">
         <v>3519884937211</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>2652129250669</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>2484131409572</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>2337466664419</v>
       </c>
     </row>
     <row r="13">
@@ -3162,16 +4766,28 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>4637809502</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>4760923089</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>5485848150</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>8861354013</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>8582642521</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>11846230257</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>10013781125</v>
+      </c>
+      <c r="I13" s="4" t="n">
         <v>41188910080</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>10013781125</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>11846230257</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>8582642521</v>
       </c>
     </row>
     <row r="14">
@@ -3181,16 +4797,28 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>-2734037354</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-4264680599</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>-8637683094</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>-36528186336</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>-33721752227</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>-7217637455</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>-11130582486</v>
+      </c>
+      <c r="I14" s="4" t="n">
         <v>-13234356500</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>-11130582486</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>-7217637455</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>-33721752227</v>
       </c>
     </row>
     <row r="15">
@@ -3200,16 +4828,28 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>1903772148</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>496242490</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-3151834944</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>-27666832323</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>-25139109706</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>4628592802</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>-1116801361</v>
+      </c>
+      <c r="I15" s="4" t="n">
         <v>27954553580</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-1116801361</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>4628592802</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-25139109706</v>
       </c>
     </row>
     <row r="16">
@@ -3230,6 +4870,18 @@
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3238,16 +4890,28 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>1205550273121</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>1506712385551</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>1345980468715</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>1279230522031</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>2312327554713</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>2488760002374</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>2651012449308</v>
+      </c>
+      <c r="I17" s="4" t="n">
         <v>3547839490791</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>2651012449308</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>2488760002374</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>2312327554713</v>
       </c>
     </row>
     <row r="18">
@@ -3257,16 +4921,28 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>-249485408708</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-315667183537</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-279422477414</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>-259673455974</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>-521061271124</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>-517592806160</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>-615476890636</v>
+      </c>
+      <c r="I18" s="4" t="n">
         <v>-849656975908</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-615476890636</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-517592806160</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-521061271124</v>
       </c>
     </row>
     <row r="19">
@@ -3276,16 +4952,28 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>3858482734</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>2879755229</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>2752113960</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>9485099588</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>19425559808</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>-68019079</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>77380724274</v>
+      </c>
+      <c r="I19" s="4" t="n">
         <v>130314948007</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>77380724274</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>-68019079</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>19425559808</v>
       </c>
     </row>
     <row r="20">
@@ -3295,16 +4983,28 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>-245626925974</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-312787428308</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-276670363454</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>-250188356386</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>-501635711316</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>-517660825239</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>-538096166362</v>
+      </c>
+      <c r="I20" s="4" t="n">
         <v>-719342027901</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-538096166362</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-517660825239</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-501635711316</v>
       </c>
     </row>
     <row r="21">
@@ -3314,16 +5014,28 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>959923347147</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1193924957243</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>1069310105261</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>1029042165645</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>1810691843397</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>1971099177135</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>2112916282946</v>
+      </c>
+      <c r="I21" s="4" t="n">
         <v>2828497462890</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>2112916282946</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>1971099177135</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>1810691843397</v>
       </c>
     </row>
     <row r="22">
@@ -3344,6 +5056,18 @@
       <c r="E22" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -3352,16 +5076,28 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>959923347147</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>1193924957243</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>1069310105261</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>1029042165645</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>1810691843397</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>1971099177135</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>2112916282946</v>
+      </c>
+      <c r="I23" s="4" t="n">
         <v>2828497462890</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>2112916282946</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>1971099177135</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>1810691843397</v>
       </c>
     </row>
     <row r="24">
@@ -3371,16 +5107,28 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>6481</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>4896</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>4308</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>4197</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>5350</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>5436</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>5713</v>
+      </c>
+      <c r="I24" s="4" t="n">
         <v>7652</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>5713</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>5436</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>5350</v>
       </c>
     </row>
     <row r="25">
@@ -3390,16 +5138,28 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>4896</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>4308</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>4197</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>5436</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>5713</v>
+      </c>
+      <c r="I25" s="4" t="n">
         <v>7652</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>5713</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>5436</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3418,6 +5178,18 @@
         <v>0</v>
       </c>
       <c r="E26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3432,14 +5204,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3450,22 +5226,42 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -3476,16 +5272,28 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>1205550273121</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>1506712385551</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>1345980468715</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>1279230522031</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>2312327554713</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>2488760002374</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>2651012449308</v>
+      </c>
+      <c r="I2" s="4" t="n">
         <v>3547839490791</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>2651012449308</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>2488760002374</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>2312327554713</v>
       </c>
     </row>
     <row r="3">
@@ -3495,16 +5303,28 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>42101648087</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>61066130585</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>72154867041</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>75118429219</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>79516376971</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>81257091304</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>80821846271</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>85291458403</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>80821846271</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>81257091304</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>79516376971</v>
       </c>
     </row>
     <row r="4">
@@ -3514,16 +5334,28 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>-3414537000</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>6391807846</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>64942006080</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>2868205863</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>2374779451</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>77722354056</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>-7695240894</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>77722354056</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>2374779451</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>2868205863</v>
       </c>
     </row>
     <row r="5">
@@ -3533,16 +5365,28 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-169041343</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-1242529054</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>177425063</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>2504365377</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>-8239903282</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>-1611805757</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>140360327</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>-2434348570</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>140360327</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-1611805757</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-8239903282</v>
       </c>
     </row>
     <row r="6">
@@ -3563,6 +5407,18 @@
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -3571,16 +5427,28 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>-7406944577</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>-1456968019</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1237319162</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>-3225478644</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>-21327686776</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>-79561268312</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>-47046699012</v>
+      </c>
+      <c r="I7" s="4" t="n">
         <v>-110244947701</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-47046699012</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-79561268312</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-21327686776</v>
       </c>
     </row>
     <row r="8">
@@ -3590,16 +5458,28 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>61109042390</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>115367610418</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>154416694276</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>104380274160</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>94421152974</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>118568804103</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>46775305829</v>
+      </c>
+      <c r="I8" s="4" t="n">
         <v>119082599327</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>46775305829</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>118568804103</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>94421152974</v>
       </c>
     </row>
     <row r="9">
@@ -3620,6 +5500,18 @@
       <c r="E9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -3628,16 +5520,28 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>1301184977678</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1677032092481</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1580358582103</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>1522950118223</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>2459565700463</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>2609787603163</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>2809425616779</v>
+      </c>
+      <c r="I10" s="4" t="n">
         <v>3631839011356</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>2809425616779</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>2609787603163</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>2459565700463</v>
       </c>
     </row>
     <row r="11">
@@ -3647,16 +5551,28 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>-86037746014</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>12888586942</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>17322807863</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>-23111709097</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-52151674870</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>39100711762</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>-261742771385</v>
+      </c>
+      <c r="I11" s="4" t="n">
         <v>235691148778</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>-261742771385</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>39100711762</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>-52151674870</v>
       </c>
     </row>
     <row r="12">
@@ -3666,16 +5582,28 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>-1566186716366</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-2062274428226</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>484514384160</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>-2208835725303</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>-1753323314557</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>-436683979881</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>-2129837921117</v>
+      </c>
+      <c r="I12" s="4" t="n">
         <v>-2806722790389</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>-2129837921117</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-436683979881</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>-1753323314557</v>
       </c>
     </row>
     <row r="13">
@@ -3685,16 +5613,28 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>412203203546</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>199226464534</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>-99651505808</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>354804359041</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>76506711125</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>92449328770</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>273559805376</v>
+      </c>
+      <c r="I13" s="4" t="n">
         <v>-369026498161</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>273559805376</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>92449328770</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>76506711125</v>
       </c>
     </row>
     <row r="14">
@@ -3704,16 +5644,28 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>-44784289702</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-62082212310</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>-42462273125</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>14254564032</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>-59503878567</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>-103556391934</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>13981231920</v>
+      </c>
+      <c r="I14" s="4" t="n">
         <v>169889358691</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>13981231920</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>-103556391934</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>-59503878567</v>
       </c>
     </row>
     <row r="15">
@@ -3723,16 +5675,28 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-60443657529</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-114016876155</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-155543069575</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>-105200568547</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>-90657750651</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>-122841644646</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>-46067825009</v>
+      </c>
+      <c r="I15" s="4" t="n">
         <v>-117889071318</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-46067825009</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-122841644646</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-90657750651</v>
       </c>
     </row>
     <row r="16">
@@ -3742,16 +5706,28 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>-231958086112</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>-291572199831</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>-253134374354</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>-234058441077</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>-464338080937</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>-466349274224</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>-555484436785</v>
+      </c>
+      <c r="I16" s="4" t="n">
         <v>-607285010641</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>-555484436785</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>-466349274224</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>-464338080937</v>
       </c>
     </row>
     <row r="17">
@@ -3772,6 +5748,18 @@
       <c r="E17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3780,16 +5768,28 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>-26117591079</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-20293123341</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-34492822139</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>-43169828785</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>-15516505310</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>-104164881917</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>-20648525024</v>
+      </c>
+      <c r="I18" s="4" t="n">
         <v>-19687607067</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-20648525024</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-104164881917</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-15516505310</v>
       </c>
     </row>
     <row r="19">
@@ -3799,16 +5799,28 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>-302139905578</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>-661091695906</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>1496911729125</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>-722367231513</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>100581206696</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>1507741471093</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>83185174755</v>
+      </c>
+      <c r="I19" s="4" t="n">
         <v>18890403841</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>83185174755</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>1507741471093</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>100581206696</v>
       </c>
     </row>
     <row r="20">
@@ -3818,16 +5830,28 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>-336378415370</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-223765922597</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-85433646180</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>-61304197645</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>-52384601566</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>-83115434103</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>-90406299690</v>
+      </c>
+      <c r="I20" s="4" t="n">
         <v>-115542827250</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-90406299690</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-83115434103</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-52384601566</v>
       </c>
     </row>
     <row r="21">
@@ -3837,16 +5861,28 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>1075665048</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1774979478</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>792669960</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>12869426085</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>1498185785</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>2289295529</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>3181818</v>
+      </c>
+      <c r="I21" s="4" t="n">
         <v>3636364</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>3181818</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>2289295529</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>1498185785</v>
       </c>
     </row>
     <row r="22">
@@ -3856,16 +5892,28 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>-540000000000</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>-2240100000000</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>-1120070000000</v>
+      </c>
+      <c r="I22" s="4" t="n">
         <v>-4067400000000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>-1120070000000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>-2240100000000</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>-540000000000</v>
       </c>
     </row>
     <row r="23">
@@ -3875,16 +5923,28 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>160065000000</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>200000000000</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>1680000000000</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>960000000000</v>
+      </c>
+      <c r="I23" s="4" t="n">
         <v>3210000000000</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>960000000000</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>1680000000000</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>200000000000</v>
       </c>
     </row>
     <row r="24">
@@ -3894,16 +5954,28 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>-3980000000</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4" t="n">
         <v>-1950000000</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>-3980000000</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3924,6 +5996,18 @@
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -3932,16 +6016,28 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
+        <v>6331279529</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>163983543</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>251771651</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>267480935</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>20219137155</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>66432820820</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>39436141188</v>
+      </c>
+      <c r="I26" s="4" t="n">
         <v>81101160826</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>39436141188</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>66432820820</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>20219137155</v>
       </c>
     </row>
     <row r="27">
@@ -3951,16 +6047,28 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
+        <v>-168906470793</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>-221826959576</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>-84389204569</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>-48167290625</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>-370667278626</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>-578473317754</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>-211036976684</v>
+      </c>
+      <c r="I27" s="4" t="n">
         <v>-893788030060</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>-211036976684</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>-578473317754</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>-370667278626</v>
       </c>
     </row>
     <row r="28">
@@ -3970,16 +6078,28 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
+        <v>97273160000</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>68932500000</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>46375540000</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>1447231530000</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>67243920000</v>
+      </c>
+      <c r="I28" s="4" t="n">
         <v>64823800000</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>67243920000</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>1447231530000</v>
       </c>
     </row>
     <row r="29">
@@ -3992,12 +6112,24 @@
         <v>0</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0</v>
+        <v>-2094000000</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0</v>
+        <v>-1283000000</v>
       </c>
       <c r="E29" s="4" t="n">
+        <v>-1524800000</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4008,16 +6140,28 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>4320772043080</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>5435682129077</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>7432783338336</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>7758858344889</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>6261254967206</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>8159472964689</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>6788859495016</v>
+      </c>
+      <c r="I30" s="4" t="n">
         <v>9817871495359</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>6788859495016</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>8159472964689</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>6261254967206</v>
       </c>
     </row>
     <row r="31">
@@ -4027,16 +6171,28 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>-3647003259254</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>-4387362004881</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>-8208110896493</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>-6876202707810</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>-6300139792578</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>-8458230585768</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>-5831605732949</v>
+      </c>
+      <c r="I31" s="4" t="n">
         <v>-8936027876466</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>-5831605732949</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>-8458230585768</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>-6300139792578</v>
       </c>
     </row>
     <row r="32">
@@ -4057,6 +6213,18 @@
       <c r="E32" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -4065,16 +6233,28 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>-268371812300</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>-343875424770</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>-355099739283</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>-177376257045</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>-616671158340</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>-615443389700</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>-671681829760</v>
+      </c>
+      <c r="I33" s="4" t="n">
         <v>-673692457830</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>-671681829760</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>-615443389700</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>-616671158340</v>
       </c>
     </row>
     <row r="34">
@@ -4095,6 +6275,18 @@
       <c r="E34" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -4103,16 +6295,28 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
+        <v>502670131526</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>771283199426</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>-1085334757440</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>703754580034</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>791675546288</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>-914201010779</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>352815852307</v>
+      </c>
+      <c r="I35" s="4" t="n">
         <v>272974961063</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>352815852307</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>-914201010779</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>791675546288</v>
       </c>
     </row>
     <row r="36">
@@ -4122,16 +6326,28 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
+        <v>31623755155</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>-111635456056</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>327187767116</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>-66779942104</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>521589474358</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>15067142560</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>224964050378</v>
+      </c>
+      <c r="I36" s="4" t="n">
         <v>-601922665156</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>224964050378</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>15067142560</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>521589474358</v>
       </c>
     </row>
     <row r="37">
@@ -4141,16 +6357,28 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>175208552187</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>206721179629</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>95224439008</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>422234781061</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>355454838957</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>879548130711</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>896147917336</v>
+      </c>
+      <c r="I37" s="4" t="n">
         <v>1122712392130</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>896147917336</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>879548130711</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>355454838957</v>
       </c>
     </row>
     <row r="38">
@@ -4160,16 +6388,28 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
+        <v>-111127713</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>138715435</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>-177425063</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>2503817396</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>1532644065</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>1600424416</v>
+      </c>
+      <c r="I38" s="4" t="n">
         <v>1235530057</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>1600424416</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>1532644065</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>2503817396</v>
       </c>
     </row>
     <row r="39">
@@ -4179,16 +6419,28 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>206721179629</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>95224439008</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>422234781061</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>355454838957</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>879548130711</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>896147917336</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>1122712392130</v>
+      </c>
+      <c r="I39" s="4" t="n">
         <v>522025257031</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>1122712392130</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>896147917336</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>879548130711</v>
       </c>
     </row>
     <row r="40">
@@ -4209,6 +6461,18 @@
       <c r="E40" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -4228,6 +6492,18 @@
       <c r="E41" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -4236,16 +6512,28 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="4" t="n">
         <v>-97918137408</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/financials/PNJ/PNJ_financials.xlsx
+++ b/financials/PNJ/PNJ_financials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -151,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -178,10 +178,28 @@
     <xf numFmtId="166" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -6547,15 +6565,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -6565,59 +6587,151 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Khối "CHỈ SỐ TÀI CHÍNH" tính bằng công thức từ khối "DỮ LIỆU TRÍCH XUẤT" bên dưới, không phải số nhập tay. Khối "DỮ LIỆU TRÍCH XUẤT" được dò tự động theo TÊN khoản mục (đúng theo tên gốc trong báo cáo) và theo NĂM từ 3 sheet balance_sheet / income_statement — không tham chiếu ô cố định. Có thể sửa nhãn khoản mục ở cột A khối này nếu công ty đổi tên dòng; công thức sẽ tự dò lại. Các năm được xếp tăng dần từ trái sang phải.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>I. CHỈ SỐ TÀI CHÍNH</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="19" t="n"/>
+      <c r="I2" s="19" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Chỉ tiêu</t>
+        </is>
+      </c>
+      <c r="B3" s="10">
+        <f>'balance_sheet'!B1</f>
+        <v/>
+      </c>
+      <c r="C3" s="10">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="D3" s="10">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="E3" s="10">
+        <f>'balance_sheet'!E1</f>
+        <v/>
+      </c>
+      <c r="F3" s="10">
+        <f>'balance_sheet'!F1</f>
+        <v/>
+      </c>
+      <c r="G3" s="10">
+        <f>'balance_sheet'!G1</f>
+        <v/>
+      </c>
+      <c r="H3" s="10">
+        <f>'balance_sheet'!H1</f>
+        <v/>
+      </c>
+      <c r="I3" s="10">
+        <f>'balance_sheet'!I1</f>
+        <v/>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>I. CHỈ SỐ TÀI CHÍNH</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>1. Khả năng sinh lời</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Chỉ tiêu</t>
-        </is>
-      </c>
-      <c r="B5" s="10">
-        <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="C5" s="10">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="D5" s="10">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="E5" s="10">
-        <f>'balance_sheet'!B1</f>
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C5" s="14">
+        <f>IFERROR(C$47/((C$32+B$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D5" s="14">
+        <f>IFERROR(D$47/((D$32+C$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E5" s="14">
+        <f>IFERROR(E$47/((E$32+D$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F5" s="14">
+        <f>IFERROR(F$47/((F$32+E$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G5" s="14">
+        <f>IFERROR(G$47/((G$32+F$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H5" s="14">
+        <f>IFERROR(H$47/((H$32+G$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I5" s="14">
+        <f>IFERROR(I$47/((I$32+H$32)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>1. Khả năng sinh lời</t>
-        </is>
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>ROA (LNST / Tổng tài sản bình quân)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C6" s="14">
+        <f>IFERROR(C$46/((C$33+B$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D6" s="14">
+        <f>IFERROR(D$46/((D$33+C$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E6" s="14">
+        <f>IFERROR(E$46/((E$33+D$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F6" s="14">
+        <f>IFERROR(F$46/((F$33+E$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G6" s="14">
+        <f>IFERROR(G$46/((G$33+F$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H6" s="14">
+        <f>IFERROR(H$46/((H$33+G$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I6" s="14">
+        <f>IFERROR(I$46/((I$33+H$33)/2),"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
+          <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -6626,22 +6740,38 @@
         </is>
       </c>
       <c r="C7" s="14">
-        <f>IFERROR(C$54/((C$39+B$39)/2),"n/a")</f>
+        <f>IFERROR((C$47-B$47)/ABS(B$47),"n/a")</f>
         <v/>
       </c>
       <c r="D7" s="14">
-        <f>IFERROR(D$54/((D$39+C$39)/2),"n/a")</f>
+        <f>IFERROR((D$47-C$47)/ABS(C$47),"n/a")</f>
         <v/>
       </c>
       <c r="E7" s="14">
-        <f>IFERROR(E$54/((E$39+D$39)/2),"n/a")</f>
+        <f>IFERROR((E$47-D$47)/ABS(D$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F7" s="14">
+        <f>IFERROR((F$47-E$47)/ABS(E$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G7" s="14">
+        <f>IFERROR((G$47-F$47)/ABS(F$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H7" s="14">
+        <f>IFERROR((H$47-G$47)/ABS(G$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I7" s="14">
+        <f>IFERROR((I$47-H$47)/ABS(H$47),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>ROA (LNST / Tổng tài sản bình quân)</t>
+          <t>Tăng trưởng Doanh thu thuần</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -6650,954 +6780,1568 @@
         </is>
       </c>
       <c r="C8" s="14">
-        <f>IFERROR(C$53/((C$40+B$40)/2),"n/a")</f>
+        <f>IFERROR((C$39-B$39)/ABS(B$39),"n/a")</f>
         <v/>
       </c>
       <c r="D8" s="14">
-        <f>IFERROR(D$53/((D$40+C$40)/2),"n/a")</f>
+        <f>IFERROR((D$39-C$39)/ABS(C$39),"n/a")</f>
         <v/>
       </c>
       <c r="E8" s="14">
-        <f>IFERROR(E$53/((E$40+D$40)/2),"n/a")</f>
+        <f>IFERROR((E$39-D$39)/ABS(D$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F8" s="14">
+        <f>IFERROR((F$39-E$39)/ABS(E$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G8" s="14">
+        <f>IFERROR((G$39-F$39)/ABS(F$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H8" s="14">
+        <f>IFERROR((H$39-G$39)/ABS(G$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I8" s="14">
+        <f>IFERROR((I$39-H$39)/ABS(H$39),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C9" s="14">
-        <f>IFERROR((C$54-B$54)/ABS(B$54),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D9" s="14">
-        <f>IFERROR((D$54-C$54)/ABS(C$54),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E9" s="14">
-        <f>IFERROR((E$54-D$54)/ABS(D$54),"n/a")</f>
-        <v/>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>2. Biên lợi nhuận</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Tăng trưởng Doanh thu thuần</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+          <t>Biên lợi nhuận gộp</t>
+        </is>
+      </c>
+      <c r="B10" s="14">
+        <f>IFERROR(B$41/B$39,"n/a")</f>
+        <v/>
       </c>
       <c r="C10" s="14">
-        <f>IFERROR((C$46-B$46)/ABS(B$46),"n/a")</f>
+        <f>IFERROR(C$41/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>IFERROR((D$46-C$46)/ABS(C$46),"n/a")</f>
+        <f>IFERROR(D$41/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E10" s="14">
-        <f>IFERROR((E$46-D$46)/ABS(D$46),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11"/>
+        <f>IFERROR(E$41/E$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F10" s="14">
+        <f>IFERROR(F$41/F$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G10" s="14">
+        <f>IFERROR(G$41/G$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H10" s="14">
+        <f>IFERROR(H$41/H$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I10" s="14">
+        <f>IFERROR(I$41/I$39,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Biên lợi nhuận ròng</t>
+        </is>
+      </c>
+      <c r="B11" s="14">
+        <f>IFERROR(B$46/B$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C11" s="14">
+        <f>IFERROR(C$46/C$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D11" s="14">
+        <f>IFERROR(D$46/D$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E11" s="14">
+        <f>IFERROR(E$46/E$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F11" s="14">
+        <f>IFERROR(F$46/F$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G11" s="14">
+        <f>IFERROR(G$46/G$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H11" s="14">
+        <f>IFERROR(H$46/H$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I11" s="14">
+        <f>IFERROR(I$46/I$39,"n/a")</f>
+        <v/>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>2. Biên lợi nhuận</t>
+          <t>3. Đòn bẩy tài chính</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Biên lợi nhuận gộp</t>
-        </is>
-      </c>
-      <c r="B13" s="14">
-        <f>IFERROR(B$48/B$46,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C13" s="14">
-        <f>IFERROR(C$48/C$46,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D13" s="14">
-        <f>IFERROR(D$48/D$46,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E13" s="14">
-        <f>IFERROR(E$48/E$46,"n/a")</f>
+          <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
+        </is>
+      </c>
+      <c r="B13" s="15">
+        <f>IFERROR((B$37+B$38)/B$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C13" s="15">
+        <f>IFERROR((C$37+C$38)/C$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D13" s="15">
+        <f>IFERROR((D$37+D$38)/D$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E13" s="15">
+        <f>IFERROR((E$37+E$38)/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F13" s="15">
+        <f>IFERROR((F$37+F$38)/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G13" s="15">
+        <f>IFERROR((G$37+G$38)/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H13" s="15">
+        <f>IFERROR((H$37+H$38)/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I13" s="15">
+        <f>IFERROR((I$37+I$38)/I$32,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Biên lợi nhuận ròng</t>
-        </is>
-      </c>
-      <c r="B14" s="14">
-        <f>IFERROR(B$53/B$46,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C14" s="14">
-        <f>IFERROR(C$53/C$46,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D14" s="14">
-        <f>IFERROR(D$53/D$46,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E14" s="14">
-        <f>IFERROR(E$53/E$46,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B14" s="15">
+        <f>IFERROR(B$38/B$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C14" s="15">
+        <f>IFERROR(C$38/C$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D14" s="15">
+        <f>IFERROR(D$38/D$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E14" s="15">
+        <f>IFERROR(E$38/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F14" s="15">
+        <f>IFERROR(F$38/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G14" s="15">
+        <f>IFERROR(G$38/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H14" s="15">
+        <f>IFERROR(H$38/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I14" s="15">
+        <f>IFERROR(I$38/I$32,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B15" s="15">
+        <f>IFERROR(B$37/B$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C15" s="15">
+        <f>IFERROR(C$37/C$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D15" s="15">
+        <f>IFERROR(D$37/D$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E15" s="15">
+        <f>IFERROR(E$37/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F15" s="15">
+        <f>IFERROR(F$37/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G15" s="15">
+        <f>IFERROR(G$37/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H15" s="15">
+        <f>IFERROR(H$37/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I15" s="15">
+        <f>IFERROR(I$37/I$32,"n/a")</f>
+        <v/>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>3. Đòn bẩy tài chính</t>
-        </is>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Nợ phải trả/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B16" s="15">
+        <f>IFERROR(B$34/B$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C16" s="15">
+        <f>IFERROR(C$34/C$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D16" s="15">
+        <f>IFERROR(D$34/D$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E16" s="15">
+        <f>IFERROR(E$34/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F16" s="15">
+        <f>IFERROR(F$34/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G16" s="15">
+        <f>IFERROR(G$34/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H16" s="15">
+        <f>IFERROR(H$34/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I16" s="15">
+        <f>IFERROR(I$34/I$32,"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
       <c r="B17" s="15">
-        <f>IFERROR((B$44+B$45)/B$39,"n/a")</f>
+        <f>IFERROR(B$36/B$32,"n/a")</f>
         <v/>
       </c>
       <c r="C17" s="15">
-        <f>IFERROR((C$44+C$45)/C$39,"n/a")</f>
+        <f>IFERROR(C$36/C$32,"n/a")</f>
         <v/>
       </c>
       <c r="D17" s="15">
-        <f>IFERROR((D$44+D$45)/D$39,"n/a")</f>
+        <f>IFERROR(D$36/D$32,"n/a")</f>
         <v/>
       </c>
       <c r="E17" s="15">
-        <f>IFERROR((E$44+E$45)/E$39,"n/a")</f>
+        <f>IFERROR(E$36/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F17" s="15">
+        <f>IFERROR(F$36/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G17" s="15">
+        <f>IFERROR(G$36/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H17" s="15">
+        <f>IFERROR(H$36/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I17" s="15">
+        <f>IFERROR(I$36/I$32,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
+          <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
       <c r="B18" s="15">
-        <f>IFERROR(B$45/B$39,"n/a")</f>
+        <f>IFERROR(B$35/B$32,"n/a")</f>
         <v/>
       </c>
       <c r="C18" s="15">
-        <f>IFERROR(C$45/C$39,"n/a")</f>
+        <f>IFERROR(C$35/C$32,"n/a")</f>
         <v/>
       </c>
       <c r="D18" s="15">
-        <f>IFERROR(D$45/D$39,"n/a")</f>
+        <f>IFERROR(D$35/D$32,"n/a")</f>
         <v/>
       </c>
       <c r="E18" s="15">
-        <f>IFERROR(E$45/E$39,"n/a")</f>
+        <f>IFERROR(E$35/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F18" s="15">
+        <f>IFERROR(F$35/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G18" s="15">
+        <f>IFERROR(G$35/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H18" s="15">
+        <f>IFERROR(H$35/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I18" s="15">
+        <f>IFERROR(I$35/I$32,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B19" s="15">
-        <f>IFERROR(B$44/B$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C19" s="15">
-        <f>IFERROR(C$44/C$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D19" s="15">
-        <f>IFERROR(D$44/D$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E19" s="15">
-        <f>IFERROR(E$44/E$39,"n/a")</f>
-        <v/>
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>4. Chi phí &amp; khả năng trả lãi</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Nợ phải trả/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B20" s="15">
-        <f>IFERROR(B$41/B$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C20" s="15">
-        <f>IFERROR(C$41/C$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D20" s="15">
-        <f>IFERROR(D$41/D$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E20" s="15">
-        <f>IFERROR(E$41/E$39,"n/a")</f>
+          <t>Chi phí bán hàng, quản lý/LN gộp</t>
+        </is>
+      </c>
+      <c r="B20" s="14">
+        <f>IFERROR((ABS(B$42)+ABS(B$43))/B$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C20" s="14">
+        <f>IFERROR((ABS(C$42)+ABS(C$43))/C$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D20" s="14">
+        <f>IFERROR((ABS(D$42)+ABS(D$43))/D$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E20" s="14">
+        <f>IFERROR((ABS(E$42)+ABS(E$43))/E$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F20" s="14">
+        <f>IFERROR((ABS(F$42)+ABS(F$43))/F$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G20" s="14">
+        <f>IFERROR((ABS(G$42)+ABS(G$43))/G$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H20" s="14">
+        <f>IFERROR((ABS(H$42)+ABS(H$43))/H$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I20" s="14">
+        <f>IFERROR((ABS(I$42)+ABS(I$43))/I$41,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B21" s="15">
-        <f>IFERROR(B$43/B$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C21" s="15">
-        <f>IFERROR(C$43/C$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D21" s="15">
-        <f>IFERROR(D$43/D$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E21" s="15">
-        <f>IFERROR(E$43/E$39,"n/a")</f>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
+        </is>
+      </c>
+      <c r="B21" s="14">
+        <f>IFERROR(ABS(B$45)/B$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C21" s="14">
+        <f>IFERROR(ABS(C$45)/C$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D21" s="14">
+        <f>IFERROR(ABS(D$45)/D$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E21" s="14">
+        <f>IFERROR(ABS(E$45)/E$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F21" s="14">
+        <f>IFERROR(ABS(F$45)/F$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G21" s="14">
+        <f>IFERROR(ABS(G$45)/G$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H21" s="14">
+        <f>IFERROR(ABS(H$45)/H$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I21" s="14">
+        <f>IFERROR(ABS(I$45)/I$44,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B22" s="15">
-        <f>IFERROR(B$42/B$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C22" s="15">
-        <f>IFERROR(C$42/C$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D22" s="15">
-        <f>IFERROR(D$42/D$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E22" s="15">
-        <f>IFERROR(E$42/E$39,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23"/>
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>5. Chu kỳ hoạt động vốn lưu động</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Số ngày phải trả (DPO)</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C23" s="16">
+        <f>IFERROR(((C$49+B$49)/2)/ABS(C$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D23" s="16">
+        <f>IFERROR(((D$49+C$49)/2)/ABS(D$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E23" s="16">
+        <f>IFERROR(((E$49+D$49)/2)/ABS(E$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F23" s="16">
+        <f>IFERROR(((F$49+E$49)/2)/ABS(F$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G23" s="16">
+        <f>IFERROR(((G$49+F$49)/2)/ABS(G$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H23" s="16">
+        <f>IFERROR(((H$49+G$49)/2)/ABS(H$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I23" s="16">
+        <f>IFERROR(((I$49+H$49)/2)/ABS(I$40)*365,"n/a")</f>
+        <v/>
+      </c>
+    </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>4. Chi phí &amp; khả năng trả lãi</t>
-        </is>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Số ngày phải thu (DSO)</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C24" s="16">
+        <f>IFERROR(((C$48+B$48)/2)/C$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D24" s="16">
+        <f>IFERROR(((D$48+C$48)/2)/D$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E24" s="16">
+        <f>IFERROR(((E$48+D$48)/2)/E$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F24" s="16">
+        <f>IFERROR(((F$48+E$48)/2)/F$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G24" s="16">
+        <f>IFERROR(((G$48+F$48)/2)/G$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H24" s="16">
+        <f>IFERROR(((H$48+G$48)/2)/H$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I24" s="16">
+        <f>IFERROR(((I$48+H$48)/2)/I$39*365,"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Chi phí bán hàng, quản lý/LN gộp</t>
-        </is>
-      </c>
-      <c r="B25" s="14">
-        <f>IFERROR((ABS(B$49)+ABS(B$50))/B$48,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C25" s="14">
-        <f>IFERROR((ABS(C$49)+ABS(C$50))/C$48,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D25" s="14">
-        <f>IFERROR((ABS(D$49)+ABS(D$50))/D$48,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E25" s="14">
-        <f>IFERROR((ABS(E$49)+ABS(E$50))/E$48,"n/a")</f>
+          <t>Số ngày tồn kho (DIO)</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C25" s="16">
+        <f>IFERROR(((C$50+B$50)/2)/ABS(C$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D25" s="16">
+        <f>IFERROR(((D$50+C$50)/2)/ABS(D$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E25" s="16">
+        <f>IFERROR(((E$50+D$50)/2)/ABS(E$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F25" s="16">
+        <f>IFERROR(((F$50+E$50)/2)/ABS(F$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G25" s="16">
+        <f>IFERROR(((G$50+F$50)/2)/ABS(G$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H25" s="16">
+        <f>IFERROR(((H$50+G$50)/2)/ABS(H$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I25" s="16">
+        <f>IFERROR(((I$50+H$50)/2)/ABS(I$40)*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
-        </is>
-      </c>
-      <c r="B26" s="14">
-        <f>IFERROR(ABS(B$52)/B$51,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C26" s="14">
-        <f>IFERROR(ABS(C$52)/C$51,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D26" s="14">
-        <f>IFERROR(ABS(D$52)/D$51,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E26" s="14">
-        <f>IFERROR(ABS(E$52)/E$51,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27"/>
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>6. Cơ cấu tài sản</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Tiền và tương đương tiền/Tài sản</t>
+        </is>
+      </c>
+      <c r="B27" s="14">
+        <f>IFERROR(B$51/B$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C27" s="14">
+        <f>IFERROR(C$51/C$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D27" s="14">
+        <f>IFERROR(D$51/D$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E27" s="14">
+        <f>IFERROR(E$51/E$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F27" s="14">
+        <f>IFERROR(F$51/F$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G27" s="14">
+        <f>IFERROR(G$51/G$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H27" s="14">
+        <f>IFERROR(H$51/H$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I27" s="14">
+        <f>IFERROR(I$51/I$33,"n/a")</f>
+        <v/>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>5. Chu kỳ hoạt động vốn lưu động</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Số ngày phải trả (DPO)</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C29" s="16">
-        <f>IFERROR(((C$56+B$56)/2)/ABS(C$47)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D29" s="16">
-        <f>IFERROR(((D$56+C$56)/2)/ABS(D$47)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E29" s="16">
-        <f>IFERROR(((E$56+D$56)/2)/ABS(E$47)*365,"n/a")</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Hàng tồn kho/Tài sản</t>
+        </is>
+      </c>
+      <c r="B28" s="14">
+        <f>IFERROR(B$50/B$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C28" s="14">
+        <f>IFERROR(C$50/C$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D28" s="14">
+        <f>IFERROR(D$50/D$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E28" s="14">
+        <f>IFERROR(E$50/E$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F28" s="14">
+        <f>IFERROR(F$50/F$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G28" s="14">
+        <f>IFERROR(G$50/G$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H28" s="14">
+        <f>IFERROR(H$50/H$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I28" s="14">
+        <f>IFERROR(I$50/I$33,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Số ngày phải thu (DSO)</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C30" s="16">
-        <f>IFERROR(((C$55+B$55)/2)/C$46*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D30" s="16">
-        <f>IFERROR(((D$55+C$55)/2)/D$46*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E30" s="16">
-        <f>IFERROR(((E$55+D$55)/2)/E$46*365,"n/a")</f>
-        <v/>
-      </c>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="n"/>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="19" t="n"/>
+      <c r="G30" s="19" t="n"/>
+      <c r="H30" s="19" t="n"/>
+      <c r="I30" s="19" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>Số ngày tồn kho (DIO)</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C31" s="16">
-        <f>IFERROR(((C$57+B$57)/2)/ABS(C$47)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D31" s="16">
-        <f>IFERROR(((D$57+C$57)/2)/ABS(D$47)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E31" s="16">
-        <f>IFERROR(((E$57+D$57)/2)/ABS(E$47)*365,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32"/>
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Khoản mục</t>
+        </is>
+      </c>
+      <c r="B31" s="10">
+        <f>'balance_sheet'!B1</f>
+        <v/>
+      </c>
+      <c r="C31" s="10">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="D31" s="10">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="E31" s="10">
+        <f>'balance_sheet'!E1</f>
+        <v/>
+      </c>
+      <c r="F31" s="10">
+        <f>'balance_sheet'!F1</f>
+        <v/>
+      </c>
+      <c r="G31" s="10">
+        <f>'balance_sheet'!G1</f>
+        <v/>
+      </c>
+      <c r="H31" s="10">
+        <f>'balance_sheet'!H1</f>
+        <v/>
+      </c>
+      <c r="I31" s="10">
+        <f>'balance_sheet'!I1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B32" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>6. Cơ cấu tài sản</t>
-        </is>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG TÀI SẢN</t>
+        </is>
+      </c>
+      <c r="B33" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>Tiền và tương đương tiền/Tài sản</t>
-        </is>
-      </c>
-      <c r="B34" s="14">
-        <f>IFERROR(B$58/B$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C34" s="14">
-        <f>IFERROR(C$58/C$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D34" s="14">
-        <f>IFERROR(D$58/D$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E34" s="14">
-        <f>IFERROR(E$58/E$40,"n/a")</f>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>NỢ PHẢI TRẢ</t>
+        </is>
+      </c>
+      <c r="B34" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho/Tài sản</t>
-        </is>
-      </c>
-      <c r="B35" s="14">
-        <f>IFERROR(B$57/B$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C35" s="14">
-        <f>IFERROR(C$57/C$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D35" s="14">
-        <f>IFERROR(D$57/D$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E35" s="14">
-        <f>IFERROR(E$57/E$40,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36"/>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Nợ ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B35" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Nợ dài hạn</t>
+        </is>
+      </c>
+      <c r="B36" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Vay ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B37" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>Khoản mục</t>
-        </is>
-      </c>
-      <c r="B38" s="10">
-        <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="C38" s="10">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="D38" s="10">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="E38" s="10">
-        <f>'balance_sheet'!B1</f>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Vay dài hạn</t>
+        </is>
+      </c>
+      <c r="B38" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Vốn chủ sở hữu</t>
+          <t>Doanh thu thuần</t>
         </is>
       </c>
       <c r="B39" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C39" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D39" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E39" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TỔNG CỘNG TÀI SẢN</t>
+          <t>Giá vốn hàng bán</t>
         </is>
       </c>
       <c r="B40" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C40" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E40" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>NỢ PHẢI TRẢ</t>
+          <t>Lợi nhuận gộp</t>
         </is>
       </c>
       <c r="B41" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C41" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E41" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Nợ ngắn hạn</t>
+          <t>Chi phí bán hàng</t>
         </is>
       </c>
       <c r="B42" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C42" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D42" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E42" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Nợ dài hạn</t>
+          <t>Chi phí quản lý doanh nghiệp</t>
         </is>
       </c>
       <c r="B43" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C43" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D43" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E43" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Vay ngắn hạn</t>
+          <t>Lãi/(lỗ) từ hoạt động kinh doanh</t>
         </is>
       </c>
       <c r="B44" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C44" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D44" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E44" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I44" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Vay dài hạn</t>
+          <t>Chi phí lãi vay</t>
         </is>
       </c>
       <c r="B45" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C45" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D45" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E45" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I45" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Doanh thu thuần</t>
+          <t>Lãi/(lỗ) thuần sau thuế</t>
         </is>
       </c>
       <c r="B46" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C46" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D46" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E46" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Giá vốn hàng bán</t>
+          <t>Lợi nhuận của Cổ đông của Công ty mẹ</t>
         </is>
       </c>
       <c r="B47" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C47" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D47" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E47" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Lợi nhuận gộp</t>
+          <t>Phải thu khách hàng</t>
         </is>
       </c>
       <c r="B48" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C48" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D48" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E48" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F48" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I48" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Chi phí bán hàng</t>
+          <t>Phải trả người bán</t>
         </is>
       </c>
       <c r="B49" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C49" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D49" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E49" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I49" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Chi phí quản lý doanh nghiệp</t>
+          <t>Hàng tồn kho, ròng</t>
         </is>
       </c>
       <c r="B50" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C50" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D50" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E50" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I50" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Lãi/(lỗ) từ hoạt động kinh doanh</t>
+          <t>Tiền và tương đương tiền</t>
         </is>
       </c>
       <c r="B51" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C51" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D51" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E51" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Chi phí lãi vay</t>
-        </is>
-      </c>
-      <c r="B52" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C52" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D52" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E52" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Lãi/(lỗ) thuần sau thuế</t>
-        </is>
-      </c>
-      <c r="B53" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C53" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D53" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E53" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Lợi nhuận của Cổ đông của Công ty mẹ</t>
-        </is>
-      </c>
-      <c r="B54" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C54" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D54" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E54" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Phải thu khách hàng</t>
-        </is>
-      </c>
-      <c r="B55" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C55" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D55" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E55" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Phải trả người bán</t>
-        </is>
-      </c>
-      <c r="B56" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C56" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D56" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E56" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho, ròng</t>
-        </is>
-      </c>
-      <c r="B57" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C57" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D57" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E57" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Tiền và tương đương tiền</t>
-        </is>
-      </c>
-      <c r="B58" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C58" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D58" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E58" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I51" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
+  <conditionalFormatting sqref="B5:I5">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:I6">
+    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:I7">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8:I8">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10:I10">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:I11">
+    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13:I13">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="1">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="0">
+      <formula>0.3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:I16">
+    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="1">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="0">
+      <formula>0.3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21:I21">
+    <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="1">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="0">
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/financials/PNJ/PNJ_financials.xlsx
+++ b/financials/PNJ/PNJ_financials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
     <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;ngày&quot;"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,20 +53,7 @@
     </font>
     <font>
       <name val="Tahoma"/>
-      <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="2"/>
-      <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
@@ -151,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -162,44 +149,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00C6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -6588,353 +6554,353 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>I. CHỈ SỐ TÀI CHÍNH</t>
         </is>
       </c>
-      <c r="B2" s="19" t="n"/>
-      <c r="C2" s="19" t="n"/>
-      <c r="D2" s="19" t="n"/>
-      <c r="E2" s="19" t="n"/>
-      <c r="F2" s="19" t="n"/>
-      <c r="G2" s="19" t="n"/>
-      <c r="H2" s="19" t="n"/>
-      <c r="I2" s="19" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Chỉ tiêu</t>
         </is>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <f>'balance_sheet'!B1</f>
         <v/>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <f>'balance_sheet'!C1</f>
         <v/>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <f>'balance_sheet'!D1</f>
         <v/>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <f>'balance_sheet'!E1</f>
         <v/>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <f>'balance_sheet'!F1</f>
         <v/>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <f>'balance_sheet'!G1</f>
         <v/>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="9">
         <f>'balance_sheet'!H1</f>
         <v/>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="9">
         <f>'balance_sheet'!I1</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>1. Khả năng sinh lời</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="13">
         <f>IFERROR(C$47/((C$32+B$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <f>IFERROR(D$47/((D$32+C$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="13">
         <f>IFERROR(E$47/((E$32+D$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="13">
         <f>IFERROR(F$47/((F$32+E$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="13">
         <f>IFERROR(G$47/((G$32+F$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <f>IFERROR(H$47/((H$32+G$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <f>IFERROR(I$47/((I$32+H$32)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>ROA (LNST / Tổng tài sản bình quân)</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="13">
         <f>IFERROR(C$46/((C$33+B$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="13">
         <f>IFERROR(D$46/((D$33+C$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="13">
         <f>IFERROR(E$46/((E$33+D$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="13">
         <f>IFERROR(F$46/((F$33+E$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="13">
         <f>IFERROR(G$46/((G$33+F$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <f>IFERROR(H$46/((H$33+G$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
         <f>IFERROR(I$46/((I$33+H$33)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="13">
         <f>IFERROR((C$47-B$47)/ABS(B$47),"n/a")</f>
         <v/>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <f>IFERROR((D$47-C$47)/ABS(C$47),"n/a")</f>
         <v/>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="13">
         <f>IFERROR((E$47-D$47)/ABS(D$47),"n/a")</f>
         <v/>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="13">
         <f>IFERROR((F$47-E$47)/ABS(E$47),"n/a")</f>
         <v/>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="13">
         <f>IFERROR((G$47-F$47)/ABS(F$47),"n/a")</f>
         <v/>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <f>IFERROR((H$47-G$47)/ABS(G$47),"n/a")</f>
         <v/>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="13">
         <f>IFERROR((I$47-H$47)/ABS(H$47),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Tăng trưởng Doanh thu thuần</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="13">
         <f>IFERROR((C$39-B$39)/ABS(B$39),"n/a")</f>
         <v/>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="13">
         <f>IFERROR((D$39-C$39)/ABS(C$39),"n/a")</f>
         <v/>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="13">
         <f>IFERROR((E$39-D$39)/ABS(D$39),"n/a")</f>
         <v/>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="13">
         <f>IFERROR((F$39-E$39)/ABS(E$39),"n/a")</f>
         <v/>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="13">
         <f>IFERROR((G$39-F$39)/ABS(F$39),"n/a")</f>
         <v/>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <f>IFERROR((H$39-G$39)/ABS(G$39),"n/a")</f>
         <v/>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="13">
         <f>IFERROR((I$39-H$39)/ABS(H$39),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>2. Biên lợi nhuận</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Biên lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="13">
         <f>IFERROR(B$41/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="13">
         <f>IFERROR(C$41/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="13">
         <f>IFERROR(D$41/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="13">
         <f>IFERROR(E$41/E$39,"n/a")</f>
         <v/>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="13">
         <f>IFERROR(F$41/F$39,"n/a")</f>
         <v/>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="13">
         <f>IFERROR(G$41/G$39,"n/a")</f>
         <v/>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="13">
         <f>IFERROR(H$41/H$39,"n/a")</f>
         <v/>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="13">
         <f>IFERROR(I$41/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Biên lợi nhuận ròng</t>
         </is>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="13">
         <f>IFERROR(B$46/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="13">
         <f>IFERROR(C$46/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="13">
         <f>IFERROR(D$46/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="13">
         <f>IFERROR(E$46/E$39,"n/a")</f>
         <v/>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="13">
         <f>IFERROR(F$46/F$39,"n/a")</f>
         <v/>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="13">
         <f>IFERROR(G$46/G$39,"n/a")</f>
         <v/>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="13">
         <f>IFERROR(H$46/H$39,"n/a")</f>
         <v/>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="13">
         <f>IFERROR(I$46/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>3. Đòn bẩy tài chính</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
         </is>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="14">
         <f>IFERROR((B$37+B$38)/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="14">
         <f>IFERROR((C$37+C$38)/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="14">
         <f>IFERROR((D$37+D$38)/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="14">
         <f>IFERROR((E$37+E$38)/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="14">
         <f>IFERROR((F$37+F$38)/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="14">
         <f>IFERROR((G$37+G$38)/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="14">
         <f>IFERROR((H$37+H$38)/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I13" s="15">
+      <c r="I13" s="14">
         <f>IFERROR((I$37+I$38)/I$32,"n/a")</f>
         <v/>
       </c>
@@ -6945,35 +6911,35 @@
           <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="14">
         <f>IFERROR(B$38/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="14">
         <f>IFERROR(C$38/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="14">
         <f>IFERROR(D$38/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="14">
         <f>IFERROR(E$38/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="14">
         <f>IFERROR(F$38/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="14">
         <f>IFERROR(G$38/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="14">
         <f>IFERROR(H$38/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="14">
         <f>IFERROR(I$38/I$32,"n/a")</f>
         <v/>
       </c>
@@ -6984,74 +6950,74 @@
           <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="14">
         <f>IFERROR(B$37/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="14">
         <f>IFERROR(C$37/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="14">
         <f>IFERROR(D$37/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="14">
         <f>IFERROR(E$37/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="14">
         <f>IFERROR(F$37/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="14">
         <f>IFERROR(G$37/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="14">
         <f>IFERROR(H$37/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="14">
         <f>IFERROR(I$37/I$32,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Nợ phải trả/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="14">
         <f>IFERROR(B$34/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="14">
         <f>IFERROR(C$34/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="14">
         <f>IFERROR(D$34/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="14">
         <f>IFERROR(E$34/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="14">
         <f>IFERROR(F$34/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="14">
         <f>IFERROR(G$34/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="14">
         <f>IFERROR(H$34/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I16" s="15">
+      <c r="I16" s="14">
         <f>IFERROR(I$34/I$32,"n/a")</f>
         <v/>
       </c>
@@ -7062,35 +7028,35 @@
           <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="14">
         <f>IFERROR(B$36/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="14">
         <f>IFERROR(C$36/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="14">
         <f>IFERROR(D$36/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="14">
         <f>IFERROR(E$36/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="14">
         <f>IFERROR(F$36/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="14">
         <f>IFERROR(G$36/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="14">
         <f>IFERROR(H$36/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="14">
         <f>IFERROR(I$36/I$32,"n/a")</f>
         <v/>
       </c>
@@ -7101,387 +7067,387 @@
           <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="14">
         <f>IFERROR(B$35/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="14">
         <f>IFERROR(C$35/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="14">
         <f>IFERROR(D$35/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="14">
         <f>IFERROR(E$35/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="14">
         <f>IFERROR(F$35/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="14">
         <f>IFERROR(G$35/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="14">
         <f>IFERROR(H$35/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I18" s="15">
+      <c r="I18" s="14">
         <f>IFERROR(I$35/I$32,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>4. Chi phí &amp; khả năng trả lãi</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Chi phí bán hàng, quản lý/LN gộp</t>
         </is>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="13">
         <f>IFERROR((ABS(B$42)+ABS(B$43))/B$41,"n/a")</f>
         <v/>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13">
         <f>IFERROR((ABS(C$42)+ABS(C$43))/C$41,"n/a")</f>
         <v/>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="13">
         <f>IFERROR((ABS(D$42)+ABS(D$43))/D$41,"n/a")</f>
         <v/>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="13">
         <f>IFERROR((ABS(E$42)+ABS(E$43))/E$41,"n/a")</f>
         <v/>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="13">
         <f>IFERROR((ABS(F$42)+ABS(F$43))/F$41,"n/a")</f>
         <v/>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="13">
         <f>IFERROR((ABS(G$42)+ABS(G$43))/G$41,"n/a")</f>
         <v/>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="13">
         <f>IFERROR((ABS(H$42)+ABS(H$43))/H$41,"n/a")</f>
         <v/>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="13">
         <f>IFERROR((ABS(I$42)+ABS(I$43))/I$41,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="13">
         <f>IFERROR(ABS(B$45)/B$44,"n/a")</f>
         <v/>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="13">
         <f>IFERROR(ABS(C$45)/C$44,"n/a")</f>
         <v/>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="13">
         <f>IFERROR(ABS(D$45)/D$44,"n/a")</f>
         <v/>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="13">
         <f>IFERROR(ABS(E$45)/E$44,"n/a")</f>
         <v/>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="13">
         <f>IFERROR(ABS(F$45)/F$44,"n/a")</f>
         <v/>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="13">
         <f>IFERROR(ABS(G$45)/G$44,"n/a")</f>
         <v/>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="13">
         <f>IFERROR(ABS(H$45)/H$44,"n/a")</f>
         <v/>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="13">
         <f>IFERROR(ABS(I$45)/I$44,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>5. Chu kỳ hoạt động vốn lưu động</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Số ngày phải trả (DPO)</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="15">
         <f>IFERROR(((C$49+B$49)/2)/ABS(C$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="15">
         <f>IFERROR(((D$49+C$49)/2)/ABS(D$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="15">
         <f>IFERROR(((E$49+D$49)/2)/ABS(E$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="15">
         <f>IFERROR(((F$49+E$49)/2)/ABS(F$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="15">
         <f>IFERROR(((G$49+F$49)/2)/ABS(G$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="15">
         <f>IFERROR(((H$49+G$49)/2)/ABS(H$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="15">
         <f>IFERROR(((I$49+H$49)/2)/ABS(I$40)*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Số ngày phải thu (DSO)</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="15">
         <f>IFERROR(((C$48+B$48)/2)/C$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="15">
         <f>IFERROR(((D$48+C$48)/2)/D$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="15">
         <f>IFERROR(((E$48+D$48)/2)/E$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="15">
         <f>IFERROR(((F$48+E$48)/2)/F$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="15">
         <f>IFERROR(((G$48+F$48)/2)/G$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="15">
         <f>IFERROR(((H$48+G$48)/2)/H$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="15">
         <f>IFERROR(((I$48+H$48)/2)/I$39*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Số ngày tồn kho (DIO)</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="15">
         <f>IFERROR(((C$50+B$50)/2)/ABS(C$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="15">
         <f>IFERROR(((D$50+C$50)/2)/ABS(D$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="15">
         <f>IFERROR(((E$50+D$50)/2)/ABS(E$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="15">
         <f>IFERROR(((F$50+E$50)/2)/ABS(F$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="15">
         <f>IFERROR(((G$50+F$50)/2)/ABS(G$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="15">
         <f>IFERROR(((H$50+G$50)/2)/ABS(H$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="15">
         <f>IFERROR(((I$50+H$50)/2)/ABS(I$40)*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>6. Cơ cấu tài sản</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Tiền và tương đương tiền/Tài sản</t>
         </is>
       </c>
-      <c r="B27" s="14">
+      <c r="B27" s="13">
         <f>IFERROR(B$51/B$33,"n/a")</f>
         <v/>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13">
         <f>IFERROR(C$51/C$33,"n/a")</f>
         <v/>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13">
         <f>IFERROR(D$51/D$33,"n/a")</f>
         <v/>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="13">
         <f>IFERROR(E$51/E$33,"n/a")</f>
         <v/>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="13">
         <f>IFERROR(F$51/F$33,"n/a")</f>
         <v/>
       </c>
-      <c r="G27" s="14">
+      <c r="G27" s="13">
         <f>IFERROR(G$51/G$33,"n/a")</f>
         <v/>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="13">
         <f>IFERROR(H$51/H$33,"n/a")</f>
         <v/>
       </c>
-      <c r="I27" s="14">
+      <c r="I27" s="13">
         <f>IFERROR(I$51/I$33,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Hàng tồn kho/Tài sản</t>
         </is>
       </c>
-      <c r="B28" s="14">
+      <c r="B28" s="13">
         <f>IFERROR(B$50/B$33,"n/a")</f>
         <v/>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13">
         <f>IFERROR(C$50/C$33,"n/a")</f>
         <v/>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="13">
         <f>IFERROR(D$50/D$33,"n/a")</f>
         <v/>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="13">
         <f>IFERROR(E$50/E$33,"n/a")</f>
         <v/>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="13">
         <f>IFERROR(F$50/F$33,"n/a")</f>
         <v/>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="13">
         <f>IFERROR(G$50/G$33,"n/a")</f>
         <v/>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="13">
         <f>IFERROR(H$50/H$33,"n/a")</f>
         <v/>
       </c>
-      <c r="I28" s="14">
+      <c r="I28" s="13">
         <f>IFERROR(I$50/I$33,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="29"/>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
         </is>
       </c>
-      <c r="B30" s="19" t="n"/>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="19" t="n"/>
-      <c r="F30" s="19" t="n"/>
-      <c r="G30" s="19" t="n"/>
-      <c r="H30" s="19" t="n"/>
-      <c r="I30" s="19" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Khoản mục</t>
         </is>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="9">
         <f>'balance_sheet'!B1</f>
         <v/>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="9">
         <f>'balance_sheet'!C1</f>
         <v/>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="9">
         <f>'balance_sheet'!D1</f>
         <v/>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="9">
         <f>'balance_sheet'!E1</f>
         <v/>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="9">
         <f>'balance_sheet'!F1</f>
         <v/>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="9">
         <f>'balance_sheet'!G1</f>
         <v/>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="9">
         <f>'balance_sheet'!H1</f>
         <v/>
       </c>
-      <c r="I31" s="10">
+      <c r="I31" s="9">
         <f>'balance_sheet'!I1</f>
         <v/>
       </c>
@@ -7492,35 +7458,35 @@
           <t>Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C32" s="17">
+      <c r="C32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I32" s="17">
+      <c r="I32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7531,35 +7497,35 @@
           <t>TỔNG CỘNG TÀI SẢN</t>
         </is>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C33" s="17">
+      <c r="C33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D33" s="17">
+      <c r="D33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E33" s="17">
+      <c r="E33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="17">
+      <c r="G33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I33" s="17">
+      <c r="I33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7570,35 +7536,35 @@
           <t>NỢ PHẢI TRẢ</t>
         </is>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C34" s="17">
+      <c r="C34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D34" s="17">
+      <c r="D34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E34" s="17">
+      <c r="E34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H34" s="17">
+      <c r="H34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I34" s="17">
+      <c r="I34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7609,35 +7575,35 @@
           <t>Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C35" s="17">
+      <c r="C35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D35" s="17">
+      <c r="D35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E35" s="17">
+      <c r="E35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G35" s="17">
+      <c r="G35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H35" s="17">
+      <c r="H35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I35" s="17">
+      <c r="I35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7648,35 +7614,35 @@
           <t>Nợ dài hạn</t>
         </is>
       </c>
-      <c r="B36" s="17">
+      <c r="B36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C36" s="17">
+      <c r="C36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D36" s="17">
+      <c r="D36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E36" s="17">
+      <c r="E36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F36" s="17">
+      <c r="F36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G36" s="17">
+      <c r="G36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H36" s="17">
+      <c r="H36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I36" s="17">
+      <c r="I36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7687,35 +7653,35 @@
           <t>Vay ngắn hạn</t>
         </is>
       </c>
-      <c r="B37" s="17">
+      <c r="B37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C37" s="17">
+      <c r="C37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D37" s="17">
+      <c r="D37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E37" s="17">
+      <c r="E37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F37" s="17">
+      <c r="F37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G37" s="17">
+      <c r="G37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H37" s="17">
+      <c r="H37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I37" s="17">
+      <c r="I37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7726,35 +7692,35 @@
           <t>Vay dài hạn</t>
         </is>
       </c>
-      <c r="B38" s="17">
+      <c r="B38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C38" s="17">
+      <c r="C38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D38" s="17">
+      <c r="D38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E38" s="17">
+      <c r="E38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F38" s="17">
+      <c r="F38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G38" s="17">
+      <c r="G38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H38" s="17">
+      <c r="H38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I38" s="17">
+      <c r="I38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7765,35 +7731,35 @@
           <t>Doanh thu thuần</t>
         </is>
       </c>
-      <c r="B39" s="17">
+      <c r="B39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C39" s="17">
+      <c r="C39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D39" s="17">
+      <c r="D39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E39" s="17">
+      <c r="E39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F39" s="17">
+      <c r="F39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G39" s="17">
+      <c r="G39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H39" s="17">
+      <c r="H39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I39" s="17">
+      <c r="I39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7804,35 +7770,35 @@
           <t>Giá vốn hàng bán</t>
         </is>
       </c>
-      <c r="B40" s="17">
+      <c r="B40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C40" s="17">
+      <c r="C40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D40" s="17">
+      <c r="D40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E40" s="17">
+      <c r="E40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F40" s="17">
+      <c r="F40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G40" s="17">
+      <c r="G40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H40" s="17">
+      <c r="H40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I40" s="17">
+      <c r="I40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7843,35 +7809,35 @@
           <t>Lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B41" s="17">
+      <c r="B41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C41" s="17">
+      <c r="C41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D41" s="17">
+      <c r="D41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E41" s="17">
+      <c r="E41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F41" s="17">
+      <c r="F41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G41" s="17">
+      <c r="G41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H41" s="17">
+      <c r="H41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I41" s="17">
+      <c r="I41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7882,35 +7848,35 @@
           <t>Chi phí bán hàng</t>
         </is>
       </c>
-      <c r="B42" s="17">
+      <c r="B42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C42" s="17">
+      <c r="C42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D42" s="17">
+      <c r="D42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E42" s="17">
+      <c r="E42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F42" s="17">
+      <c r="F42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G42" s="17">
+      <c r="G42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H42" s="17">
+      <c r="H42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I42" s="17">
+      <c r="I42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7921,35 +7887,35 @@
           <t>Chi phí quản lý doanh nghiệp</t>
         </is>
       </c>
-      <c r="B43" s="17">
+      <c r="B43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C43" s="17">
+      <c r="C43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D43" s="17">
+      <c r="D43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E43" s="17">
+      <c r="E43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F43" s="17">
+      <c r="F43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G43" s="17">
+      <c r="G43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H43" s="17">
+      <c r="H43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I43" s="17">
+      <c r="I43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7960,35 +7926,35 @@
           <t>Lãi/(lỗ) từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B44" s="17">
+      <c r="B44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C44" s="17">
+      <c r="C44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D44" s="17">
+      <c r="D44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E44" s="17">
+      <c r="E44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F44" s="17">
+      <c r="F44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G44" s="17">
+      <c r="G44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H44" s="17">
+      <c r="H44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I44" s="17">
+      <c r="I44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7999,35 +7965,35 @@
           <t>Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B45" s="17">
+      <c r="B45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C45" s="17">
+      <c r="C45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D45" s="17">
+      <c r="D45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E45" s="17">
+      <c r="E45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F45" s="17">
+      <c r="F45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G45" s="17">
+      <c r="G45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H45" s="17">
+      <c r="H45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I45" s="17">
+      <c r="I45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -8038,35 +8004,35 @@
           <t>Lãi/(lỗ) thuần sau thuế</t>
         </is>
       </c>
-      <c r="B46" s="17">
+      <c r="B46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C46" s="17">
+      <c r="C46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D46" s="17">
+      <c r="D46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E46" s="17">
+      <c r="E46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F46" s="17">
+      <c r="F46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G46" s="17">
+      <c r="G46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H46" s="17">
+      <c r="H46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I46" s="17">
+      <c r="I46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -8077,35 +8043,35 @@
           <t>Lợi nhuận của Cổ đông của Công ty mẹ</t>
         </is>
       </c>
-      <c r="B47" s="17">
+      <c r="B47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C47" s="17">
+      <c r="C47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D47" s="17">
+      <c r="D47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E47" s="17">
+      <c r="E47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F47" s="17">
+      <c r="F47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G47" s="17">
+      <c r="G47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H47" s="17">
+      <c r="H47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I47" s="17">
+      <c r="I47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -8116,35 +8082,35 @@
           <t>Phải thu khách hàng</t>
         </is>
       </c>
-      <c r="B48" s="17">
+      <c r="B48" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C48" s="17">
+      <c r="C48" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D48" s="17">
+      <c r="D48" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E48" s="17">
+      <c r="E48" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F48" s="17">
+      <c r="F48" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G48" s="17">
+      <c r="G48" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H48" s="17">
+      <c r="H48" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I48" s="17">
+      <c r="I48" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -8155,35 +8121,35 @@
           <t>Phải trả người bán</t>
         </is>
       </c>
-      <c r="B49" s="17">
+      <c r="B49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C49" s="17">
+      <c r="C49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D49" s="17">
+      <c r="D49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E49" s="17">
+      <c r="E49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F49" s="17">
+      <c r="F49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G49" s="17">
+      <c r="G49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H49" s="17">
+      <c r="H49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="17">
+      <c r="I49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -8194,35 +8160,35 @@
           <t>Hàng tồn kho, ròng</t>
         </is>
       </c>
-      <c r="B50" s="17">
+      <c r="B50" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C50" s="17">
+      <c r="C50" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D50" s="17">
+      <c r="D50" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E50" s="17">
+      <c r="E50" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F50" s="17">
+      <c r="F50" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G50" s="17">
+      <c r="G50" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H50" s="17">
+      <c r="H50" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I50" s="17">
+      <c r="I50" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -8233,35 +8199,35 @@
           <t>Tiền và tương đương tiền</t>
         </is>
       </c>
-      <c r="B51" s="17">
+      <c r="B51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C51" s="17">
+      <c r="C51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D51" s="17">
+      <c r="D51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E51" s="17">
+      <c r="E51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F51" s="17">
+      <c r="F51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G51" s="17">
+      <c r="G51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H51" s="17">
+      <c r="H51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I51" s="17">
+      <c r="I51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -8270,78 +8236,6 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:I5">
-    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6:I6">
-    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7:I7">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8:I8">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10:I10">
-    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11:I11">
-    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13:I13">
-    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="1">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="0">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16:I16">
-    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="1">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="0">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B21:I21">
-    <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="1">
-      <formula>0.5</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="0">
-      <formula>0.15</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>